--- a/Data/senate_general_polls_2026.xlsx
+++ b/Data/senate_general_polls_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennyqu/Library/CloudStorage/OneDrive-WilfridLaurierUniversity/us_trade_conflict/us_trade_conflict/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{083194C0-0DC6-9249-A46D-DB7FB2FE5F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_missing-docid_{4C5FDBE2-870F-6348-8296-D509506434A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16660" xr2:uid="{03306125-F0D3-F642-8A56-CAC244325849}"/>
   </bookViews>

--- a/Data/senate_general_polls_2026.xlsx
+++ b/Data/senate_general_polls_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennyqu/Library/CloudStorage/OneDrive-WilfridLaurierUniversity/us_trade_conflict/us_trade_conflict/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D93E97C7-B978-EA47-884B-E6FCDC4B1A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{62722A5A-5EA5-9349-804C-AA0C9F34F560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16660" xr2:uid="{03306125-F0D3-F642-8A56-CAC244325849}"/>
+    <workbookView xWindow="5600" yWindow="1760" windowWidth="28040" windowHeight="16660" xr2:uid="{03306125-F0D3-F642-8A56-CAC244325849}"/>
   </bookViews>
   <sheets>
     <sheet name="senate_general_polls_2026" sheetId="1" r:id="rId1"/>
@@ -3197,8 +3197,14 @@
       <c r="D2" t="s">
         <v>22</v>
       </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
       <c r="F2" t="s">
         <v>23</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -3256,8 +3262,14 @@
       <c r="D3" t="s">
         <v>31</v>
       </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
       <c r="F3" t="s">
         <v>32</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3" t="s">
         <v>33</v>
@@ -3315,8 +3327,14 @@
       <c r="D4" t="s">
         <v>31</v>
       </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
       <c r="F4" t="s">
         <v>32</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
       <c r="H4" t="s">
         <v>38</v>
@@ -3374,8 +3392,14 @@
       <c r="D5" t="s">
         <v>31</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
       <c r="F5" t="s">
         <v>32</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
       <c r="H5" t="s">
         <v>33</v>
@@ -3433,8 +3457,14 @@
       <c r="D6" t="s">
         <v>31</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
       <c r="F6" t="s">
         <v>32</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
@@ -3492,8 +3522,14 @@
       <c r="D7" t="s">
         <v>31</v>
       </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
       <c r="F7" t="s">
         <v>32</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
       <c r="H7" t="s">
         <v>38</v>
@@ -3551,8 +3587,14 @@
       <c r="D8" t="s">
         <v>31</v>
       </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
       <c r="F8" t="s">
         <v>32</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
       <c r="H8" t="s">
         <v>33</v>
@@ -3610,8 +3652,14 @@
       <c r="D9" t="s">
         <v>31</v>
       </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
       <c r="F9" t="s">
         <v>32</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
       <c r="H9" t="s">
         <v>44</v>
@@ -3669,8 +3717,14 @@
       <c r="D10" t="s">
         <v>48</v>
       </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
       <c r="F10" t="s">
         <v>49</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
       </c>
       <c r="H10" t="s">
         <v>33</v>
@@ -3728,8 +3782,14 @@
       <c r="D11" t="s">
         <v>31</v>
       </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
       <c r="F11" t="s">
         <v>32</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -3787,8 +3847,14 @@
       <c r="D12" t="s">
         <v>52</v>
       </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
       <c r="F12" t="s">
         <v>53</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>33</v>
@@ -3846,8 +3912,14 @@
       <c r="D13" t="s">
         <v>52</v>
       </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
       <c r="F13" t="s">
         <v>53</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>33</v>
@@ -3905,8 +3977,14 @@
       <c r="D14" t="s">
         <v>52</v>
       </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
       <c r="F14" t="s">
         <v>53</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
@@ -3964,8 +4042,14 @@
       <c r="D15" t="s">
         <v>31</v>
       </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
       <c r="F15" t="s">
         <v>32</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>33</v>
@@ -4023,8 +4107,14 @@
       <c r="D16" t="s">
         <v>52</v>
       </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
       <c r="F16" t="s">
         <v>53</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>33</v>
@@ -4082,8 +4172,14 @@
       <c r="D17" t="s">
         <v>52</v>
       </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
       <c r="F17" t="s">
         <v>53</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>33</v>
@@ -4141,8 +4237,14 @@
       <c r="D18" t="s">
         <v>31</v>
       </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
       <c r="F18" t="s">
         <v>32</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
       </c>
       <c r="H18" t="s">
         <v>33</v>
@@ -4200,8 +4302,14 @@
       <c r="D19" t="s">
         <v>31</v>
       </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
       <c r="F19" t="s">
         <v>32</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>33</v>
@@ -4259,8 +4367,14 @@
       <c r="D20" t="s">
         <v>31</v>
       </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
       <c r="F20" t="s">
         <v>32</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>57</v>
@@ -4318,8 +4432,14 @@
       <c r="D21" t="s">
         <v>52</v>
       </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
       <c r="F21" t="s">
         <v>53</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
       </c>
       <c r="H21" t="s">
         <v>38</v>
@@ -4377,8 +4497,14 @@
       <c r="D22" t="s">
         <v>52</v>
       </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
       <c r="F22" t="s">
         <v>53</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>38</v>
@@ -4436,8 +4562,14 @@
       <c r="D23" t="s">
         <v>52</v>
       </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
       <c r="F23" t="s">
         <v>53</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
       </c>
       <c r="H23" t="s">
         <v>38</v>
@@ -4495,8 +4627,14 @@
       <c r="D24" t="s">
         <v>52</v>
       </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
       <c r="F24" t="s">
         <v>53</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
       </c>
       <c r="H24" t="s">
         <v>38</v>
@@ -4554,8 +4692,14 @@
       <c r="D25" t="s">
         <v>52</v>
       </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
       <c r="F25" t="s">
         <v>53</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
       </c>
       <c r="H25" t="s">
         <v>38</v>
@@ -4613,8 +4757,14 @@
       <c r="D26" t="s">
         <v>31</v>
       </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
       <c r="F26" t="s">
         <v>32</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
       </c>
       <c r="H26" t="s">
         <v>38</v>
@@ -4672,8 +4822,14 @@
       <c r="D27" t="s">
         <v>31</v>
       </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
       <c r="F27" t="s">
         <v>32</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
       </c>
       <c r="H27" t="s">
         <v>33</v>
@@ -4731,8 +4887,14 @@
       <c r="D28" t="s">
         <v>31</v>
       </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
       <c r="F28" t="s">
         <v>32</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
       </c>
       <c r="H28" t="s">
         <v>33</v>
@@ -4790,8 +4952,14 @@
       <c r="D29" t="s">
         <v>52</v>
       </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
       <c r="F29" t="s">
         <v>53</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
       </c>
       <c r="H29" t="s">
         <v>63</v>
@@ -4849,8 +5017,14 @@
       <c r="D30" t="s">
         <v>52</v>
       </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
       <c r="F30" t="s">
         <v>53</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
       </c>
       <c r="H30" t="s">
         <v>63</v>
@@ -4908,8 +5082,14 @@
       <c r="D31" t="s">
         <v>52</v>
       </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
       <c r="F31" t="s">
         <v>53</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
       </c>
       <c r="H31" t="s">
         <v>63</v>
@@ -4967,8 +5147,14 @@
       <c r="D32" t="s">
         <v>52</v>
       </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
       <c r="F32" t="s">
         <v>53</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
       </c>
       <c r="H32" t="s">
         <v>63</v>
@@ -5026,8 +5212,14 @@
       <c r="D33" t="s">
         <v>31</v>
       </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
       <c r="F33" t="s">
         <v>32</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
       </c>
       <c r="H33" t="s">
         <v>63</v>
@@ -5085,8 +5277,14 @@
       <c r="D34" t="s">
         <v>31</v>
       </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
       <c r="F34" t="s">
         <v>32</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
       </c>
       <c r="H34" t="s">
         <v>65</v>
@@ -5144,8 +5342,14 @@
       <c r="D35" t="s">
         <v>31</v>
       </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
       <c r="F35" t="s">
         <v>32</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
       </c>
       <c r="H35" t="s">
         <v>67</v>
@@ -5203,8 +5407,14 @@
       <c r="D36" t="s">
         <v>31</v>
       </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
       <c r="F36" t="s">
         <v>32</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
       </c>
       <c r="H36" t="s">
         <v>67</v>
@@ -5262,8 +5472,14 @@
       <c r="D37" t="s">
         <v>71</v>
       </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
       <c r="F37" t="s">
         <v>72</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
       </c>
       <c r="H37" t="s">
         <v>73</v>
@@ -5321,8 +5537,14 @@
       <c r="D38" t="s">
         <v>71</v>
       </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
       <c r="F38" t="s">
         <v>72</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
       </c>
       <c r="H38" t="s">
         <v>76</v>
@@ -5380,8 +5602,14 @@
       <c r="D39" t="s">
         <v>71</v>
       </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
       <c r="F39" t="s">
         <v>72</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
       </c>
       <c r="H39" t="s">
         <v>78</v>
@@ -5439,8 +5667,14 @@
       <c r="D40" t="s">
         <v>71</v>
       </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
       <c r="F40" t="s">
         <v>72</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
       </c>
       <c r="H40" t="s">
         <v>80</v>
@@ -5498,8 +5732,14 @@
       <c r="D41" t="s">
         <v>85</v>
       </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
       <c r="F41" t="s">
         <v>86</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>87</v>
@@ -5557,8 +5797,14 @@
       <c r="D42" t="s">
         <v>85</v>
       </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
       <c r="F42" t="s">
         <v>86</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>90</v>
@@ -5616,8 +5862,14 @@
       <c r="D43" t="s">
         <v>85</v>
       </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
       <c r="F43" t="s">
         <v>86</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>90</v>
@@ -5675,8 +5927,14 @@
       <c r="D44" t="s">
         <v>93</v>
       </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
       <c r="F44" t="s">
         <v>94</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>90</v>
@@ -5734,8 +5992,14 @@
       <c r="D45" t="s">
         <v>97</v>
       </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
       <c r="F45" t="s">
         <v>86</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>90</v>
@@ -5793,8 +6057,14 @@
       <c r="D46" t="s">
         <v>93</v>
       </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
       <c r="F46" t="s">
         <v>94</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
       </c>
       <c r="H46" t="s">
         <v>98</v>
@@ -5852,8 +6122,14 @@
       <c r="D47" t="s">
         <v>97</v>
       </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
       <c r="F47" t="s">
         <v>86</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
       </c>
       <c r="H47" t="s">
         <v>98</v>
@@ -5911,8 +6187,14 @@
       <c r="D48" t="s">
         <v>101</v>
       </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
       <c r="F48" t="s">
         <v>86</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
       </c>
       <c r="H48" t="s">
         <v>98</v>
@@ -5970,8 +6252,14 @@
       <c r="D49" t="s">
         <v>97</v>
       </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
       <c r="F49" t="s">
         <v>86</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
       </c>
       <c r="H49" t="s">
         <v>102</v>
@@ -6029,8 +6317,14 @@
       <c r="D50" t="s">
         <v>97</v>
       </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
       <c r="F50" t="s">
         <v>86</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
       </c>
       <c r="H50" t="s">
         <v>44</v>
@@ -6088,8 +6382,14 @@
       <c r="D51" t="s">
         <v>97</v>
       </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
       <c r="F51" t="s">
         <v>86</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
       </c>
       <c r="H51" t="s">
         <v>106</v>
@@ -6147,8 +6447,14 @@
       <c r="D52" t="s">
         <v>93</v>
       </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
       <c r="F52" t="s">
         <v>94</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
       </c>
       <c r="H52" t="s">
         <v>108</v>
@@ -6206,8 +6512,14 @@
       <c r="D53" t="s">
         <v>97</v>
       </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
       <c r="F53" t="s">
         <v>86</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
       </c>
       <c r="H53" t="s">
         <v>108</v>
@@ -6265,8 +6577,14 @@
       <c r="D54" t="s">
         <v>97</v>
       </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
       <c r="F54" t="s">
         <v>86</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
       </c>
       <c r="H54" t="s">
         <v>110</v>
@@ -6324,8 +6642,14 @@
       <c r="D55" t="s">
         <v>97</v>
       </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
       <c r="F55" t="s">
         <v>86</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
       </c>
       <c r="H55" t="s">
         <v>112</v>
@@ -6383,8 +6707,14 @@
       <c r="D56" t="s">
         <v>97</v>
       </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
       <c r="F56" t="s">
         <v>86</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
       </c>
       <c r="H56" t="s">
         <v>114</v>
@@ -6442,8 +6772,14 @@
       <c r="D57" t="s">
         <v>97</v>
       </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
       <c r="F57" t="s">
         <v>86</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
       </c>
       <c r="H57" t="s">
         <v>116</v>
@@ -6501,8 +6837,14 @@
       <c r="D58" t="s">
         <v>97</v>
       </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
       <c r="F58" t="s">
         <v>86</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
       </c>
       <c r="H58" t="s">
         <v>112</v>
@@ -6560,8 +6902,14 @@
       <c r="D59" t="s">
         <v>93</v>
       </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
       <c r="F59" t="s">
         <v>94</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
       </c>
       <c r="H59" t="s">
         <v>90</v>
@@ -6619,8 +6967,14 @@
       <c r="D60" t="s">
         <v>97</v>
       </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
       <c r="F60" t="s">
         <v>86</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
       </c>
       <c r="H60" t="s">
         <v>90</v>
@@ -6678,8 +7032,14 @@
       <c r="D61" t="s">
         <v>93</v>
       </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
       <c r="F61" t="s">
         <v>94</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
       </c>
       <c r="H61" t="s">
         <v>112</v>
@@ -6737,8 +7097,14 @@
       <c r="D62" t="s">
         <v>93</v>
       </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
       <c r="F62" t="s">
         <v>94</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
       </c>
       <c r="H62" t="s">
         <v>121</v>
@@ -6796,8 +7162,14 @@
       <c r="D63" t="s">
         <v>93</v>
       </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
       <c r="F63" t="s">
         <v>94</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
       </c>
       <c r="H63" t="s">
         <v>123</v>
@@ -6855,8 +7227,14 @@
       <c r="D64" t="s">
         <v>127</v>
       </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
       <c r="F64" t="s">
         <v>128</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
       </c>
       <c r="H64" t="s">
         <v>129</v>
@@ -6914,8 +7292,14 @@
       <c r="D65" t="s">
         <v>133</v>
       </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
       <c r="F65" t="s">
         <v>134</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
       </c>
       <c r="H65" t="s">
         <v>129</v>
@@ -6973,8 +7357,14 @@
       <c r="D66" t="s">
         <v>133</v>
       </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
       <c r="F66" t="s">
         <v>136</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
       </c>
       <c r="H66" t="s">
         <v>129</v>
@@ -7032,8 +7422,14 @@
       <c r="D67" t="s">
         <v>133</v>
       </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
       <c r="F67" t="s">
         <v>138</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
       </c>
       <c r="H67" t="s">
         <v>129</v>
@@ -7091,8 +7487,14 @@
       <c r="D68" t="s">
         <v>133</v>
       </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
       <c r="F68" t="s">
         <v>140</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
       </c>
       <c r="H68" t="s">
         <v>129</v>
@@ -7150,8 +7552,14 @@
       <c r="D69" t="s">
         <v>133</v>
       </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
       <c r="F69" t="s">
         <v>142</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
       </c>
       <c r="H69" t="s">
         <v>129</v>
@@ -7209,8 +7617,14 @@
       <c r="D70" t="s">
         <v>133</v>
       </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
       <c r="F70" t="s">
         <v>134</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
       </c>
       <c r="H70" t="s">
         <v>143</v>
@@ -7268,8 +7682,14 @@
       <c r="D71" t="s">
         <v>133</v>
       </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
       <c r="F71" t="s">
         <v>138</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
       </c>
       <c r="H71" t="s">
         <v>143</v>
@@ -7327,8 +7747,14 @@
       <c r="D72" t="s">
         <v>133</v>
       </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
       <c r="F72" t="s">
         <v>146</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
       </c>
       <c r="H72" t="s">
         <v>143</v>
@@ -7386,8 +7812,14 @@
       <c r="D73" t="s">
         <v>133</v>
       </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
       <c r="F73" t="s">
         <v>138</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
       </c>
       <c r="H73" t="s">
         <v>121</v>
@@ -7445,8 +7877,14 @@
       <c r="D74" t="s">
         <v>133</v>
       </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
       <c r="F74" t="s">
         <v>136</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
       </c>
       <c r="H74" t="s">
         <v>148</v>
@@ -7504,8 +7942,14 @@
       <c r="D75" t="s">
         <v>133</v>
       </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
       <c r="F75" t="s">
         <v>138</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
       </c>
       <c r="H75" t="s">
         <v>148</v>
@@ -7563,8 +8007,14 @@
       <c r="D76" t="s">
         <v>133</v>
       </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
       <c r="F76" t="s">
         <v>140</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
       </c>
       <c r="H76" t="s">
         <v>148</v>
@@ -7622,8 +8072,14 @@
       <c r="D77" t="s">
         <v>133</v>
       </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
       <c r="F77" t="s">
         <v>146</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
       </c>
       <c r="H77" t="s">
         <v>148</v>
@@ -7681,8 +8137,14 @@
       <c r="D78" t="s">
         <v>127</v>
       </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
       <c r="F78" t="s">
         <v>128</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
       </c>
       <c r="H78" t="s">
         <v>150</v>
@@ -7740,8 +8202,14 @@
       <c r="D79" t="s">
         <v>133</v>
       </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
       <c r="F79" t="s">
         <v>136</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
       </c>
       <c r="H79" t="s">
         <v>150</v>
@@ -7799,8 +8267,14 @@
       <c r="D80" t="s">
         <v>133</v>
       </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
       <c r="F80" t="s">
         <v>146</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
       </c>
       <c r="H80" t="s">
         <v>150</v>
@@ -7858,8 +8332,14 @@
       <c r="D81" t="s">
         <v>127</v>
       </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
       <c r="F81" t="s">
         <v>128</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
       </c>
       <c r="H81" t="s">
         <v>152</v>
@@ -7917,8 +8397,14 @@
       <c r="D82" t="s">
         <v>133</v>
       </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
       <c r="F82" t="s">
         <v>134</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
       </c>
       <c r="H82" t="s">
         <v>152</v>
@@ -7976,8 +8462,14 @@
       <c r="D83" t="s">
         <v>133</v>
       </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
       <c r="F83" t="s">
         <v>136</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
       </c>
       <c r="H83" t="s">
         <v>152</v>
@@ -8035,8 +8527,14 @@
       <c r="D84" t="s">
         <v>133</v>
       </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
       <c r="F84" t="s">
         <v>140</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
       </c>
       <c r="H84" t="s">
         <v>152</v>
@@ -8094,8 +8592,14 @@
       <c r="D85" t="s">
         <v>133</v>
       </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
       <c r="F85" t="s">
         <v>155</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
       </c>
       <c r="H85" t="s">
         <v>152</v>
@@ -8153,8 +8657,14 @@
       <c r="D86" t="s">
         <v>133</v>
       </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
       <c r="F86" t="s">
         <v>134</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
       </c>
       <c r="H86" t="s">
         <v>152</v>
@@ -8212,8 +8722,14 @@
       <c r="D87" t="s">
         <v>133</v>
       </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
       <c r="F87" t="s">
         <v>140</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
       </c>
       <c r="H87" t="s">
         <v>152</v>
@@ -8271,8 +8787,14 @@
       <c r="D88" t="s">
         <v>127</v>
       </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
       <c r="F88" t="s">
         <v>128</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
       </c>
       <c r="H88" t="s">
         <v>157</v>
@@ -8330,8 +8852,14 @@
       <c r="D89" t="s">
         <v>133</v>
       </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
       <c r="F89" t="s">
         <v>155</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
       </c>
       <c r="H89" t="s">
         <v>157</v>
@@ -8389,8 +8917,14 @@
       <c r="D90" t="s">
         <v>133</v>
       </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
       <c r="F90" t="s">
         <v>134</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
       </c>
       <c r="H90" t="s">
         <v>157</v>
@@ -8448,8 +8982,14 @@
       <c r="D91" t="s">
         <v>127</v>
       </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
       <c r="F91" t="s">
         <v>128</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
       </c>
       <c r="H91" t="s">
         <v>121</v>
@@ -8507,8 +9047,14 @@
       <c r="D92" t="s">
         <v>133</v>
       </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
       <c r="F92" t="s">
         <v>155</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
       </c>
       <c r="H92" t="s">
         <v>121</v>
@@ -8566,8 +9112,14 @@
       <c r="D93" t="s">
         <v>133</v>
       </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
       <c r="F93" t="s">
         <v>134</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
       </c>
       <c r="H93" t="s">
         <v>121</v>
@@ -8625,8 +9177,14 @@
       <c r="D94" t="s">
         <v>127</v>
       </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
       <c r="F94" t="s">
         <v>128</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
       </c>
       <c r="H94" t="s">
         <v>98</v>
@@ -8684,8 +9242,14 @@
       <c r="D95" t="s">
         <v>133</v>
       </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
       <c r="F95" t="s">
         <v>155</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
       </c>
       <c r="H95" t="s">
         <v>98</v>
@@ -8743,8 +9307,14 @@
       <c r="D96" t="s">
         <v>133</v>
       </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
       <c r="F96" t="s">
         <v>134</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
       </c>
       <c r="H96" t="s">
         <v>98</v>
@@ -8802,8 +9372,14 @@
       <c r="D97" t="s">
         <v>127</v>
       </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
       <c r="F97" t="s">
         <v>128</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
       </c>
       <c r="H97" t="s">
         <v>106</v>
@@ -8861,8 +9437,14 @@
       <c r="D98" t="s">
         <v>133</v>
       </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
       <c r="F98" t="s">
         <v>134</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
       </c>
       <c r="H98" t="s">
         <v>106</v>
@@ -8920,8 +9502,14 @@
       <c r="D99" t="s">
         <v>127</v>
       </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
       <c r="F99" t="s">
         <v>128</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
       </c>
       <c r="H99" t="s">
         <v>161</v>
@@ -8979,8 +9567,14 @@
       <c r="D100" t="s">
         <v>127</v>
       </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
       <c r="F100" t="s">
         <v>128</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
       </c>
       <c r="H100" t="s">
         <v>163</v>
@@ -9038,8 +9632,14 @@
       <c r="D101" t="s">
         <v>127</v>
       </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
       <c r="F101" t="s">
         <v>128</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
       </c>
       <c r="H101" t="s">
         <v>63</v>
@@ -9097,8 +9697,14 @@
       <c r="D102" t="s">
         <v>127</v>
       </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
       <c r="F102" t="s">
         <v>128</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
       </c>
       <c r="H102" t="s">
         <v>166</v>
@@ -9156,8 +9762,14 @@
       <c r="D103" t="s">
         <v>127</v>
       </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
       <c r="F103" t="s">
         <v>128</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
       </c>
       <c r="H103" t="s">
         <v>150</v>
@@ -9215,8 +9827,14 @@
       <c r="D104" t="s">
         <v>127</v>
       </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
       <c r="F104" t="s">
         <v>128</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
       </c>
       <c r="H104" t="s">
         <v>65</v>
@@ -9274,8 +9892,14 @@
       <c r="D105" t="s">
         <v>127</v>
       </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
       <c r="F105" t="s">
         <v>128</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
       </c>
       <c r="H105" t="s">
         <v>121</v>
@@ -9333,8 +9957,14 @@
       <c r="D106" t="s">
         <v>172</v>
       </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
       <c r="F106" t="s">
         <v>173</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
       </c>
       <c r="H106" t="s">
         <v>174</v>
@@ -9392,8 +10022,14 @@
       <c r="D107" t="s">
         <v>172</v>
       </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
       <c r="F107" t="s">
         <v>173</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
       </c>
       <c r="H107" t="s">
         <v>177</v>
@@ -9451,8 +10087,14 @@
       <c r="D108" t="s">
         <v>172</v>
       </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
       <c r="F108" t="s">
         <v>173</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
       </c>
       <c r="H108" t="s">
         <v>179</v>
@@ -9510,8 +10152,14 @@
       <c r="D109" t="s">
         <v>183</v>
       </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
       <c r="F109" t="s">
         <v>184</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
       </c>
       <c r="H109" t="s">
         <v>44</v>
@@ -9569,8 +10217,14 @@
       <c r="D110" t="s">
         <v>188</v>
       </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
       <c r="F110" t="s">
         <v>184</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
       </c>
       <c r="H110" t="s">
         <v>44</v>
@@ -9628,8 +10282,14 @@
       <c r="D111" t="s">
         <v>190</v>
       </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
       <c r="F111" t="s">
         <v>184</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
       </c>
       <c r="H111" t="s">
         <v>44</v>
@@ -9687,8 +10347,14 @@
       <c r="D112" t="s">
         <v>192</v>
       </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
       <c r="F112" t="s">
         <v>184</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
       </c>
       <c r="H112" t="s">
         <v>44</v>
@@ -9746,8 +10412,14 @@
       <c r="D113" t="s">
         <v>194</v>
       </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
       <c r="F113" t="s">
         <v>195</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
       </c>
       <c r="H113" t="s">
         <v>112</v>
@@ -9805,8 +10477,14 @@
       <c r="D114" t="s">
         <v>188</v>
       </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
       <c r="F114" t="s">
         <v>197</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
       </c>
       <c r="H114" t="s">
         <v>112</v>
@@ -9864,8 +10542,14 @@
       <c r="D115" t="s">
         <v>192</v>
       </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
       <c r="F115" t="s">
         <v>197</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
       </c>
       <c r="H115" t="s">
         <v>112</v>
@@ -9923,8 +10607,14 @@
       <c r="D116" t="s">
         <v>194</v>
       </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
       <c r="F116" t="s">
         <v>195</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
       </c>
       <c r="H116" t="s">
         <v>199</v>
@@ -9982,8 +10672,14 @@
       <c r="D117" t="s">
         <v>192</v>
       </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
       <c r="F117" t="s">
         <v>197</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
       </c>
       <c r="H117" t="s">
         <v>199</v>
@@ -10041,8 +10737,14 @@
       <c r="D118" t="s">
         <v>194</v>
       </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
       <c r="F118" t="s">
         <v>195</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
       </c>
       <c r="H118" t="s">
         <v>106</v>
@@ -10100,8 +10802,14 @@
       <c r="D119" t="s">
         <v>192</v>
       </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
       <c r="F119" t="s">
         <v>197</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
       </c>
       <c r="H119" t="s">
         <v>106</v>
@@ -10159,8 +10867,14 @@
       <c r="D120" t="s">
         <v>194</v>
       </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
       <c r="F120" t="s">
         <v>195</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
       </c>
       <c r="H120" t="s">
         <v>44</v>
@@ -10218,8 +10932,14 @@
       <c r="D121" t="s">
         <v>194</v>
       </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
       <c r="F121" t="s">
         <v>195</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
       </c>
       <c r="H121" t="s">
         <v>114</v>
@@ -10277,8 +10997,14 @@
       <c r="D122" t="s">
         <v>194</v>
       </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
       <c r="F122" t="s">
         <v>195</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
       </c>
       <c r="H122" t="s">
         <v>152</v>
@@ -10336,8 +11062,14 @@
       <c r="D123" t="s">
         <v>194</v>
       </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
       <c r="F123" t="s">
         <v>195</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
       </c>
       <c r="H123" t="s">
         <v>161</v>
@@ -10395,8 +11127,14 @@
       <c r="D124" t="s">
         <v>194</v>
       </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
       <c r="F124" t="s">
         <v>195</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
       </c>
       <c r="H124" t="s">
         <v>57</v>
@@ -10454,8 +11192,14 @@
       <c r="D125" t="s">
         <v>194</v>
       </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
       <c r="F125" t="s">
         <v>195</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
       </c>
       <c r="H125" t="s">
         <v>98</v>
@@ -10513,8 +11257,14 @@
       <c r="D126" t="s">
         <v>194</v>
       </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
       <c r="F126" t="s">
         <v>195</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
       </c>
       <c r="H126" t="s">
         <v>206</v>
@@ -10572,8 +11322,14 @@
       <c r="D127" t="s">
         <v>194</v>
       </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
       <c r="F127" t="s">
         <v>195</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
       </c>
       <c r="H127" t="s">
         <v>207</v>
@@ -10631,8 +11387,14 @@
       <c r="D128" t="s">
         <v>194</v>
       </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
       <c r="F128" t="s">
         <v>195</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
       </c>
       <c r="H128" t="s">
         <v>207</v>
@@ -10690,8 +11452,14 @@
       <c r="D129" t="s">
         <v>194</v>
       </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
       <c r="F129" t="s">
         <v>195</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
       </c>
       <c r="H129" t="s">
         <v>209</v>
@@ -10749,8 +11517,14 @@
       <c r="D130" t="s">
         <v>194</v>
       </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
       <c r="F130" t="s">
         <v>195</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
       </c>
       <c r="H130" t="s">
         <v>114</v>
@@ -10808,8 +11582,14 @@
       <c r="D131" t="s">
         <v>194</v>
       </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
       <c r="F131" t="s">
         <v>195</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
       </c>
       <c r="H131" t="s">
         <v>98</v>
@@ -10867,8 +11647,14 @@
       <c r="D132" t="s">
         <v>194</v>
       </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
       <c r="F132" t="s">
         <v>195</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
       </c>
       <c r="H132" t="s">
         <v>213</v>
@@ -10926,8 +11712,14 @@
       <c r="D133" t="s">
         <v>194</v>
       </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
       <c r="F133" t="s">
         <v>195</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
       </c>
       <c r="H133" t="s">
         <v>213</v>
@@ -10985,8 +11777,14 @@
       <c r="D134" t="s">
         <v>194</v>
       </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
       <c r="F134" t="s">
         <v>195</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
       </c>
       <c r="H134" t="s">
         <v>65</v>
@@ -11044,8 +11842,14 @@
       <c r="D135" t="s">
         <v>194</v>
       </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
       <c r="F135" t="s">
         <v>195</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
       </c>
       <c r="H135" t="s">
         <v>67</v>
@@ -11103,8 +11907,14 @@
       <c r="D136" t="s">
         <v>194</v>
       </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
       <c r="F136" t="s">
         <v>195</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
       </c>
       <c r="H136" t="s">
         <v>67</v>
@@ -11162,8 +11972,14 @@
       <c r="D137" t="s">
         <v>217</v>
       </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
       <c r="F137" t="s">
         <v>218</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
       </c>
       <c r="H137" t="s">
         <v>219</v>
@@ -11221,8 +12037,14 @@
       <c r="D138" t="s">
         <v>223</v>
       </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
       <c r="F138" t="s">
         <v>224</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
       </c>
       <c r="H138" t="s">
         <v>219</v>
@@ -11280,8 +12102,14 @@
       <c r="D139" t="s">
         <v>226</v>
       </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
       <c r="F139" t="s">
         <v>224</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
       </c>
       <c r="H139" t="s">
         <v>219</v>
@@ -11339,8 +12167,14 @@
       <c r="D140" t="s">
         <v>226</v>
       </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
       <c r="F140" t="s">
         <v>224</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
       </c>
       <c r="H140" t="s">
         <v>199</v>
@@ -11398,8 +12232,14 @@
       <c r="D141" t="s">
         <v>217</v>
       </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
       <c r="F141" t="s">
         <v>218</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
       </c>
       <c r="H141" t="s">
         <v>228</v>
@@ -11457,8 +12297,14 @@
       <c r="D142" t="s">
         <v>217</v>
       </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
       <c r="F142" t="s">
         <v>218</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
       </c>
       <c r="H142" t="s">
         <v>44</v>
@@ -11516,8 +12362,14 @@
       <c r="D143" t="s">
         <v>217</v>
       </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
       <c r="F143" t="s">
         <v>218</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
       </c>
       <c r="H143" t="s">
         <v>114</v>
@@ -11575,8 +12427,14 @@
       <c r="D144" t="s">
         <v>217</v>
       </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
       <c r="F144" t="s">
         <v>218</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
       </c>
       <c r="H144" t="s">
         <v>67</v>
@@ -11634,8 +12492,14 @@
       <c r="D145" t="s">
         <v>217</v>
       </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
       <c r="F145" t="s">
         <v>218</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
       </c>
       <c r="H145" t="s">
         <v>98</v>
@@ -11693,8 +12557,14 @@
       <c r="D146" t="s">
         <v>235</v>
       </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
       <c r="F146" t="s">
         <v>236</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
       </c>
       <c r="H146" t="s">
         <v>44</v>
@@ -11752,8 +12622,14 @@
       <c r="D147" t="s">
         <v>235</v>
       </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
       <c r="F147" t="s">
         <v>240</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
       </c>
       <c r="H147" t="s">
         <v>44</v>
@@ -11811,8 +12687,14 @@
       <c r="D148" t="s">
         <v>235</v>
       </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
       <c r="F148" t="s">
         <v>242</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
       </c>
       <c r="H148" t="s">
         <v>44</v>
@@ -11870,8 +12752,14 @@
       <c r="D149" t="s">
         <v>235</v>
       </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
       <c r="F149" t="s">
         <v>236</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
       </c>
       <c r="H149" t="s">
         <v>114</v>
@@ -11929,8 +12817,14 @@
       <c r="D150" t="s">
         <v>246</v>
       </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
       <c r="F150" t="s">
         <v>247</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
       </c>
       <c r="H150" t="s">
         <v>44</v>
@@ -11988,8 +12882,14 @@
       <c r="D151" t="s">
         <v>252</v>
       </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
       <c r="F151" t="s">
         <v>253</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
       </c>
       <c r="H151" t="s">
         <v>44</v>
@@ -12047,8 +12947,14 @@
       <c r="D152" t="s">
         <v>257</v>
       </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
       <c r="F152" t="s">
         <v>258</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
       </c>
       <c r="H152" t="s">
         <v>259</v>
@@ -12106,8 +13012,14 @@
       <c r="D153" t="s">
         <v>262</v>
       </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
       <c r="F153" t="s">
         <v>258</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
       </c>
       <c r="H153" t="s">
         <v>259</v>
@@ -12165,8 +13077,14 @@
       <c r="D154" t="s">
         <v>257</v>
       </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
       <c r="F154" t="s">
         <v>258</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
       </c>
       <c r="H154" t="s">
         <v>263</v>
@@ -12224,8 +13142,14 @@
       <c r="D155" t="s">
         <v>262</v>
       </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
       <c r="F155" t="s">
         <v>258</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
       </c>
       <c r="H155" t="s">
         <v>263</v>
@@ -12283,8 +13207,14 @@
       <c r="D156" t="s">
         <v>257</v>
       </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
       <c r="F156" t="s">
         <v>258</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
       </c>
       <c r="H156" t="s">
         <v>265</v>
@@ -12342,8 +13272,14 @@
       <c r="D157" t="s">
         <v>262</v>
       </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
       <c r="F157" t="s">
         <v>258</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
       </c>
       <c r="H157" t="s">
         <v>265</v>
@@ -12401,8 +13337,14 @@
       <c r="D158" t="s">
         <v>257</v>
       </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
       <c r="F158" t="s">
         <v>258</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
       </c>
       <c r="H158" t="s">
         <v>267</v>
@@ -12460,8 +13402,14 @@
       <c r="D159" t="s">
         <v>262</v>
       </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
       <c r="F159" t="s">
         <v>258</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
       </c>
       <c r="H159" t="s">
         <v>267</v>
@@ -12519,8 +13467,14 @@
       <c r="D160" t="s">
         <v>257</v>
       </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
       <c r="F160" t="s">
         <v>258</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
       </c>
       <c r="H160" t="s">
         <v>269</v>
@@ -12578,8 +13532,14 @@
       <c r="D161" t="s">
         <v>262</v>
       </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
       <c r="F161" t="s">
         <v>258</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
       </c>
       <c r="H161" t="s">
         <v>269</v>
@@ -12637,8 +13597,14 @@
       <c r="D162" t="s">
         <v>257</v>
       </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
       <c r="F162" t="s">
         <v>258</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
       </c>
       <c r="H162" t="s">
         <v>271</v>
@@ -12696,8 +13662,14 @@
       <c r="D163" t="s">
         <v>262</v>
       </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
       <c r="F163" t="s">
         <v>258</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
       </c>
       <c r="H163" t="s">
         <v>271</v>
@@ -12755,8 +13727,14 @@
       <c r="D164" t="s">
         <v>257</v>
       </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
       <c r="F164" t="s">
         <v>258</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
       </c>
       <c r="H164" t="s">
         <v>265</v>
@@ -12814,8 +13792,14 @@
       <c r="D165" t="s">
         <v>262</v>
       </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
       <c r="F165" t="s">
         <v>258</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
       </c>
       <c r="H165" t="s">
         <v>265</v>
@@ -12873,8 +13857,14 @@
       <c r="D166" t="s">
         <v>257</v>
       </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
       <c r="F166" t="s">
         <v>258</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
       </c>
       <c r="H166" t="s">
         <v>121</v>
@@ -12932,8 +13922,14 @@
       <c r="D167" t="s">
         <v>262</v>
       </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
       <c r="F167" t="s">
         <v>258</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
       </c>
       <c r="H167" t="s">
         <v>121</v>
@@ -12991,8 +13987,14 @@
       <c r="D168" t="s">
         <v>257</v>
       </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
       <c r="F168" t="s">
         <v>258</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
       </c>
       <c r="H168" t="s">
         <v>274</v>
@@ -13050,8 +14052,14 @@
       <c r="D169" t="s">
         <v>262</v>
       </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
       <c r="F169" t="s">
         <v>258</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
       </c>
       <c r="H169" t="s">
         <v>274</v>
@@ -13109,8 +14117,14 @@
       <c r="D170" t="s">
         <v>257</v>
       </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
       <c r="F170" t="s">
         <v>258</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
       </c>
       <c r="H170" t="s">
         <v>98</v>
@@ -13168,8 +14182,14 @@
       <c r="D171" t="s">
         <v>262</v>
       </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
       <c r="F171" t="s">
         <v>258</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
       </c>
       <c r="H171" t="s">
         <v>98</v>
@@ -13227,8 +14247,14 @@
       <c r="D172" t="s">
         <v>257</v>
       </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
       <c r="F172" t="s">
         <v>258</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
       </c>
       <c r="H172" t="s">
         <v>277</v>
@@ -13286,8 +14312,14 @@
       <c r="D173" t="s">
         <v>262</v>
       </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
       <c r="F173" t="s">
         <v>258</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
       </c>
       <c r="H173" t="s">
         <v>277</v>
@@ -13345,8 +14377,14 @@
       <c r="D174" t="s">
         <v>257</v>
       </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
       <c r="F174" t="s">
         <v>258</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
       </c>
       <c r="H174" t="s">
         <v>106</v>
@@ -13404,8 +14442,14 @@
       <c r="D175" t="s">
         <v>262</v>
       </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
       <c r="F175" t="s">
         <v>258</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
       </c>
       <c r="H175" t="s">
         <v>106</v>
@@ -13463,8 +14507,14 @@
       <c r="D176" t="s">
         <v>257</v>
       </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
       <c r="F176" t="s">
         <v>258</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
       </c>
       <c r="H176" t="s">
         <v>265</v>
@@ -13522,8 +14572,14 @@
       <c r="D177" t="s">
         <v>257</v>
       </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
       <c r="F177" t="s">
         <v>258</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
       </c>
       <c r="H177" t="s">
         <v>271</v>
@@ -13581,8 +14637,14 @@
       <c r="D178" t="s">
         <v>257</v>
       </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
       <c r="F178" t="s">
         <v>258</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
       </c>
       <c r="H178" t="s">
         <v>281</v>
@@ -13640,8 +14702,14 @@
       <c r="D179" t="s">
         <v>257</v>
       </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
       <c r="F179" t="s">
         <v>258</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
       </c>
       <c r="H179" t="s">
         <v>44</v>
@@ -13699,8 +14767,14 @@
       <c r="D180" t="s">
         <v>257</v>
       </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
       <c r="F180" t="s">
         <v>258</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
       </c>
       <c r="H180" t="s">
         <v>269</v>
@@ -13758,8 +14832,14 @@
       <c r="D181" t="s">
         <v>257</v>
       </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
       <c r="F181" t="s">
         <v>258</v>
+      </c>
+      <c r="G181">
+        <v>1</v>
       </c>
       <c r="H181" t="s">
         <v>285</v>
@@ -13817,8 +14897,14 @@
       <c r="D182" t="s">
         <v>257</v>
       </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
       <c r="F182" t="s">
         <v>258</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
       </c>
       <c r="H182" t="s">
         <v>219</v>
@@ -13876,8 +14962,14 @@
       <c r="D183" t="s">
         <v>262</v>
       </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
       <c r="F183" t="s">
         <v>258</v>
+      </c>
+      <c r="G183">
+        <v>1</v>
       </c>
       <c r="H183" t="s">
         <v>219</v>
@@ -13935,8 +15027,14 @@
       <c r="D184" t="s">
         <v>257</v>
       </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
       <c r="F184" t="s">
         <v>258</v>
+      </c>
+      <c r="G184">
+        <v>1</v>
       </c>
       <c r="H184" t="s">
         <v>121</v>
@@ -13994,8 +15092,14 @@
       <c r="D185" t="s">
         <v>257</v>
       </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
       <c r="F185" t="s">
         <v>258</v>
+      </c>
+      <c r="G185">
+        <v>1</v>
       </c>
       <c r="H185" t="s">
         <v>288</v>
@@ -14053,8 +15157,14 @@
       <c r="D186" t="s">
         <v>257</v>
       </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
       <c r="F186" t="s">
         <v>258</v>
+      </c>
+      <c r="G186">
+        <v>1</v>
       </c>
       <c r="H186" t="s">
         <v>290</v>
@@ -14112,8 +15222,14 @@
       <c r="D187" t="s">
         <v>257</v>
       </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
       <c r="F187" t="s">
         <v>258</v>
+      </c>
+      <c r="G187">
+        <v>1</v>
       </c>
       <c r="H187" t="s">
         <v>161</v>
@@ -14171,8 +15287,14 @@
       <c r="D188" t="s">
         <v>293</v>
       </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
       <c r="F188" t="s">
         <v>258</v>
+      </c>
+      <c r="G188">
+        <v>1</v>
       </c>
       <c r="H188" t="s">
         <v>294</v>
@@ -14230,8 +15352,14 @@
       <c r="D189" t="s">
         <v>257</v>
       </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
       <c r="F189" t="s">
         <v>258</v>
+      </c>
+      <c r="G189">
+        <v>1</v>
       </c>
       <c r="H189" t="s">
         <v>209</v>
@@ -14289,8 +15417,14 @@
       <c r="D190" t="s">
         <v>257</v>
       </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
       <c r="F190" t="s">
         <v>258</v>
+      </c>
+      <c r="G190">
+        <v>1</v>
       </c>
       <c r="H190" t="s">
         <v>219</v>
@@ -14348,8 +15482,14 @@
       <c r="D191" t="s">
         <v>262</v>
       </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
       <c r="F191" t="s">
         <v>258</v>
+      </c>
+      <c r="G191">
+        <v>1</v>
       </c>
       <c r="H191" t="s">
         <v>209</v>
@@ -14407,8 +15547,14 @@
       <c r="D192" t="s">
         <v>293</v>
       </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
       <c r="F192" t="s">
         <v>258</v>
+      </c>
+      <c r="G192">
+        <v>1</v>
       </c>
       <c r="H192" t="s">
         <v>44</v>
@@ -14466,8 +15612,14 @@
       <c r="D193" t="s">
         <v>298</v>
       </c>
+      <c r="E193">
+        <v>0</v>
+      </c>
       <c r="F193" t="s">
         <v>253</v>
+      </c>
+      <c r="G193">
+        <v>1</v>
       </c>
       <c r="H193" t="s">
         <v>44</v>
@@ -14525,8 +15677,14 @@
       <c r="D194" t="s">
         <v>257</v>
       </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
       <c r="F194" t="s">
         <v>258</v>
+      </c>
+      <c r="G194">
+        <v>1</v>
       </c>
       <c r="H194" t="s">
         <v>44</v>
@@ -14584,8 +15742,14 @@
       <c r="D195" t="s">
         <v>262</v>
       </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
       <c r="F195" t="s">
         <v>258</v>
+      </c>
+      <c r="G195">
+        <v>1</v>
       </c>
       <c r="H195" t="s">
         <v>44</v>
@@ -14643,8 +15807,14 @@
       <c r="D196" t="s">
         <v>300</v>
       </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
       <c r="F196" t="s">
         <v>253</v>
+      </c>
+      <c r="G196">
+        <v>1</v>
       </c>
       <c r="H196" t="s">
         <v>44</v>
@@ -14702,8 +15872,14 @@
       <c r="D197" t="s">
         <v>302</v>
       </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
       <c r="F197" t="s">
         <v>253</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
       </c>
       <c r="H197" t="s">
         <v>44</v>
@@ -14761,8 +15937,14 @@
       <c r="D198" t="s">
         <v>293</v>
       </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
       <c r="F198" t="s">
         <v>258</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
       </c>
       <c r="H198" t="s">
         <v>303</v>
@@ -14820,8 +16002,14 @@
       <c r="D199" t="s">
         <v>298</v>
       </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
       <c r="F199" t="s">
         <v>253</v>
+      </c>
+      <c r="G199">
+        <v>1</v>
       </c>
       <c r="H199" t="s">
         <v>303</v>
@@ -14879,8 +16067,14 @@
       <c r="D200" t="s">
         <v>300</v>
       </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
       <c r="F200" t="s">
         <v>253</v>
+      </c>
+      <c r="G200">
+        <v>1</v>
       </c>
       <c r="H200" t="s">
         <v>303</v>
@@ -14938,8 +16132,14 @@
       <c r="D201" t="s">
         <v>293</v>
       </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
       <c r="F201" t="s">
         <v>258</v>
+      </c>
+      <c r="G201">
+        <v>1</v>
       </c>
       <c r="H201" t="s">
         <v>271</v>
@@ -14997,8 +16197,14 @@
       <c r="D202" t="s">
         <v>293</v>
       </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
       <c r="F202" t="s">
         <v>258</v>
+      </c>
+      <c r="G202">
+        <v>1</v>
       </c>
       <c r="H202" t="s">
         <v>306</v>
@@ -15056,8 +16262,14 @@
       <c r="D203" t="s">
         <v>293</v>
       </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
       <c r="F203" t="s">
         <v>258</v>
+      </c>
+      <c r="G203">
+        <v>1</v>
       </c>
       <c r="H203" t="s">
         <v>161</v>
@@ -15115,8 +16327,14 @@
       <c r="D204" t="s">
         <v>293</v>
       </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
       <c r="F204" t="s">
         <v>258</v>
+      </c>
+      <c r="G204">
+        <v>1</v>
       </c>
       <c r="H204" t="s">
         <v>207</v>
@@ -15174,8 +16392,14 @@
       <c r="D205" t="s">
         <v>293</v>
       </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
       <c r="F205" t="s">
         <v>258</v>
+      </c>
+      <c r="G205">
+        <v>1</v>
       </c>
       <c r="H205" t="s">
         <v>207</v>
@@ -15233,8 +16457,14 @@
       <c r="D206" t="s">
         <v>293</v>
       </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
       <c r="F206" t="s">
         <v>258</v>
+      </c>
+      <c r="G206">
+        <v>1</v>
       </c>
       <c r="H206" t="s">
         <v>309</v>
@@ -15292,8 +16522,14 @@
       <c r="D207" t="s">
         <v>293</v>
       </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
       <c r="F207" t="s">
         <v>258</v>
+      </c>
+      <c r="G207">
+        <v>1</v>
       </c>
       <c r="H207" t="s">
         <v>213</v>
@@ -15351,8 +16587,14 @@
       <c r="D208" t="s">
         <v>293</v>
       </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
       <c r="F208" t="s">
         <v>258</v>
+      </c>
+      <c r="G208">
+        <v>1</v>
       </c>
       <c r="H208" t="s">
         <v>213</v>
@@ -15410,8 +16652,14 @@
       <c r="D209" t="s">
         <v>293</v>
       </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
       <c r="F209" t="s">
         <v>258</v>
+      </c>
+      <c r="G209">
+        <v>1</v>
       </c>
       <c r="H209" t="s">
         <v>65</v>
@@ -15469,8 +16717,14 @@
       <c r="D210" t="s">
         <v>293</v>
       </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
       <c r="F210" t="s">
         <v>258</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
       </c>
       <c r="H210" t="s">
         <v>121</v>
@@ -15528,8 +16782,14 @@
       <c r="D211" t="s">
         <v>293</v>
       </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
       <c r="F211" t="s">
         <v>258</v>
+      </c>
+      <c r="G211">
+        <v>1</v>
       </c>
       <c r="H211" t="s">
         <v>121</v>
@@ -15587,8 +16847,14 @@
       <c r="D212" t="s">
         <v>315</v>
       </c>
+      <c r="E212">
+        <v>1</v>
+      </c>
       <c r="F212" t="s">
         <v>316</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
       </c>
       <c r="H212" t="s">
         <v>317</v>
@@ -15646,8 +16912,14 @@
       <c r="D213" t="s">
         <v>315</v>
       </c>
+      <c r="E213">
+        <v>1</v>
+      </c>
       <c r="F213" t="s">
         <v>316</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
       </c>
       <c r="H213" t="s">
         <v>320</v>
@@ -15705,8 +16977,14 @@
       <c r="D214" t="s">
         <v>315</v>
       </c>
+      <c r="E214">
+        <v>1</v>
+      </c>
       <c r="F214" t="s">
         <v>324</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
       </c>
       <c r="H214" t="s">
         <v>325</v>
@@ -15764,8 +17042,14 @@
       <c r="D215" t="s">
         <v>315</v>
       </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
       <c r="F215" t="s">
         <v>324</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
       </c>
       <c r="H215" t="s">
         <v>206</v>
@@ -15823,8 +17107,14 @@
       <c r="D216" t="s">
         <v>329</v>
       </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
       <c r="F216" t="s">
         <v>324</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
       </c>
       <c r="H216" t="s">
         <v>206</v>
@@ -15882,8 +17172,14 @@
       <c r="D217" t="s">
         <v>315</v>
       </c>
+      <c r="E217">
+        <v>1</v>
+      </c>
       <c r="F217" t="s">
         <v>324</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
       </c>
       <c r="H217" t="s">
         <v>152</v>
@@ -15941,8 +17237,14 @@
       <c r="D218" t="s">
         <v>315</v>
       </c>
+      <c r="E218">
+        <v>1</v>
+      </c>
       <c r="F218" t="s">
         <v>324</v>
+      </c>
+      <c r="G218">
+        <v>0</v>
       </c>
       <c r="H218" t="s">
         <v>271</v>
@@ -16000,8 +17302,14 @@
       <c r="D219" t="s">
         <v>329</v>
       </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
       <c r="F219" t="s">
         <v>324</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
       </c>
       <c r="H219" t="s">
         <v>271</v>
@@ -16059,8 +17367,14 @@
       <c r="D220" t="s">
         <v>315</v>
       </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
       <c r="F220" t="s">
         <v>324</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
       </c>
       <c r="H220" t="s">
         <v>271</v>
@@ -16118,8 +17432,14 @@
       <c r="D221" t="s">
         <v>329</v>
       </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
       <c r="F221" t="s">
         <v>324</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
       </c>
       <c r="H221" t="s">
         <v>271</v>
@@ -16177,8 +17497,14 @@
       <c r="D222" t="s">
         <v>315</v>
       </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
       <c r="F222" t="s">
         <v>324</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
       </c>
       <c r="H222" t="s">
         <v>206</v>
@@ -16236,8 +17562,14 @@
       <c r="D223" t="s">
         <v>329</v>
       </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
       <c r="F223" t="s">
         <v>324</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
       </c>
       <c r="H223" t="s">
         <v>206</v>
@@ -16295,8 +17627,14 @@
       <c r="D224" t="s">
         <v>315</v>
       </c>
+      <c r="E224">
+        <v>1</v>
+      </c>
       <c r="F224" t="s">
         <v>324</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
       </c>
       <c r="H224" t="s">
         <v>271</v>
@@ -16354,8 +17692,14 @@
       <c r="D225" t="s">
         <v>329</v>
       </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
       <c r="F225" t="s">
         <v>324</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
       </c>
       <c r="H225" t="s">
         <v>271</v>
@@ -16413,8 +17757,14 @@
       <c r="D226" t="s">
         <v>315</v>
       </c>
+      <c r="E226">
+        <v>1</v>
+      </c>
       <c r="F226" t="s">
         <v>324</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
       </c>
       <c r="H226" t="s">
         <v>320</v>
@@ -16472,8 +17822,14 @@
       <c r="D227" t="s">
         <v>329</v>
       </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
       <c r="F227" t="s">
         <v>324</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
       </c>
       <c r="H227" t="s">
         <v>320</v>
@@ -16531,8 +17887,14 @@
       <c r="D228" t="s">
         <v>315</v>
       </c>
+      <c r="E228">
+        <v>1</v>
+      </c>
       <c r="F228" t="s">
         <v>324</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
       </c>
       <c r="H228" t="s">
         <v>271</v>
@@ -16590,8 +17952,14 @@
       <c r="D229" t="s">
         <v>329</v>
       </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
       <c r="F229" t="s">
         <v>324</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
       </c>
       <c r="H229" t="s">
         <v>271</v>
@@ -16649,8 +18017,14 @@
       <c r="D230" t="s">
         <v>338</v>
       </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
       <c r="F230" t="s">
         <v>339</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
       </c>
       <c r="H230" t="s">
         <v>340</v>
@@ -16708,8 +18082,14 @@
       <c r="D231" t="s">
         <v>344</v>
       </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
       <c r="F231" t="s">
         <v>339</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
       </c>
       <c r="H231" t="s">
         <v>345</v>
@@ -16767,8 +18147,14 @@
       <c r="D232" t="s">
         <v>338</v>
       </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
       <c r="F232" t="s">
         <v>339</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
       </c>
       <c r="H232" t="s">
         <v>345</v>
@@ -16826,8 +18212,14 @@
       <c r="D233" t="s">
         <v>348</v>
       </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
       <c r="F233" t="s">
         <v>339</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
       </c>
       <c r="H233" t="s">
         <v>345</v>
@@ -16885,8 +18277,14 @@
       <c r="D234" t="s">
         <v>350</v>
       </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
       <c r="F234" t="s">
         <v>339</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
       </c>
       <c r="H234" t="s">
         <v>351</v>
@@ -16944,8 +18342,14 @@
       <c r="D235" t="s">
         <v>350</v>
       </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
       <c r="F235" t="s">
         <v>353</v>
+      </c>
+      <c r="G235">
+        <v>0</v>
       </c>
       <c r="H235" t="s">
         <v>351</v>
@@ -17003,8 +18407,14 @@
       <c r="D236" t="s">
         <v>348</v>
       </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
       <c r="F236" t="s">
         <v>355</v>
+      </c>
+      <c r="G236">
+        <v>0</v>
       </c>
       <c r="H236" t="s">
         <v>351</v>
@@ -17062,8 +18472,14 @@
       <c r="D237" t="s">
         <v>348</v>
       </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
       <c r="F237" t="s">
         <v>339</v>
+      </c>
+      <c r="G237">
+        <v>0</v>
       </c>
       <c r="H237" t="s">
         <v>351</v>
@@ -17121,8 +18537,14 @@
       <c r="D238" t="s">
         <v>348</v>
       </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
       <c r="F238" t="s">
         <v>357</v>
+      </c>
+      <c r="G238">
+        <v>0</v>
       </c>
       <c r="H238" t="s">
         <v>351</v>
@@ -17180,8 +18602,14 @@
       <c r="D239" t="s">
         <v>348</v>
       </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
       <c r="F239" t="s">
         <v>353</v>
+      </c>
+      <c r="G239">
+        <v>0</v>
       </c>
       <c r="H239" t="s">
         <v>351</v>
@@ -17239,8 +18667,14 @@
       <c r="D240" t="s">
         <v>360</v>
       </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
       <c r="F240" t="s">
         <v>361</v>
+      </c>
+      <c r="G240">
+        <v>0</v>
       </c>
       <c r="H240" t="s">
         <v>362</v>
@@ -17298,8 +18732,14 @@
       <c r="D241" t="s">
         <v>360</v>
       </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
       <c r="F241" t="s">
         <v>361</v>
+      </c>
+      <c r="G241">
+        <v>0</v>
       </c>
       <c r="H241" t="s">
         <v>362</v>
@@ -17357,8 +18797,14 @@
       <c r="D242" t="s">
         <v>344</v>
       </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
       <c r="F242" t="s">
         <v>339</v>
+      </c>
+      <c r="G242">
+        <v>0</v>
       </c>
       <c r="H242" t="s">
         <v>362</v>
@@ -17416,8 +18862,14 @@
       <c r="D243" t="s">
         <v>344</v>
       </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
       <c r="F243" t="s">
         <v>339</v>
+      </c>
+      <c r="G243">
+        <v>0</v>
       </c>
       <c r="H243" t="s">
         <v>362</v>
@@ -17475,8 +18927,14 @@
       <c r="D244" t="s">
         <v>365</v>
       </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
       <c r="F244" t="s">
         <v>339</v>
+      </c>
+      <c r="G244">
+        <v>0</v>
       </c>
       <c r="H244" t="s">
         <v>362</v>
@@ -17534,8 +18992,14 @@
       <c r="D245" t="s">
         <v>365</v>
       </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
       <c r="F245" t="s">
         <v>339</v>
+      </c>
+      <c r="G245">
+        <v>0</v>
       </c>
       <c r="H245" t="s">
         <v>362</v>
@@ -17593,8 +19057,14 @@
       <c r="D246" t="s">
         <v>344</v>
       </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
       <c r="F246" t="s">
         <v>367</v>
+      </c>
+      <c r="G246">
+        <v>0</v>
       </c>
       <c r="H246" t="s">
         <v>362</v>
@@ -17652,8 +19122,14 @@
       <c r="D247" t="s">
         <v>344</v>
       </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
       <c r="F247" t="s">
         <v>367</v>
+      </c>
+      <c r="G247">
+        <v>0</v>
       </c>
       <c r="H247" t="s">
         <v>362</v>
@@ -17711,8 +19187,14 @@
       <c r="D248" t="s">
         <v>369</v>
       </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
       <c r="F248" t="s">
         <v>367</v>
+      </c>
+      <c r="G248">
+        <v>0</v>
       </c>
       <c r="H248" t="s">
         <v>362</v>
@@ -17770,8 +19252,14 @@
       <c r="D249" t="s">
         <v>369</v>
       </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
       <c r="F249" t="s">
         <v>367</v>
+      </c>
+      <c r="G249">
+        <v>0</v>
       </c>
       <c r="H249" t="s">
         <v>362</v>
@@ -17829,8 +19317,14 @@
       <c r="D250" t="s">
         <v>365</v>
       </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
       <c r="F250" t="s">
         <v>367</v>
+      </c>
+      <c r="G250">
+        <v>0</v>
       </c>
       <c r="H250" t="s">
         <v>362</v>
@@ -17888,8 +19382,14 @@
       <c r="D251" t="s">
         <v>365</v>
       </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
       <c r="F251" t="s">
         <v>367</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
       </c>
       <c r="H251" t="s">
         <v>362</v>
@@ -17947,8 +19447,14 @@
       <c r="D252" t="s">
         <v>344</v>
       </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
       <c r="F252" t="s">
         <v>339</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
       </c>
       <c r="H252" t="s">
         <v>371</v>
@@ -18006,8 +19512,14 @@
       <c r="D253" t="s">
         <v>365</v>
       </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
       <c r="F253" t="s">
         <v>339</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
       </c>
       <c r="H253" t="s">
         <v>371</v>
@@ -18065,8 +19577,14 @@
       <c r="D254" t="s">
         <v>360</v>
       </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
       <c r="F254" t="s">
         <v>361</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
       </c>
       <c r="H254" t="s">
         <v>373</v>
@@ -18124,8 +19642,14 @@
       <c r="D255" t="s">
         <v>344</v>
       </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
       <c r="F255" t="s">
         <v>339</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
       </c>
       <c r="H255" t="s">
         <v>373</v>
@@ -18183,8 +19707,14 @@
       <c r="D256" t="s">
         <v>365</v>
       </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
       <c r="F256" t="s">
         <v>339</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
       </c>
       <c r="H256" t="s">
         <v>373</v>
@@ -18242,8 +19772,14 @@
       <c r="D257" t="s">
         <v>344</v>
       </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
       <c r="F257" t="s">
         <v>339</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
       </c>
       <c r="H257" t="s">
         <v>340</v>
@@ -18301,8 +19837,14 @@
       <c r="D258" t="s">
         <v>365</v>
       </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
       <c r="F258" t="s">
         <v>339</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
       </c>
       <c r="H258" t="s">
         <v>340</v>
@@ -18360,8 +19902,14 @@
       <c r="D259" t="s">
         <v>360</v>
       </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
       <c r="F259" t="s">
         <v>361</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
       </c>
       <c r="H259" t="s">
         <v>376</v>
@@ -18419,8 +19967,14 @@
       <c r="D260" t="s">
         <v>344</v>
       </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
       <c r="F260" t="s">
         <v>339</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
       </c>
       <c r="H260" t="s">
         <v>376</v>
@@ -18478,8 +20032,14 @@
       <c r="D261" t="s">
         <v>365</v>
       </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
       <c r="F261" t="s">
         <v>339</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
       </c>
       <c r="H261" t="s">
         <v>376</v>
@@ -18537,8 +20097,14 @@
       <c r="D262" t="s">
         <v>360</v>
       </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
       <c r="F262" t="s">
         <v>361</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
       </c>
       <c r="H262" t="s">
         <v>362</v>
@@ -18596,8 +20162,14 @@
       <c r="D263" t="s">
         <v>360</v>
       </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
       <c r="F263" t="s">
         <v>361</v>
+      </c>
+      <c r="G263">
+        <v>0</v>
       </c>
       <c r="H263" t="s">
         <v>362</v>
@@ -18655,8 +20227,14 @@
       <c r="D264" t="s">
         <v>344</v>
       </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
       <c r="F264" t="s">
         <v>339</v>
+      </c>
+      <c r="G264">
+        <v>0</v>
       </c>
       <c r="H264" t="s">
         <v>362</v>
@@ -18714,8 +20292,14 @@
       <c r="D265" t="s">
         <v>344</v>
       </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
       <c r="F265" t="s">
         <v>339</v>
+      </c>
+      <c r="G265">
+        <v>0</v>
       </c>
       <c r="H265" t="s">
         <v>362</v>
@@ -18773,8 +20357,14 @@
       <c r="D266" t="s">
         <v>365</v>
       </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
       <c r="F266" t="s">
         <v>339</v>
+      </c>
+      <c r="G266">
+        <v>0</v>
       </c>
       <c r="H266" t="s">
         <v>362</v>
@@ -18832,8 +20422,14 @@
       <c r="D267" t="s">
         <v>365</v>
       </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
       <c r="F267" t="s">
         <v>339</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
       </c>
       <c r="H267" t="s">
         <v>362</v>
@@ -18891,8 +20487,14 @@
       <c r="D268" t="s">
         <v>360</v>
       </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
       <c r="F268" t="s">
         <v>361</v>
+      </c>
+      <c r="G268">
+        <v>0</v>
       </c>
       <c r="H268" t="s">
         <v>98</v>
@@ -18950,8 +20552,14 @@
       <c r="D269" t="s">
         <v>344</v>
       </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
       <c r="F269" t="s">
         <v>339</v>
+      </c>
+      <c r="G269">
+        <v>0</v>
       </c>
       <c r="H269" t="s">
         <v>98</v>
@@ -19009,8 +20617,14 @@
       <c r="D270" t="s">
         <v>365</v>
       </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
       <c r="F270" t="s">
         <v>339</v>
+      </c>
+      <c r="G270">
+        <v>0</v>
       </c>
       <c r="H270" t="s">
         <v>98</v>
@@ -19068,8 +20682,14 @@
       <c r="D271" t="s">
         <v>360</v>
       </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
       <c r="F271" t="s">
         <v>361</v>
+      </c>
+      <c r="G271">
+        <v>0</v>
       </c>
       <c r="H271" t="s">
         <v>362</v>
@@ -19127,8 +20747,14 @@
       <c r="D272" t="s">
         <v>360</v>
       </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
       <c r="F272" t="s">
         <v>361</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
       </c>
       <c r="H272" t="s">
         <v>362</v>
@@ -19186,8 +20812,14 @@
       <c r="D273" t="s">
         <v>344</v>
       </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
       <c r="F273" t="s">
         <v>339</v>
+      </c>
+      <c r="G273">
+        <v>0</v>
       </c>
       <c r="H273" t="s">
         <v>362</v>
@@ -19245,8 +20877,14 @@
       <c r="D274" t="s">
         <v>344</v>
       </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
       <c r="F274" t="s">
         <v>339</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
       </c>
       <c r="H274" t="s">
         <v>362</v>
@@ -19304,8 +20942,14 @@
       <c r="D275" t="s">
         <v>365</v>
       </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
       <c r="F275" t="s">
         <v>339</v>
+      </c>
+      <c r="G275">
+        <v>0</v>
       </c>
       <c r="H275" t="s">
         <v>362</v>
@@ -19363,8 +21007,14 @@
       <c r="D276" t="s">
         <v>365</v>
       </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
       <c r="F276" t="s">
         <v>339</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
       </c>
       <c r="H276" t="s">
         <v>362</v>
@@ -19422,8 +21072,14 @@
       <c r="D277" t="s">
         <v>360</v>
       </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
       <c r="F277" t="s">
         <v>361</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
       </c>
       <c r="H277" t="s">
         <v>351</v>
@@ -19481,8 +21137,14 @@
       <c r="D278" t="s">
         <v>344</v>
       </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
       <c r="F278" t="s">
         <v>339</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
       </c>
       <c r="H278" t="s">
         <v>351</v>
@@ -19540,8 +21202,14 @@
       <c r="D279" t="s">
         <v>365</v>
       </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
       <c r="F279" t="s">
         <v>339</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
       </c>
       <c r="H279" t="s">
         <v>351</v>
@@ -19599,8 +21267,14 @@
       <c r="D280" t="s">
         <v>360</v>
       </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
       <c r="F280" t="s">
         <v>361</v>
+      </c>
+      <c r="G280">
+        <v>0</v>
       </c>
       <c r="H280" t="s">
         <v>382</v>
@@ -19658,8 +21332,14 @@
       <c r="D281" t="s">
         <v>360</v>
       </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
       <c r="F281" t="s">
         <v>361</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
       </c>
       <c r="H281" t="s">
         <v>382</v>
@@ -19717,8 +21397,14 @@
       <c r="D282" t="s">
         <v>344</v>
       </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
       <c r="F282" t="s">
         <v>339</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
       </c>
       <c r="H282" t="s">
         <v>382</v>
@@ -19776,8 +21462,14 @@
       <c r="D283" t="s">
         <v>344</v>
       </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
       <c r="F283" t="s">
         <v>339</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
       </c>
       <c r="H283" t="s">
         <v>382</v>
@@ -19835,8 +21527,14 @@
       <c r="D284" t="s">
         <v>365</v>
       </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
       <c r="F284" t="s">
         <v>339</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
       </c>
       <c r="H284" t="s">
         <v>382</v>
@@ -19894,8 +21592,14 @@
       <c r="D285" t="s">
         <v>365</v>
       </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
       <c r="F285" t="s">
         <v>339</v>
+      </c>
+      <c r="G285">
+        <v>0</v>
       </c>
       <c r="H285" t="s">
         <v>382</v>
@@ -19953,8 +21657,14 @@
       <c r="D286" t="s">
         <v>360</v>
       </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
       <c r="F286" t="s">
         <v>361</v>
+      </c>
+      <c r="G286">
+        <v>0</v>
       </c>
       <c r="H286" t="s">
         <v>384</v>
@@ -20012,8 +21722,14 @@
       <c r="D287" t="s">
         <v>360</v>
       </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
       <c r="F287" t="s">
         <v>361</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
       </c>
       <c r="H287" t="s">
         <v>376</v>
@@ -20071,8 +21787,14 @@
       <c r="D288" t="s">
         <v>344</v>
       </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
       <c r="F288" t="s">
         <v>339</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
       </c>
       <c r="H288" t="s">
         <v>376</v>
@@ -20130,8 +21852,14 @@
       <c r="D289" t="s">
         <v>365</v>
       </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
       <c r="F289" t="s">
         <v>339</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
       </c>
       <c r="H289" t="s">
         <v>376</v>
@@ -20189,8 +21917,14 @@
       <c r="D290" t="s">
         <v>360</v>
       </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
       <c r="F290" t="s">
         <v>361</v>
+      </c>
+      <c r="G290">
+        <v>0</v>
       </c>
       <c r="H290" t="s">
         <v>259</v>
@@ -20248,8 +21982,14 @@
       <c r="D291" t="s">
         <v>344</v>
       </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
       <c r="F291" t="s">
         <v>339</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
       </c>
       <c r="H291" t="s">
         <v>259</v>
@@ -20307,8 +22047,14 @@
       <c r="D292" t="s">
         <v>365</v>
       </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
       <c r="F292" t="s">
         <v>339</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
       </c>
       <c r="H292" t="s">
         <v>259</v>
@@ -20366,8 +22112,14 @@
       <c r="D293" t="s">
         <v>360</v>
       </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
       <c r="F293" t="s">
         <v>361</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
       </c>
       <c r="H293" t="s">
         <v>38</v>
@@ -20425,8 +22177,14 @@
       <c r="D294" t="s">
         <v>344</v>
       </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
       <c r="F294" t="s">
         <v>339</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
       </c>
       <c r="H294" t="s">
         <v>38</v>
@@ -20484,8 +22242,14 @@
       <c r="D295" t="s">
         <v>360</v>
       </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
       <c r="F295" t="s">
         <v>361</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
       </c>
       <c r="H295" t="s">
         <v>121</v>
@@ -20543,8 +22307,14 @@
       <c r="D296" t="s">
         <v>344</v>
       </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
       <c r="F296" t="s">
         <v>339</v>
+      </c>
+      <c r="G296">
+        <v>0</v>
       </c>
       <c r="H296" t="s">
         <v>121</v>
@@ -20602,8 +22372,14 @@
       <c r="D297" t="s">
         <v>365</v>
       </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
       <c r="F297" t="s">
         <v>339</v>
+      </c>
+      <c r="G297">
+        <v>0</v>
       </c>
       <c r="H297" t="s">
         <v>121</v>
@@ -20661,8 +22437,14 @@
       <c r="D298" t="s">
         <v>360</v>
       </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
       <c r="F298" t="s">
         <v>361</v>
+      </c>
+      <c r="G298">
+        <v>0</v>
       </c>
       <c r="H298" t="s">
         <v>362</v>
@@ -20720,8 +22502,14 @@
       <c r="D299" t="s">
         <v>344</v>
       </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
       <c r="F299" t="s">
         <v>339</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
       </c>
       <c r="H299" t="s">
         <v>362</v>
@@ -20779,8 +22567,14 @@
       <c r="D300" t="s">
         <v>360</v>
       </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
       <c r="F300" t="s">
         <v>361</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
       </c>
       <c r="H300" t="s">
         <v>376</v>
@@ -20838,8 +22632,14 @@
       <c r="D301" t="s">
         <v>344</v>
       </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
       <c r="F301" t="s">
         <v>339</v>
+      </c>
+      <c r="G301">
+        <v>0</v>
       </c>
       <c r="H301" t="s">
         <v>376</v>
@@ -20897,8 +22697,14 @@
       <c r="D302" t="s">
         <v>360</v>
       </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
       <c r="F302" t="s">
         <v>361</v>
+      </c>
+      <c r="G302">
+        <v>0</v>
       </c>
       <c r="H302" t="s">
         <v>391</v>
@@ -20956,8 +22762,14 @@
       <c r="D303" t="s">
         <v>344</v>
       </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
       <c r="F303" t="s">
         <v>339</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
       </c>
       <c r="H303" t="s">
         <v>391</v>
@@ -21015,8 +22827,14 @@
       <c r="D304" t="s">
         <v>360</v>
       </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
       <c r="F304" t="s">
         <v>361</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
       </c>
       <c r="H304" t="s">
         <v>340</v>
@@ -21074,8 +22892,14 @@
       <c r="D305" t="s">
         <v>344</v>
       </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
       <c r="F305" t="s">
         <v>339</v>
+      </c>
+      <c r="G305">
+        <v>0</v>
       </c>
       <c r="H305" t="s">
         <v>340</v>
@@ -21133,8 +22957,14 @@
       <c r="D306" t="s">
         <v>360</v>
       </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
       <c r="F306" t="s">
         <v>361</v>
+      </c>
+      <c r="G306">
+        <v>0</v>
       </c>
       <c r="H306" t="s">
         <v>382</v>
@@ -21192,8 +23022,14 @@
       <c r="D307" t="s">
         <v>360</v>
       </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
       <c r="F307" t="s">
         <v>361</v>
+      </c>
+      <c r="G307">
+        <v>0</v>
       </c>
       <c r="H307" t="s">
         <v>382</v>
@@ -21251,8 +23087,14 @@
       <c r="D308" t="s">
         <v>360</v>
       </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
       <c r="F308" t="s">
         <v>361</v>
+      </c>
+      <c r="G308">
+        <v>0</v>
       </c>
       <c r="H308" t="s">
         <v>228</v>
@@ -21310,8 +23152,14 @@
       <c r="D309" t="s">
         <v>360</v>
       </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
       <c r="F309" t="s">
         <v>361</v>
+      </c>
+      <c r="G309">
+        <v>0</v>
       </c>
       <c r="H309" t="s">
         <v>161</v>
@@ -21369,8 +23217,14 @@
       <c r="D310" t="s">
         <v>360</v>
       </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
       <c r="F310" t="s">
         <v>361</v>
+      </c>
+      <c r="G310">
+        <v>0</v>
       </c>
       <c r="H310" t="s">
         <v>63</v>
@@ -21428,8 +23282,14 @@
       <c r="D311" t="s">
         <v>360</v>
       </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
       <c r="F311" t="s">
         <v>361</v>
+      </c>
+      <c r="G311">
+        <v>0</v>
       </c>
       <c r="H311" t="s">
         <v>394</v>
@@ -21487,8 +23347,14 @@
       <c r="D312" t="s">
         <v>360</v>
       </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
       <c r="F312" t="s">
         <v>361</v>
+      </c>
+      <c r="G312">
+        <v>0</v>
       </c>
       <c r="H312" t="s">
         <v>396</v>
@@ -21546,8 +23412,14 @@
       <c r="D313" t="s">
         <v>360</v>
       </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
       <c r="F313" t="s">
         <v>361</v>
+      </c>
+      <c r="G313">
+        <v>0</v>
       </c>
       <c r="H313" t="s">
         <v>396</v>
@@ -21605,8 +23477,14 @@
       <c r="D314" t="s">
         <v>360</v>
       </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
       <c r="F314" t="s">
         <v>361</v>
+      </c>
+      <c r="G314">
+        <v>0</v>
       </c>
       <c r="H314" t="s">
         <v>207</v>
@@ -21664,8 +23542,14 @@
       <c r="D315" t="s">
         <v>360</v>
       </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
       <c r="F315" t="s">
         <v>361</v>
+      </c>
+      <c r="G315">
+        <v>0</v>
       </c>
       <c r="H315" t="s">
         <v>207</v>
@@ -21723,8 +23607,14 @@
       <c r="D316" t="s">
         <v>360</v>
       </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
       <c r="F316" t="s">
         <v>361</v>
+      </c>
+      <c r="G316">
+        <v>0</v>
       </c>
       <c r="H316" t="s">
         <v>340</v>
@@ -21782,8 +23672,14 @@
       <c r="D317" t="s">
         <v>360</v>
       </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
       <c r="F317" t="s">
         <v>361</v>
+      </c>
+      <c r="G317">
+        <v>0</v>
       </c>
       <c r="H317" t="s">
         <v>340</v>
@@ -21841,8 +23737,14 @@
       <c r="D318" t="s">
         <v>360</v>
       </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
       <c r="F318" t="s">
         <v>361</v>
+      </c>
+      <c r="G318">
+        <v>0</v>
       </c>
       <c r="H318" t="s">
         <v>362</v>
@@ -21900,8 +23802,14 @@
       <c r="D319" t="s">
         <v>360</v>
       </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
       <c r="F319" t="s">
         <v>361</v>
+      </c>
+      <c r="G319">
+        <v>0</v>
       </c>
       <c r="H319" t="s">
         <v>309</v>
@@ -21959,8 +23867,14 @@
       <c r="D320" t="s">
         <v>360</v>
       </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
       <c r="F320" t="s">
         <v>361</v>
+      </c>
+      <c r="G320">
+        <v>0</v>
       </c>
       <c r="H320" t="s">
         <v>150</v>
@@ -22018,8 +23932,14 @@
       <c r="D321" t="s">
         <v>360</v>
       </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
       <c r="F321" t="s">
         <v>361</v>
+      </c>
+      <c r="G321">
+        <v>0</v>
       </c>
       <c r="H321" t="s">
         <v>98</v>
@@ -22077,8 +23997,14 @@
       <c r="D322" t="s">
         <v>360</v>
       </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
       <c r="F322" t="s">
         <v>361</v>
+      </c>
+      <c r="G322">
+        <v>0</v>
       </c>
       <c r="H322" t="s">
         <v>401</v>
@@ -22136,8 +24062,14 @@
       <c r="D323" t="s">
         <v>360</v>
       </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
       <c r="F323" t="s">
         <v>361</v>
+      </c>
+      <c r="G323">
+        <v>0</v>
       </c>
       <c r="H323" t="s">
         <v>166</v>
@@ -22195,8 +24127,14 @@
       <c r="D324" t="s">
         <v>406</v>
       </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
       <c r="F324" t="s">
         <v>407</v>
+      </c>
+      <c r="G324">
+        <v>0</v>
       </c>
       <c r="H324" t="s">
         <v>408</v>
@@ -22254,8 +24192,14 @@
       <c r="D325" t="s">
         <v>412</v>
       </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
       <c r="F325" t="s">
         <v>413</v>
+      </c>
+      <c r="G325">
+        <v>0</v>
       </c>
       <c r="H325" t="s">
         <v>408</v>
@@ -22313,8 +24257,14 @@
       <c r="D326" t="s">
         <v>406</v>
       </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
       <c r="F326" t="s">
         <v>407</v>
+      </c>
+      <c r="G326">
+        <v>0</v>
       </c>
       <c r="H326" t="s">
         <v>98</v>
@@ -22372,8 +24322,14 @@
       <c r="D327" t="s">
         <v>412</v>
       </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
       <c r="F327" t="s">
         <v>413</v>
+      </c>
+      <c r="G327">
+        <v>0</v>
       </c>
       <c r="H327" t="s">
         <v>98</v>
@@ -22431,8 +24387,14 @@
       <c r="D328" t="s">
         <v>406</v>
       </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
       <c r="F328" t="s">
         <v>407</v>
+      </c>
+      <c r="G328">
+        <v>0</v>
       </c>
       <c r="H328" t="s">
         <v>408</v>
@@ -22490,8 +24452,14 @@
       <c r="D329" t="s">
         <v>412</v>
       </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
       <c r="F329" t="s">
         <v>413</v>
+      </c>
+      <c r="G329">
+        <v>0</v>
       </c>
       <c r="H329" t="s">
         <v>408</v>
@@ -22549,8 +24517,14 @@
       <c r="D330" t="s">
         <v>406</v>
       </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
       <c r="F330" t="s">
         <v>407</v>
+      </c>
+      <c r="G330">
+        <v>0</v>
       </c>
       <c r="H330" t="s">
         <v>416</v>
@@ -22608,8 +24582,14 @@
       <c r="D331" t="s">
         <v>406</v>
       </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
       <c r="F331" t="s">
         <v>407</v>
+      </c>
+      <c r="G331">
+        <v>0</v>
       </c>
       <c r="H331" t="s">
         <v>418</v>
@@ -22667,8 +24647,14 @@
       <c r="D332" t="s">
         <v>406</v>
       </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
       <c r="F332" t="s">
         <v>407</v>
+      </c>
+      <c r="G332">
+        <v>0</v>
       </c>
       <c r="H332" t="s">
         <v>382</v>
@@ -22726,8 +24712,14 @@
       <c r="D333" t="s">
         <v>406</v>
       </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
       <c r="F333" t="s">
         <v>407</v>
+      </c>
+      <c r="G333">
+        <v>0</v>
       </c>
       <c r="H333" t="s">
         <v>382</v>
@@ -22785,8 +24777,14 @@
       <c r="D334" t="s">
         <v>406</v>
       </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
       <c r="F334" t="s">
         <v>407</v>
+      </c>
+      <c r="G334">
+        <v>0</v>
       </c>
       <c r="H334" t="s">
         <v>121</v>
@@ -22844,8 +24842,14 @@
       <c r="D335" t="s">
         <v>406</v>
       </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
       <c r="F335" t="s">
         <v>407</v>
+      </c>
+      <c r="G335">
+        <v>0</v>
       </c>
       <c r="H335" t="s">
         <v>421</v>
@@ -22903,8 +24907,14 @@
       <c r="D336" t="s">
         <v>406</v>
       </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
       <c r="F336" t="s">
         <v>407</v>
+      </c>
+      <c r="G336">
+        <v>0</v>
       </c>
       <c r="H336" t="s">
         <v>67</v>
@@ -22962,8 +24972,14 @@
       <c r="D337" t="s">
         <v>425</v>
       </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
       <c r="F337" t="s">
         <v>426</v>
+      </c>
+      <c r="G337">
+        <v>1</v>
       </c>
       <c r="H337" t="s">
         <v>408</v>
@@ -23021,8 +25037,14 @@
       <c r="D338" t="s">
         <v>425</v>
       </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
       <c r="F338" t="s">
         <v>426</v>
+      </c>
+      <c r="G338">
+        <v>1</v>
       </c>
       <c r="H338" t="s">
         <v>408</v>
@@ -23080,8 +25102,14 @@
       <c r="D339" t="s">
         <v>425</v>
       </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
       <c r="F339" t="s">
         <v>426</v>
+      </c>
+      <c r="G339">
+        <v>1</v>
       </c>
       <c r="H339" t="s">
         <v>408</v>
@@ -23139,8 +25167,14 @@
       <c r="D340" t="s">
         <v>425</v>
       </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
       <c r="F340" t="s">
         <v>426</v>
+      </c>
+      <c r="G340">
+        <v>1</v>
       </c>
       <c r="H340" t="s">
         <v>38</v>
@@ -23198,8 +25232,14 @@
       <c r="D341" t="s">
         <v>425</v>
       </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
       <c r="F341" t="s">
         <v>426</v>
+      </c>
+      <c r="G341">
+        <v>1</v>
       </c>
       <c r="H341" t="s">
         <v>38</v>
@@ -23257,8 +25297,14 @@
       <c r="D342" t="s">
         <v>433</v>
       </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
       <c r="F342" t="s">
         <v>434</v>
+      </c>
+      <c r="G342">
+        <v>1</v>
       </c>
       <c r="H342" t="s">
         <v>24</v>
@@ -23316,8 +25362,14 @@
       <c r="D343" t="s">
         <v>433</v>
       </c>
+      <c r="E343">
+        <v>0</v>
+      </c>
       <c r="F343" t="s">
         <v>434</v>
+      </c>
+      <c r="G343">
+        <v>1</v>
       </c>
       <c r="H343" t="s">
         <v>437</v>
@@ -23375,8 +25427,14 @@
       <c r="D344" t="s">
         <v>433</v>
       </c>
+      <c r="E344">
+        <v>0</v>
+      </c>
       <c r="F344" t="s">
         <v>434</v>
+      </c>
+      <c r="G344">
+        <v>1</v>
       </c>
       <c r="H344" t="s">
         <v>437</v>
@@ -23434,8 +25492,14 @@
       <c r="D345" t="s">
         <v>440</v>
       </c>
+      <c r="E345">
+        <v>0</v>
+      </c>
       <c r="F345" t="s">
         <v>434</v>
+      </c>
+      <c r="G345">
+        <v>1</v>
       </c>
       <c r="H345" t="s">
         <v>437</v>
@@ -23493,8 +25557,14 @@
       <c r="D346" t="s">
         <v>433</v>
       </c>
+      <c r="E346">
+        <v>0</v>
+      </c>
       <c r="F346" t="s">
         <v>442</v>
+      </c>
+      <c r="G346">
+        <v>0</v>
       </c>
       <c r="H346" t="s">
         <v>219</v>
@@ -23552,8 +25622,14 @@
       <c r="D347" t="s">
         <v>433</v>
       </c>
+      <c r="E347">
+        <v>0</v>
+      </c>
       <c r="F347" t="s">
         <v>442</v>
+      </c>
+      <c r="G347">
+        <v>0</v>
       </c>
       <c r="H347" t="s">
         <v>219</v>
@@ -23611,8 +25687,14 @@
       <c r="D348" t="s">
         <v>445</v>
       </c>
+      <c r="E348">
+        <v>0</v>
+      </c>
       <c r="F348" t="s">
         <v>442</v>
+      </c>
+      <c r="G348">
+        <v>0</v>
       </c>
       <c r="H348" t="s">
         <v>446</v>
@@ -23670,8 +25752,14 @@
       <c r="D349" t="s">
         <v>445</v>
       </c>
+      <c r="E349">
+        <v>0</v>
+      </c>
       <c r="F349" t="s">
         <v>442</v>
+      </c>
+      <c r="G349">
+        <v>0</v>
       </c>
       <c r="H349" t="s">
         <v>219</v>
@@ -23729,8 +25817,14 @@
       <c r="D350" t="s">
         <v>445</v>
       </c>
+      <c r="E350">
+        <v>0</v>
+      </c>
       <c r="F350" t="s">
         <v>442</v>
+      </c>
+      <c r="G350">
+        <v>0</v>
       </c>
       <c r="H350" t="s">
         <v>219</v>
@@ -23788,8 +25882,14 @@
       <c r="D351" t="s">
         <v>445</v>
       </c>
+      <c r="E351">
+        <v>0</v>
+      </c>
       <c r="F351" t="s">
         <v>442</v>
+      </c>
+      <c r="G351">
+        <v>0</v>
       </c>
       <c r="H351" t="s">
         <v>73</v>
@@ -23847,8 +25947,14 @@
       <c r="D352" t="s">
         <v>445</v>
       </c>
+      <c r="E352">
+        <v>0</v>
+      </c>
       <c r="F352" t="s">
         <v>442</v>
+      </c>
+      <c r="G352">
+        <v>0</v>
       </c>
       <c r="H352" t="s">
         <v>306</v>
@@ -23906,8 +26012,14 @@
       <c r="D353" t="s">
         <v>445</v>
       </c>
+      <c r="E353">
+        <v>0</v>
+      </c>
       <c r="F353" t="s">
         <v>442</v>
+      </c>
+      <c r="G353">
+        <v>0</v>
       </c>
       <c r="H353" t="s">
         <v>306</v>
@@ -23965,8 +26077,14 @@
       <c r="D354" t="s">
         <v>445</v>
       </c>
+      <c r="E354">
+        <v>0</v>
+      </c>
       <c r="F354" t="s">
         <v>442</v>
+      </c>
+      <c r="G354">
+        <v>0</v>
       </c>
       <c r="H354" t="s">
         <v>449</v>
@@ -24024,8 +26142,14 @@
       <c r="D355" t="s">
         <v>445</v>
       </c>
+      <c r="E355">
+        <v>0</v>
+      </c>
       <c r="F355" t="s">
         <v>442</v>
+      </c>
+      <c r="G355">
+        <v>0</v>
       </c>
       <c r="H355" t="s">
         <v>199</v>
@@ -24083,8 +26207,14 @@
       <c r="D356" t="s">
         <v>445</v>
       </c>
+      <c r="E356">
+        <v>0</v>
+      </c>
       <c r="F356" t="s">
         <v>442</v>
+      </c>
+      <c r="G356">
+        <v>0</v>
       </c>
       <c r="H356" t="s">
         <v>199</v>
@@ -24142,8 +26272,14 @@
       <c r="D357" t="s">
         <v>445</v>
       </c>
+      <c r="E357">
+        <v>0</v>
+      </c>
       <c r="F357" t="s">
         <v>442</v>
+      </c>
+      <c r="G357">
+        <v>0</v>
       </c>
       <c r="H357" t="s">
         <v>199</v>
@@ -24201,8 +26337,14 @@
       <c r="D358" t="s">
         <v>445</v>
       </c>
+      <c r="E358">
+        <v>0</v>
+      </c>
       <c r="F358" t="s">
         <v>442</v>
+      </c>
+      <c r="G358">
+        <v>0</v>
       </c>
       <c r="H358" t="s">
         <v>219</v>
@@ -24260,8 +26402,14 @@
       <c r="D359" t="s">
         <v>445</v>
       </c>
+      <c r="E359">
+        <v>0</v>
+      </c>
       <c r="F359" t="s">
         <v>442</v>
+      </c>
+      <c r="G359">
+        <v>0</v>
       </c>
       <c r="H359" t="s">
         <v>219</v>
@@ -24319,8 +26467,14 @@
       <c r="D360" t="s">
         <v>445</v>
       </c>
+      <c r="E360">
+        <v>0</v>
+      </c>
       <c r="F360" t="s">
         <v>442</v>
+      </c>
+      <c r="G360">
+        <v>0</v>
       </c>
       <c r="H360" t="s">
         <v>219</v>
@@ -24378,8 +26532,14 @@
       <c r="D361" t="s">
         <v>445</v>
       </c>
+      <c r="E361">
+        <v>0</v>
+      </c>
       <c r="F361" t="s">
         <v>442</v>
+      </c>
+      <c r="G361">
+        <v>0</v>
       </c>
       <c r="H361" t="s">
         <v>306</v>
@@ -24437,8 +26597,14 @@
       <c r="D362" t="s">
         <v>445</v>
       </c>
+      <c r="E362">
+        <v>0</v>
+      </c>
       <c r="F362" t="s">
         <v>442</v>
+      </c>
+      <c r="G362">
+        <v>0</v>
       </c>
       <c r="H362" t="s">
         <v>306</v>
@@ -24496,8 +26662,14 @@
       <c r="D363" t="s">
         <v>445</v>
       </c>
+      <c r="E363">
+        <v>0</v>
+      </c>
       <c r="F363" t="s">
         <v>442</v>
+      </c>
+      <c r="G363">
+        <v>0</v>
       </c>
       <c r="H363" t="s">
         <v>453</v>
@@ -24555,8 +26727,14 @@
       <c r="D364" t="s">
         <v>445</v>
       </c>
+      <c r="E364">
+        <v>0</v>
+      </c>
       <c r="F364" t="s">
         <v>442</v>
+      </c>
+      <c r="G364">
+        <v>0</v>
       </c>
       <c r="H364" t="s">
         <v>455</v>
@@ -24614,8 +26792,14 @@
       <c r="D365" t="s">
         <v>459</v>
       </c>
+      <c r="E365">
+        <v>0</v>
+      </c>
       <c r="F365" t="s">
         <v>460</v>
+      </c>
+      <c r="G365">
+        <v>1</v>
       </c>
       <c r="H365" t="s">
         <v>219</v>
@@ -24673,8 +26857,14 @@
       <c r="D366" t="s">
         <v>464</v>
       </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
       <c r="F366" t="s">
         <v>460</v>
+      </c>
+      <c r="G366">
+        <v>1</v>
       </c>
       <c r="H366" t="s">
         <v>219</v>
@@ -24732,8 +26922,14 @@
       <c r="D367" t="s">
         <v>467</v>
       </c>
+      <c r="E367">
+        <v>1</v>
+      </c>
       <c r="F367" t="s">
         <v>468</v>
+      </c>
+      <c r="G367">
+        <v>0</v>
       </c>
       <c r="H367" t="s">
         <v>469</v>
@@ -24791,8 +26987,14 @@
       <c r="D368" t="s">
         <v>467</v>
       </c>
+      <c r="E368">
+        <v>1</v>
+      </c>
       <c r="F368" t="s">
         <v>473</v>
+      </c>
+      <c r="G368">
+        <v>0</v>
       </c>
       <c r="H368" t="s">
         <v>469</v>
@@ -24850,8 +27052,14 @@
       <c r="D369" t="s">
         <v>467</v>
       </c>
+      <c r="E369">
+        <v>1</v>
+      </c>
       <c r="F369" t="s">
         <v>475</v>
+      </c>
+      <c r="G369">
+        <v>0</v>
       </c>
       <c r="H369" t="s">
         <v>469</v>
@@ -24909,8 +27117,14 @@
       <c r="D370" t="s">
         <v>477</v>
       </c>
+      <c r="E370">
+        <v>0</v>
+      </c>
       <c r="F370" t="s">
         <v>468</v>
+      </c>
+      <c r="G370">
+        <v>0</v>
       </c>
       <c r="H370" t="s">
         <v>121</v>
@@ -24968,8 +27182,14 @@
       <c r="D371" t="s">
         <v>477</v>
       </c>
+      <c r="E371">
+        <v>0</v>
+      </c>
       <c r="F371" t="s">
         <v>475</v>
+      </c>
+      <c r="G371">
+        <v>0</v>
       </c>
       <c r="H371" t="s">
         <v>480</v>
@@ -25027,8 +27247,14 @@
       <c r="D372" t="s">
         <v>477</v>
       </c>
+      <c r="E372">
+        <v>0</v>
+      </c>
       <c r="F372" t="s">
         <v>483</v>
+      </c>
+      <c r="G372">
+        <v>0</v>
       </c>
       <c r="H372" t="s">
         <v>480</v>
@@ -25086,8 +27312,14 @@
       <c r="D373" t="s">
         <v>485</v>
       </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
       <c r="F373" t="s">
         <v>486</v>
+      </c>
+      <c r="G373">
+        <v>0</v>
       </c>
       <c r="H373" t="s">
         <v>487</v>
@@ -25145,8 +27377,14 @@
       <c r="D374" t="s">
         <v>485</v>
       </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
       <c r="F374" t="s">
         <v>486</v>
+      </c>
+      <c r="G374">
+        <v>0</v>
       </c>
       <c r="H374" t="s">
         <v>67</v>
@@ -25204,8 +27442,14 @@
       <c r="D375" t="s">
         <v>477</v>
       </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
       <c r="F375" t="s">
         <v>475</v>
+      </c>
+      <c r="G375">
+        <v>0</v>
       </c>
       <c r="H375" t="s">
         <v>67</v>
@@ -25263,8 +27507,14 @@
       <c r="D376" t="s">
         <v>477</v>
       </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
       <c r="F376" t="s">
         <v>483</v>
+      </c>
+      <c r="G376">
+        <v>0</v>
       </c>
       <c r="H376" t="s">
         <v>67</v>
@@ -25322,8 +27572,14 @@
       <c r="D377" t="s">
         <v>485</v>
       </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
       <c r="F377" t="s">
         <v>486</v>
+      </c>
+      <c r="G377">
+        <v>0</v>
       </c>
       <c r="H377" t="s">
         <v>271</v>
@@ -25381,8 +27637,14 @@
       <c r="D378" t="s">
         <v>477</v>
       </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
       <c r="F378" t="s">
         <v>475</v>
+      </c>
+      <c r="G378">
+        <v>0</v>
       </c>
       <c r="H378" t="s">
         <v>271</v>
@@ -25440,8 +27702,14 @@
       <c r="D379" t="s">
         <v>485</v>
       </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
       <c r="F379" t="s">
         <v>486</v>
+      </c>
+      <c r="G379">
+        <v>0</v>
       </c>
       <c r="H379" t="s">
         <v>67</v>
@@ -25499,8 +27767,14 @@
       <c r="D380" t="s">
         <v>477</v>
       </c>
+      <c r="E380">
+        <v>0</v>
+      </c>
       <c r="F380" t="s">
         <v>475</v>
+      </c>
+      <c r="G380">
+        <v>0</v>
       </c>
       <c r="H380" t="s">
         <v>67</v>
@@ -25558,8 +27832,14 @@
       <c r="D381" t="s">
         <v>485</v>
       </c>
+      <c r="E381">
+        <v>0</v>
+      </c>
       <c r="F381" t="s">
         <v>486</v>
+      </c>
+      <c r="G381">
+        <v>0</v>
       </c>
       <c r="H381" t="s">
         <v>480</v>
@@ -25617,8 +27897,14 @@
       <c r="D382" t="s">
         <v>477</v>
       </c>
+      <c r="E382">
+        <v>0</v>
+      </c>
       <c r="F382" t="s">
         <v>475</v>
+      </c>
+      <c r="G382">
+        <v>0</v>
       </c>
       <c r="H382" t="s">
         <v>480</v>
@@ -25676,8 +27962,14 @@
       <c r="D383" t="s">
         <v>485</v>
       </c>
+      <c r="E383">
+        <v>0</v>
+      </c>
       <c r="F383" t="s">
         <v>486</v>
+      </c>
+      <c r="G383">
+        <v>0</v>
       </c>
       <c r="H383" t="s">
         <v>493</v>
@@ -25735,8 +28027,14 @@
       <c r="D384" t="s">
         <v>477</v>
       </c>
+      <c r="E384">
+        <v>0</v>
+      </c>
       <c r="F384" t="s">
         <v>475</v>
+      </c>
+      <c r="G384">
+        <v>0</v>
       </c>
       <c r="H384" t="s">
         <v>493</v>
@@ -25794,8 +28092,14 @@
       <c r="D385" t="s">
         <v>485</v>
       </c>
+      <c r="E385">
+        <v>0</v>
+      </c>
       <c r="F385" t="s">
         <v>486</v>
+      </c>
+      <c r="G385">
+        <v>0</v>
       </c>
       <c r="H385" t="s">
         <v>495</v>
@@ -25853,8 +28157,14 @@
       <c r="D386" t="s">
         <v>477</v>
       </c>
+      <c r="E386">
+        <v>0</v>
+      </c>
       <c r="F386" t="s">
         <v>475</v>
+      </c>
+      <c r="G386">
+        <v>0</v>
       </c>
       <c r="H386" t="s">
         <v>495</v>
@@ -25912,8 +28222,14 @@
       <c r="D387" t="s">
         <v>485</v>
       </c>
+      <c r="E387">
+        <v>0</v>
+      </c>
       <c r="F387" t="s">
         <v>486</v>
+      </c>
+      <c r="G387">
+        <v>0</v>
       </c>
       <c r="H387" t="s">
         <v>271</v>
@@ -25971,8 +28287,14 @@
       <c r="D388" t="s">
         <v>477</v>
       </c>
+      <c r="E388">
+        <v>0</v>
+      </c>
       <c r="F388" t="s">
         <v>475</v>
+      </c>
+      <c r="G388">
+        <v>0</v>
       </c>
       <c r="H388" t="s">
         <v>271</v>
@@ -26030,8 +28352,14 @@
       <c r="D389" t="s">
         <v>485</v>
       </c>
+      <c r="E389">
+        <v>0</v>
+      </c>
       <c r="F389" t="s">
         <v>486</v>
+      </c>
+      <c r="G389">
+        <v>0</v>
       </c>
       <c r="H389" t="s">
         <v>24</v>
@@ -26089,8 +28417,14 @@
       <c r="D390" t="s">
         <v>485</v>
       </c>
+      <c r="E390">
+        <v>0</v>
+      </c>
       <c r="F390" t="s">
         <v>486</v>
+      </c>
+      <c r="G390">
+        <v>0</v>
       </c>
       <c r="H390" t="s">
         <v>480</v>
@@ -26148,8 +28482,14 @@
       <c r="D391" t="s">
         <v>477</v>
       </c>
+      <c r="E391">
+        <v>0</v>
+      </c>
       <c r="F391" t="s">
         <v>475</v>
+      </c>
+      <c r="G391">
+        <v>0</v>
       </c>
       <c r="H391" t="s">
         <v>480</v>
@@ -26207,8 +28547,14 @@
       <c r="D392" t="s">
         <v>485</v>
       </c>
+      <c r="E392">
+        <v>0</v>
+      </c>
       <c r="F392" t="s">
         <v>486</v>
+      </c>
+      <c r="G392">
+        <v>0</v>
       </c>
       <c r="H392" t="s">
         <v>98</v>
@@ -26266,8 +28612,14 @@
       <c r="D393" t="s">
         <v>477</v>
       </c>
+      <c r="E393">
+        <v>0</v>
+      </c>
       <c r="F393" t="s">
         <v>475</v>
+      </c>
+      <c r="G393">
+        <v>0</v>
       </c>
       <c r="H393" t="s">
         <v>98</v>
@@ -26325,8 +28677,14 @@
       <c r="D394" t="s">
         <v>485</v>
       </c>
+      <c r="E394">
+        <v>0</v>
+      </c>
       <c r="F394" t="s">
         <v>486</v>
+      </c>
+      <c r="G394">
+        <v>0</v>
       </c>
       <c r="H394" t="s">
         <v>271</v>
@@ -26384,8 +28742,14 @@
       <c r="D395" t="s">
         <v>477</v>
       </c>
+      <c r="E395">
+        <v>0</v>
+      </c>
       <c r="F395" t="s">
         <v>475</v>
+      </c>
+      <c r="G395">
+        <v>0</v>
       </c>
       <c r="H395" t="s">
         <v>271</v>
@@ -26443,8 +28807,14 @@
       <c r="D396" t="s">
         <v>485</v>
       </c>
+      <c r="E396">
+        <v>0</v>
+      </c>
       <c r="F396" t="s">
         <v>486</v>
+      </c>
+      <c r="G396">
+        <v>0</v>
       </c>
       <c r="H396" t="s">
         <v>271</v>
@@ -26502,8 +28872,14 @@
       <c r="D397" t="s">
         <v>477</v>
       </c>
+      <c r="E397">
+        <v>0</v>
+      </c>
       <c r="F397" t="s">
         <v>475</v>
+      </c>
+      <c r="G397">
+        <v>0</v>
       </c>
       <c r="H397" t="s">
         <v>271</v>
@@ -26561,8 +28937,14 @@
       <c r="D398" t="s">
         <v>485</v>
       </c>
+      <c r="E398">
+        <v>0</v>
+      </c>
       <c r="F398" t="s">
         <v>486</v>
+      </c>
+      <c r="G398">
+        <v>0</v>
       </c>
       <c r="H398" t="s">
         <v>480</v>
@@ -26620,8 +29002,14 @@
       <c r="D399" t="s">
         <v>477</v>
       </c>
+      <c r="E399">
+        <v>0</v>
+      </c>
       <c r="F399" t="s">
         <v>475</v>
+      </c>
+      <c r="G399">
+        <v>0</v>
       </c>
       <c r="H399" t="s">
         <v>480</v>
@@ -26679,8 +29067,14 @@
       <c r="D400" t="s">
         <v>485</v>
       </c>
+      <c r="E400">
+        <v>0</v>
+      </c>
       <c r="F400" t="s">
         <v>486</v>
+      </c>
+      <c r="G400">
+        <v>0</v>
       </c>
       <c r="H400" t="s">
         <v>177</v>
@@ -26738,8 +29132,14 @@
       <c r="D401" t="s">
         <v>485</v>
       </c>
+      <c r="E401">
+        <v>0</v>
+      </c>
       <c r="F401" t="s">
         <v>486</v>
+      </c>
+      <c r="G401">
+        <v>0</v>
       </c>
       <c r="H401" t="s">
         <v>480</v>
@@ -26797,8 +29197,14 @@
       <c r="D402" t="s">
         <v>477</v>
       </c>
+      <c r="E402">
+        <v>0</v>
+      </c>
       <c r="F402" t="s">
         <v>475</v>
+      </c>
+      <c r="G402">
+        <v>0</v>
       </c>
       <c r="H402" t="s">
         <v>480</v>
@@ -26856,8 +29262,14 @@
       <c r="D403" t="s">
         <v>485</v>
       </c>
+      <c r="E403">
+        <v>0</v>
+      </c>
       <c r="F403" t="s">
         <v>486</v>
+      </c>
+      <c r="G403">
+        <v>0</v>
       </c>
       <c r="H403" t="s">
         <v>271</v>
@@ -26915,8 +29327,14 @@
       <c r="D404" t="s">
         <v>477</v>
       </c>
+      <c r="E404">
+        <v>0</v>
+      </c>
       <c r="F404" t="s">
         <v>475</v>
+      </c>
+      <c r="G404">
+        <v>0</v>
       </c>
       <c r="H404" t="s">
         <v>271</v>
@@ -26974,8 +29392,14 @@
       <c r="D405" t="s">
         <v>485</v>
       </c>
+      <c r="E405">
+        <v>0</v>
+      </c>
       <c r="F405" t="s">
         <v>486</v>
+      </c>
+      <c r="G405">
+        <v>0</v>
       </c>
       <c r="H405" t="s">
         <v>503</v>
@@ -27033,8 +29457,14 @@
       <c r="D406" t="s">
         <v>485</v>
       </c>
+      <c r="E406">
+        <v>0</v>
+      </c>
       <c r="F406" t="s">
         <v>486</v>
+      </c>
+      <c r="G406">
+        <v>0</v>
       </c>
       <c r="H406" t="s">
         <v>65</v>
@@ -27092,8 +29522,14 @@
       <c r="D407" t="s">
         <v>485</v>
       </c>
+      <c r="E407">
+        <v>0</v>
+      </c>
       <c r="F407" t="s">
         <v>486</v>
+      </c>
+      <c r="G407">
+        <v>0</v>
       </c>
       <c r="H407" t="s">
         <v>67</v>
@@ -27151,8 +29587,14 @@
       <c r="D408" t="s">
         <v>485</v>
       </c>
+      <c r="E408">
+        <v>0</v>
+      </c>
       <c r="F408" t="s">
         <v>486</v>
+      </c>
+      <c r="G408">
+        <v>0</v>
       </c>
       <c r="H408" t="s">
         <v>166</v>
@@ -27210,8 +29652,14 @@
       <c r="D409" t="s">
         <v>508</v>
       </c>
+      <c r="E409">
+        <v>1</v>
+      </c>
       <c r="F409" t="s">
         <v>509</v>
+      </c>
+      <c r="G409">
+        <v>0</v>
       </c>
       <c r="H409" t="s">
         <v>510</v>
@@ -27269,8 +29717,14 @@
       <c r="D410" t="s">
         <v>515</v>
       </c>
+      <c r="E410">
+        <v>0</v>
+      </c>
       <c r="F410" t="s">
         <v>516</v>
+      </c>
+      <c r="G410">
+        <v>1</v>
       </c>
       <c r="H410" t="s">
         <v>517</v>
@@ -27328,8 +29782,14 @@
       <c r="D411" t="s">
         <v>515</v>
       </c>
+      <c r="E411">
+        <v>0</v>
+      </c>
       <c r="F411" t="s">
         <v>521</v>
+      </c>
+      <c r="G411">
+        <v>0</v>
       </c>
       <c r="H411" t="s">
         <v>517</v>
@@ -27387,8 +29847,14 @@
       <c r="D412" t="s">
         <v>515</v>
       </c>
+      <c r="E412">
+        <v>0</v>
+      </c>
       <c r="F412" t="s">
         <v>516</v>
+      </c>
+      <c r="G412">
+        <v>1</v>
       </c>
       <c r="H412" t="s">
         <v>44</v>
@@ -27446,8 +29912,14 @@
       <c r="D413" t="s">
         <v>515</v>
       </c>
+      <c r="E413">
+        <v>0</v>
+      </c>
       <c r="F413" t="s">
         <v>516</v>
+      </c>
+      <c r="G413">
+        <v>1</v>
       </c>
       <c r="H413" t="s">
         <v>112</v>
@@ -27505,8 +29977,14 @@
       <c r="D414" t="s">
         <v>515</v>
       </c>
+      <c r="E414">
+        <v>0</v>
+      </c>
       <c r="F414" t="s">
         <v>516</v>
+      </c>
+      <c r="G414">
+        <v>1</v>
       </c>
       <c r="H414" t="s">
         <v>112</v>
@@ -27564,8 +30042,14 @@
       <c r="D415" t="s">
         <v>525</v>
       </c>
+      <c r="E415">
+        <v>0</v>
+      </c>
       <c r="F415" t="s">
         <v>526</v>
+      </c>
+      <c r="G415">
+        <v>0</v>
       </c>
       <c r="H415" t="s">
         <v>98</v>
@@ -27623,8 +30107,14 @@
       <c r="D416" t="s">
         <v>525</v>
       </c>
+      <c r="E416">
+        <v>0</v>
+      </c>
       <c r="F416" t="s">
         <v>526</v>
+      </c>
+      <c r="G416">
+        <v>0</v>
       </c>
       <c r="H416" t="s">
         <v>517</v>
@@ -27682,8 +30172,14 @@
       <c r="D417" t="s">
         <v>525</v>
       </c>
+      <c r="E417">
+        <v>0</v>
+      </c>
       <c r="F417" t="s">
         <v>526</v>
+      </c>
+      <c r="G417">
+        <v>0</v>
       </c>
       <c r="H417" t="s">
         <v>517</v>
@@ -27741,8 +30237,14 @@
       <c r="D418" t="s">
         <v>525</v>
       </c>
+      <c r="E418">
+        <v>0</v>
+      </c>
       <c r="F418" t="s">
         <v>526</v>
+      </c>
+      <c r="G418">
+        <v>0</v>
       </c>
       <c r="H418" t="s">
         <v>528</v>
@@ -27800,8 +30302,14 @@
       <c r="D419" t="s">
         <v>525</v>
       </c>
+      <c r="E419">
+        <v>0</v>
+      </c>
       <c r="F419" t="s">
         <v>526</v>
+      </c>
+      <c r="G419">
+        <v>0</v>
       </c>
       <c r="H419" t="s">
         <v>112</v>
@@ -27859,8 +30367,14 @@
       <c r="D420" t="s">
         <v>525</v>
       </c>
+      <c r="E420">
+        <v>0</v>
+      </c>
       <c r="F420" t="s">
         <v>526</v>
+      </c>
+      <c r="G420">
+        <v>0</v>
       </c>
       <c r="H420" t="s">
         <v>528</v>
@@ -27918,8 +30432,14 @@
       <c r="D421" t="s">
         <v>525</v>
       </c>
+      <c r="E421">
+        <v>0</v>
+      </c>
       <c r="F421" t="s">
         <v>526</v>
+      </c>
+      <c r="G421">
+        <v>0</v>
       </c>
       <c r="H421" t="s">
         <v>528</v>
@@ -27977,8 +30497,14 @@
       <c r="D422" t="s">
         <v>515</v>
       </c>
+      <c r="E422">
+        <v>0</v>
+      </c>
       <c r="F422" t="s">
         <v>534</v>
+      </c>
+      <c r="G422">
+        <v>0</v>
       </c>
       <c r="H422" t="s">
         <v>528</v>
@@ -28036,8 +30562,14 @@
       <c r="D423" t="s">
         <v>525</v>
       </c>
+      <c r="E423">
+        <v>0</v>
+      </c>
       <c r="F423" t="s">
         <v>526</v>
+      </c>
+      <c r="G423">
+        <v>0</v>
       </c>
       <c r="H423" t="s">
         <v>112</v>
@@ -28095,8 +30627,14 @@
       <c r="D424" t="s">
         <v>525</v>
       </c>
+      <c r="E424">
+        <v>0</v>
+      </c>
       <c r="F424" t="s">
         <v>526</v>
+      </c>
+      <c r="G424">
+        <v>0</v>
       </c>
       <c r="H424" t="s">
         <v>382</v>
@@ -28154,8 +30692,14 @@
       <c r="D425" t="s">
         <v>525</v>
       </c>
+      <c r="E425">
+        <v>0</v>
+      </c>
       <c r="F425" t="s">
         <v>526</v>
+      </c>
+      <c r="G425">
+        <v>0</v>
       </c>
       <c r="H425" t="s">
         <v>112</v>
@@ -28213,8 +30757,14 @@
       <c r="D426" t="s">
         <v>525</v>
       </c>
+      <c r="E426">
+        <v>0</v>
+      </c>
       <c r="F426" t="s">
         <v>526</v>
+      </c>
+      <c r="G426">
+        <v>0</v>
       </c>
       <c r="H426" t="s">
         <v>538</v>
@@ -28272,8 +30822,14 @@
       <c r="D427" t="s">
         <v>525</v>
       </c>
+      <c r="E427">
+        <v>0</v>
+      </c>
       <c r="F427" t="s">
         <v>526</v>
+      </c>
+      <c r="G427">
+        <v>0</v>
       </c>
       <c r="H427" t="s">
         <v>44</v>
@@ -28331,8 +30887,14 @@
       <c r="D428" t="s">
         <v>525</v>
       </c>
+      <c r="E428">
+        <v>0</v>
+      </c>
       <c r="F428" t="s">
         <v>526</v>
+      </c>
+      <c r="G428">
+        <v>0</v>
       </c>
       <c r="H428" t="s">
         <v>541</v>
@@ -28390,8 +30952,14 @@
       <c r="D429" t="s">
         <v>525</v>
       </c>
+      <c r="E429">
+        <v>0</v>
+      </c>
       <c r="F429" t="s">
         <v>526</v>
+      </c>
+      <c r="G429">
+        <v>0</v>
       </c>
       <c r="H429" t="s">
         <v>528</v>
@@ -28449,8 +31017,14 @@
       <c r="D430" t="s">
         <v>525</v>
       </c>
+      <c r="E430">
+        <v>0</v>
+      </c>
       <c r="F430" t="s">
         <v>526</v>
+      </c>
+      <c r="G430">
+        <v>0</v>
       </c>
       <c r="H430" t="s">
         <v>121</v>
@@ -28508,8 +31082,14 @@
       <c r="D431" t="s">
         <v>525</v>
       </c>
+      <c r="E431">
+        <v>0</v>
+      </c>
       <c r="F431" t="s">
         <v>526</v>
+      </c>
+      <c r="G431">
+        <v>0</v>
       </c>
       <c r="H431" t="s">
         <v>545</v>
@@ -28567,8 +31147,14 @@
       <c r="D432" t="s">
         <v>525</v>
       </c>
+      <c r="E432">
+        <v>0</v>
+      </c>
       <c r="F432" t="s">
         <v>526</v>
+      </c>
+      <c r="G432">
+        <v>0</v>
       </c>
       <c r="H432" t="s">
         <v>545</v>
@@ -28626,8 +31212,14 @@
       <c r="D433" t="s">
         <v>525</v>
       </c>
+      <c r="E433">
+        <v>0</v>
+      </c>
       <c r="F433" t="s">
         <v>526</v>
+      </c>
+      <c r="G433">
+        <v>0</v>
       </c>
       <c r="H433" t="s">
         <v>547</v>
@@ -28685,8 +31277,14 @@
       <c r="D434" t="s">
         <v>525</v>
       </c>
+      <c r="E434">
+        <v>0</v>
+      </c>
       <c r="F434" t="s">
         <v>526</v>
+      </c>
+      <c r="G434">
+        <v>0</v>
       </c>
       <c r="H434" t="s">
         <v>112</v>
@@ -28744,8 +31342,14 @@
       <c r="D435" t="s">
         <v>525</v>
       </c>
+      <c r="E435">
+        <v>0</v>
+      </c>
       <c r="F435" t="s">
         <v>526</v>
+      </c>
+      <c r="G435">
+        <v>0</v>
       </c>
       <c r="H435" t="s">
         <v>528</v>
@@ -28803,8 +31407,14 @@
       <c r="D436" t="s">
         <v>525</v>
       </c>
+      <c r="E436">
+        <v>0</v>
+      </c>
       <c r="F436" t="s">
         <v>526</v>
+      </c>
+      <c r="G436">
+        <v>0</v>
       </c>
       <c r="H436" t="s">
         <v>541</v>
@@ -28862,8 +31472,14 @@
       <c r="D437" t="s">
         <v>525</v>
       </c>
+      <c r="E437">
+        <v>0</v>
+      </c>
       <c r="F437" t="s">
         <v>526</v>
+      </c>
+      <c r="G437">
+        <v>0</v>
       </c>
       <c r="H437" t="s">
         <v>57</v>
@@ -28921,8 +31537,14 @@
       <c r="D438" t="s">
         <v>525</v>
       </c>
+      <c r="E438">
+        <v>0</v>
+      </c>
       <c r="F438" t="s">
         <v>526</v>
+      </c>
+      <c r="G438">
+        <v>0</v>
       </c>
       <c r="H438" t="s">
         <v>44</v>
@@ -28980,8 +31602,14 @@
       <c r="D439" t="s">
         <v>525</v>
       </c>
+      <c r="E439">
+        <v>0</v>
+      </c>
       <c r="F439" t="s">
         <v>526</v>
+      </c>
+      <c r="G439">
+        <v>0</v>
       </c>
       <c r="H439" t="s">
         <v>161</v>
@@ -29039,8 +31667,14 @@
       <c r="D440" t="s">
         <v>525</v>
       </c>
+      <c r="E440">
+        <v>0</v>
+      </c>
       <c r="F440" t="s">
         <v>526</v>
+      </c>
+      <c r="G440">
+        <v>0</v>
       </c>
       <c r="H440" t="s">
         <v>553</v>
@@ -29098,8 +31732,14 @@
       <c r="D441" t="s">
         <v>525</v>
       </c>
+      <c r="E441">
+        <v>0</v>
+      </c>
       <c r="F441" t="s">
         <v>526</v>
+      </c>
+      <c r="G441">
+        <v>0</v>
       </c>
       <c r="H441" t="s">
         <v>553</v>
@@ -29157,8 +31797,14 @@
       <c r="D442" t="s">
         <v>525</v>
       </c>
+      <c r="E442">
+        <v>0</v>
+      </c>
       <c r="F442" t="s">
         <v>526</v>
+      </c>
+      <c r="G442">
+        <v>0</v>
       </c>
       <c r="H442" t="s">
         <v>553</v>
@@ -29216,8 +31862,14 @@
       <c r="D443" t="s">
         <v>525</v>
       </c>
+      <c r="E443">
+        <v>0</v>
+      </c>
       <c r="F443" t="s">
         <v>526</v>
+      </c>
+      <c r="G443">
+        <v>0</v>
       </c>
       <c r="H443" t="s">
         <v>112</v>
@@ -29275,8 +31927,14 @@
       <c r="D444" t="s">
         <v>525</v>
       </c>
+      <c r="E444">
+        <v>0</v>
+      </c>
       <c r="F444" t="s">
         <v>526</v>
+      </c>
+      <c r="G444">
+        <v>0</v>
       </c>
       <c r="H444" t="s">
         <v>112</v>
@@ -29334,8 +31992,14 @@
       <c r="D445" t="s">
         <v>525</v>
       </c>
+      <c r="E445">
+        <v>0</v>
+      </c>
       <c r="F445" t="s">
         <v>526</v>
+      </c>
+      <c r="G445">
+        <v>0</v>
       </c>
       <c r="H445" t="s">
         <v>528</v>
@@ -29393,8 +32057,14 @@
       <c r="D446" t="s">
         <v>525</v>
       </c>
+      <c r="E446">
+        <v>0</v>
+      </c>
       <c r="F446" t="s">
         <v>526</v>
+      </c>
+      <c r="G446">
+        <v>0</v>
       </c>
       <c r="H446" t="s">
         <v>545</v>
@@ -29452,8 +32122,14 @@
       <c r="D447" t="s">
         <v>525</v>
       </c>
+      <c r="E447">
+        <v>0</v>
+      </c>
       <c r="F447" t="s">
         <v>526</v>
+      </c>
+      <c r="G447">
+        <v>0</v>
       </c>
       <c r="H447" t="s">
         <v>545</v>
@@ -29511,8 +32187,14 @@
       <c r="D448" t="s">
         <v>525</v>
       </c>
+      <c r="E448">
+        <v>0</v>
+      </c>
       <c r="F448" t="s">
         <v>526</v>
+      </c>
+      <c r="G448">
+        <v>0</v>
       </c>
       <c r="H448" t="s">
         <v>553</v>
@@ -29570,8 +32252,14 @@
       <c r="D449" t="s">
         <v>525</v>
       </c>
+      <c r="E449">
+        <v>0</v>
+      </c>
       <c r="F449" t="s">
         <v>526</v>
+      </c>
+      <c r="G449">
+        <v>0</v>
       </c>
       <c r="H449" t="s">
         <v>553</v>
@@ -29629,8 +32317,14 @@
       <c r="D450" t="s">
         <v>525</v>
       </c>
+      <c r="E450">
+        <v>0</v>
+      </c>
       <c r="F450" t="s">
         <v>526</v>
+      </c>
+      <c r="G450">
+        <v>0</v>
       </c>
       <c r="H450" t="s">
         <v>553</v>
@@ -29688,8 +32382,14 @@
       <c r="D451" t="s">
         <v>525</v>
       </c>
+      <c r="E451">
+        <v>0</v>
+      </c>
       <c r="F451" t="s">
         <v>526</v>
+      </c>
+      <c r="G451">
+        <v>0</v>
       </c>
       <c r="H451" t="s">
         <v>560</v>
@@ -29747,8 +32447,14 @@
       <c r="D452" t="s">
         <v>525</v>
       </c>
+      <c r="E452">
+        <v>0</v>
+      </c>
       <c r="F452" t="s">
         <v>526</v>
+      </c>
+      <c r="G452">
+        <v>0</v>
       </c>
       <c r="H452" t="s">
         <v>560</v>
@@ -29806,8 +32512,14 @@
       <c r="D453" t="s">
         <v>525</v>
       </c>
+      <c r="E453">
+        <v>0</v>
+      </c>
       <c r="F453" t="s">
         <v>526</v>
+      </c>
+      <c r="G453">
+        <v>0</v>
       </c>
       <c r="H453" t="s">
         <v>561</v>
@@ -29865,8 +32577,14 @@
       <c r="D454" t="s">
         <v>525</v>
       </c>
+      <c r="E454">
+        <v>0</v>
+      </c>
       <c r="F454" t="s">
         <v>526</v>
+      </c>
+      <c r="G454">
+        <v>0</v>
       </c>
       <c r="H454" t="s">
         <v>528</v>
@@ -29924,8 +32642,14 @@
       <c r="D455" t="s">
         <v>525</v>
       </c>
+      <c r="E455">
+        <v>0</v>
+      </c>
       <c r="F455" t="s">
         <v>526</v>
+      </c>
+      <c r="G455">
+        <v>0</v>
       </c>
       <c r="H455" t="s">
         <v>166</v>
@@ -29983,8 +32707,14 @@
       <c r="D456" t="s">
         <v>565</v>
       </c>
+      <c r="E456">
+        <v>0</v>
+      </c>
       <c r="F456" t="s">
         <v>566</v>
+      </c>
+      <c r="G456">
+        <v>1</v>
       </c>
       <c r="H456" t="s">
         <v>567</v>
@@ -30042,8 +32772,14 @@
       <c r="D457" t="s">
         <v>571</v>
       </c>
+      <c r="E457">
+        <v>0</v>
+      </c>
       <c r="F457" t="s">
         <v>566</v>
+      </c>
+      <c r="G457">
+        <v>1</v>
       </c>
       <c r="H457" t="s">
         <v>567</v>
@@ -30101,8 +32837,14 @@
       <c r="D458" t="s">
         <v>565</v>
       </c>
+      <c r="E458">
+        <v>0</v>
+      </c>
       <c r="F458" t="s">
         <v>566</v>
+      </c>
+      <c r="G458">
+        <v>1</v>
       </c>
       <c r="H458" t="s">
         <v>567</v>
@@ -30160,8 +32902,14 @@
       <c r="D459" t="s">
         <v>571</v>
       </c>
+      <c r="E459">
+        <v>0</v>
+      </c>
       <c r="F459" t="s">
         <v>566</v>
+      </c>
+      <c r="G459">
+        <v>1</v>
       </c>
       <c r="H459" t="s">
         <v>567</v>
@@ -30219,8 +32967,14 @@
       <c r="D460" t="s">
         <v>565</v>
       </c>
+      <c r="E460">
+        <v>0</v>
+      </c>
       <c r="F460" t="s">
         <v>566</v>
+      </c>
+      <c r="G460">
+        <v>1</v>
       </c>
       <c r="H460" t="s">
         <v>98</v>
@@ -30278,8 +33032,14 @@
       <c r="D461" t="s">
         <v>565</v>
       </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
       <c r="F461" t="s">
         <v>566</v>
+      </c>
+      <c r="G461">
+        <v>1</v>
       </c>
       <c r="H461" t="s">
         <v>306</v>
@@ -30337,8 +33097,14 @@
       <c r="D462" t="s">
         <v>565</v>
       </c>
+      <c r="E462">
+        <v>0</v>
+      </c>
       <c r="F462" t="s">
         <v>566</v>
+      </c>
+      <c r="G462">
+        <v>1</v>
       </c>
       <c r="H462" t="s">
         <v>567</v>
@@ -30396,8 +33162,14 @@
       <c r="D463" t="s">
         <v>565</v>
       </c>
+      <c r="E463">
+        <v>0</v>
+      </c>
       <c r="F463" t="s">
         <v>566</v>
+      </c>
+      <c r="G463">
+        <v>1</v>
       </c>
       <c r="H463" t="s">
         <v>98</v>
@@ -30455,8 +33227,14 @@
       <c r="D464" t="s">
         <v>565</v>
       </c>
+      <c r="E464">
+        <v>0</v>
+      </c>
       <c r="F464" t="s">
         <v>566</v>
+      </c>
+      <c r="G464">
+        <v>1</v>
       </c>
       <c r="H464" t="s">
         <v>576</v>
@@ -30514,8 +33292,14 @@
       <c r="D465" t="s">
         <v>565</v>
       </c>
+      <c r="E465">
+        <v>0</v>
+      </c>
       <c r="F465" t="s">
         <v>566</v>
+      </c>
+      <c r="G465">
+        <v>1</v>
       </c>
       <c r="H465" t="s">
         <v>274</v>
@@ -30573,8 +33357,14 @@
       <c r="D466" t="s">
         <v>565</v>
       </c>
+      <c r="E466">
+        <v>0</v>
+      </c>
       <c r="F466" t="s">
         <v>566</v>
+      </c>
+      <c r="G466">
+        <v>1</v>
       </c>
       <c r="H466" t="s">
         <v>121</v>
@@ -30632,8 +33422,14 @@
       <c r="D467" t="s">
         <v>565</v>
       </c>
+      <c r="E467">
+        <v>0</v>
+      </c>
       <c r="F467" t="s">
         <v>566</v>
+      </c>
+      <c r="G467">
+        <v>1</v>
       </c>
       <c r="H467" t="s">
         <v>106</v>
@@ -30691,8 +33487,14 @@
       <c r="D468" t="s">
         <v>565</v>
       </c>
+      <c r="E468">
+        <v>0</v>
+      </c>
       <c r="F468" t="s">
         <v>566</v>
+      </c>
+      <c r="G468">
+        <v>1</v>
       </c>
       <c r="H468" t="s">
         <v>567</v>
@@ -30750,8 +33552,14 @@
       <c r="D469" t="s">
         <v>565</v>
       </c>
+      <c r="E469">
+        <v>0</v>
+      </c>
       <c r="F469" t="s">
         <v>566</v>
+      </c>
+      <c r="G469">
+        <v>1</v>
       </c>
       <c r="H469" t="s">
         <v>161</v>
@@ -30809,8 +33617,14 @@
       <c r="D470" t="s">
         <v>565</v>
       </c>
+      <c r="E470">
+        <v>0</v>
+      </c>
       <c r="F470" t="s">
         <v>566</v>
+      </c>
+      <c r="G470">
+        <v>1</v>
       </c>
       <c r="H470" t="s">
         <v>384</v>
@@ -30868,8 +33682,14 @@
       <c r="D471" t="s">
         <v>565</v>
       </c>
+      <c r="E471">
+        <v>0</v>
+      </c>
       <c r="F471" t="s">
         <v>566</v>
+      </c>
+      <c r="G471">
+        <v>1</v>
       </c>
       <c r="H471" t="s">
         <v>63</v>
@@ -30927,8 +33747,14 @@
       <c r="D472" t="s">
         <v>565</v>
       </c>
+      <c r="E472">
+        <v>0</v>
+      </c>
       <c r="F472" t="s">
         <v>566</v>
+      </c>
+      <c r="G472">
+        <v>1</v>
       </c>
       <c r="H472" t="s">
         <v>57</v>
@@ -30986,8 +33812,14 @@
       <c r="D473" t="s">
         <v>565</v>
       </c>
+      <c r="E473">
+        <v>0</v>
+      </c>
       <c r="F473" t="s">
         <v>566</v>
+      </c>
+      <c r="G473">
+        <v>1</v>
       </c>
       <c r="H473" t="s">
         <v>384</v>
@@ -31045,8 +33877,14 @@
       <c r="D474" t="s">
         <v>565</v>
       </c>
+      <c r="E474">
+        <v>0</v>
+      </c>
       <c r="F474" t="s">
         <v>566</v>
+      </c>
+      <c r="G474">
+        <v>1</v>
       </c>
       <c r="H474" t="s">
         <v>161</v>
@@ -31104,8 +33942,14 @@
       <c r="D475" t="s">
         <v>565</v>
       </c>
+      <c r="E475">
+        <v>0</v>
+      </c>
       <c r="F475" t="s">
         <v>566</v>
+      </c>
+      <c r="G475">
+        <v>1</v>
       </c>
       <c r="H475" t="s">
         <v>209</v>
@@ -31163,8 +34007,14 @@
       <c r="D476" t="s">
         <v>565</v>
       </c>
+      <c r="E476">
+        <v>0</v>
+      </c>
       <c r="F476" t="s">
         <v>566</v>
+      </c>
+      <c r="G476">
+        <v>1</v>
       </c>
       <c r="H476" t="s">
         <v>207</v>
@@ -31222,8 +34072,14 @@
       <c r="D477" t="s">
         <v>565</v>
       </c>
+      <c r="E477">
+        <v>0</v>
+      </c>
       <c r="F477" t="s">
         <v>566</v>
+      </c>
+      <c r="G477">
+        <v>1</v>
       </c>
       <c r="H477" t="s">
         <v>207</v>
@@ -31281,8 +34137,14 @@
       <c r="D478" t="s">
         <v>565</v>
       </c>
+      <c r="E478">
+        <v>0</v>
+      </c>
       <c r="F478" t="s">
         <v>566</v>
+      </c>
+      <c r="G478">
+        <v>1</v>
       </c>
       <c r="H478" t="s">
         <v>166</v>
@@ -31340,8 +34202,14 @@
       <c r="D479" t="s">
         <v>565</v>
       </c>
+      <c r="E479">
+        <v>0</v>
+      </c>
       <c r="F479" t="s">
         <v>566</v>
+      </c>
+      <c r="G479">
+        <v>1</v>
       </c>
       <c r="H479" t="s">
         <v>567</v>
@@ -31399,8 +34267,14 @@
       <c r="D480" t="s">
         <v>565</v>
       </c>
+      <c r="E480">
+        <v>0</v>
+      </c>
       <c r="F480" t="s">
         <v>566</v>
+      </c>
+      <c r="G480">
+        <v>1</v>
       </c>
       <c r="H480" t="s">
         <v>150</v>
@@ -31458,8 +34332,14 @@
       <c r="D481" t="s">
         <v>588</v>
       </c>
+      <c r="E481">
+        <v>0</v>
+      </c>
       <c r="F481" t="s">
         <v>589</v>
+      </c>
+      <c r="G481">
+        <v>0</v>
       </c>
       <c r="H481" t="s">
         <v>590</v>
@@ -31517,8 +34397,14 @@
       <c r="D482" t="s">
         <v>593</v>
       </c>
+      <c r="E482">
+        <v>0</v>
+      </c>
       <c r="F482" t="s">
         <v>589</v>
+      </c>
+      <c r="G482">
+        <v>0</v>
       </c>
       <c r="H482" t="s">
         <v>590</v>
@@ -31576,8 +34462,14 @@
       <c r="D483" t="s">
         <v>596</v>
       </c>
+      <c r="E483">
+        <v>1</v>
+      </c>
       <c r="F483" t="s">
         <v>597</v>
+      </c>
+      <c r="G483">
+        <v>0</v>
       </c>
       <c r="H483" t="s">
         <v>271</v>
@@ -31635,8 +34527,14 @@
       <c r="D484" t="s">
         <v>596</v>
       </c>
+      <c r="E484">
+        <v>1</v>
+      </c>
       <c r="F484" t="s">
         <v>597</v>
+      </c>
+      <c r="G484">
+        <v>0</v>
       </c>
       <c r="H484" t="s">
         <v>271</v>
@@ -31694,8 +34592,14 @@
       <c r="D485" t="s">
         <v>596</v>
       </c>
+      <c r="E485">
+        <v>1</v>
+      </c>
       <c r="F485" t="s">
         <v>597</v>
+      </c>
+      <c r="G485">
+        <v>0</v>
       </c>
       <c r="H485" t="s">
         <v>271</v>
@@ -31753,8 +34657,14 @@
       <c r="D486" t="s">
         <v>601</v>
       </c>
+      <c r="E486">
+        <v>0</v>
+      </c>
       <c r="F486" t="s">
         <v>602</v>
+      </c>
+      <c r="G486">
+        <v>1</v>
       </c>
       <c r="H486" t="s">
         <v>44</v>
@@ -31812,8 +34722,14 @@
       <c r="D487" t="s">
         <v>601</v>
       </c>
+      <c r="E487">
+        <v>0</v>
+      </c>
       <c r="F487" t="s">
         <v>602</v>
+      </c>
+      <c r="G487">
+        <v>1</v>
       </c>
       <c r="H487" t="s">
         <v>408</v>
@@ -31871,8 +34787,14 @@
       <c r="D488" t="s">
         <v>601</v>
       </c>
+      <c r="E488">
+        <v>0</v>
+      </c>
       <c r="F488" t="s">
         <v>602</v>
+      </c>
+      <c r="G488">
+        <v>1</v>
       </c>
       <c r="H488" t="s">
         <v>408</v>
@@ -31930,8 +34852,14 @@
       <c r="D489" t="s">
         <v>608</v>
       </c>
+      <c r="E489">
+        <v>0</v>
+      </c>
       <c r="F489" t="s">
         <v>609</v>
+      </c>
+      <c r="G489">
+        <v>0</v>
       </c>
       <c r="H489" t="s">
         <v>44</v>
@@ -31989,8 +34917,14 @@
       <c r="D490" t="s">
         <v>608</v>
       </c>
+      <c r="E490">
+        <v>0</v>
+      </c>
       <c r="F490" t="s">
         <v>612</v>
+      </c>
+      <c r="G490">
+        <v>0</v>
       </c>
       <c r="H490" t="s">
         <v>44</v>
@@ -32048,8 +34982,14 @@
       <c r="D491" t="s">
         <v>608</v>
       </c>
+      <c r="E491">
+        <v>0</v>
+      </c>
       <c r="F491" t="s">
         <v>614</v>
+      </c>
+      <c r="G491">
+        <v>0</v>
       </c>
       <c r="H491" t="s">
         <v>44</v>
@@ -32107,8 +35047,14 @@
       <c r="D492" t="s">
         <v>608</v>
       </c>
+      <c r="E492">
+        <v>0</v>
+      </c>
       <c r="F492" t="s">
         <v>616</v>
+      </c>
+      <c r="G492">
+        <v>0</v>
       </c>
       <c r="H492" t="s">
         <v>44</v>
@@ -32166,8 +35112,14 @@
       <c r="D493" t="s">
         <v>608</v>
       </c>
+      <c r="E493">
+        <v>0</v>
+      </c>
       <c r="F493" t="s">
         <v>618</v>
+      </c>
+      <c r="G493">
+        <v>0</v>
       </c>
       <c r="H493" t="s">
         <v>44</v>
@@ -32225,8 +35177,14 @@
       <c r="D494" t="s">
         <v>608</v>
       </c>
+      <c r="E494">
+        <v>0</v>
+      </c>
       <c r="F494" t="s">
         <v>620</v>
+      </c>
+      <c r="G494">
+        <v>0</v>
       </c>
       <c r="H494" t="s">
         <v>44</v>
@@ -32284,8 +35242,14 @@
       <c r="D495" t="s">
         <v>608</v>
       </c>
+      <c r="E495">
+        <v>0</v>
+      </c>
       <c r="F495" t="s">
         <v>622</v>
+      </c>
+      <c r="G495">
+        <v>0</v>
       </c>
       <c r="H495" t="s">
         <v>44</v>
@@ -32343,8 +35307,14 @@
       <c r="D496" t="s">
         <v>608</v>
       </c>
+      <c r="E496">
+        <v>0</v>
+      </c>
       <c r="F496" t="s">
         <v>624</v>
+      </c>
+      <c r="G496">
+        <v>0</v>
       </c>
       <c r="H496" t="s">
         <v>44</v>
@@ -32402,8 +35372,14 @@
       <c r="D497" t="s">
         <v>601</v>
       </c>
+      <c r="E497">
+        <v>0</v>
+      </c>
       <c r="F497" t="s">
         <v>626</v>
+      </c>
+      <c r="G497">
+        <v>1</v>
       </c>
       <c r="H497" t="s">
         <v>408</v>
@@ -32461,8 +35437,14 @@
       <c r="D498" t="s">
         <v>601</v>
       </c>
+      <c r="E498">
+        <v>0</v>
+      </c>
       <c r="F498" t="s">
         <v>626</v>
+      </c>
+      <c r="G498">
+        <v>1</v>
       </c>
       <c r="H498" t="s">
         <v>408</v>
@@ -32520,8 +35502,14 @@
       <c r="D499" t="s">
         <v>601</v>
       </c>
+      <c r="E499">
+        <v>0</v>
+      </c>
       <c r="F499" t="s">
         <v>626</v>
+      </c>
+      <c r="G499">
+        <v>1</v>
       </c>
       <c r="H499" t="s">
         <v>207</v>
@@ -32579,8 +35567,14 @@
       <c r="D500" t="s">
         <v>601</v>
       </c>
+      <c r="E500">
+        <v>0</v>
+      </c>
       <c r="F500" t="s">
         <v>626</v>
+      </c>
+      <c r="G500">
+        <v>1</v>
       </c>
       <c r="H500" t="s">
         <v>207</v>
@@ -32638,8 +35632,14 @@
       <c r="D501" t="s">
         <v>601</v>
       </c>
+      <c r="E501">
+        <v>0</v>
+      </c>
       <c r="F501" t="s">
         <v>626</v>
+      </c>
+      <c r="G501">
+        <v>1</v>
       </c>
       <c r="H501" t="s">
         <v>166</v>
@@ -32697,8 +35697,14 @@
       <c r="D502" t="s">
         <v>631</v>
       </c>
+      <c r="E502">
+        <v>0</v>
+      </c>
       <c r="F502" t="s">
         <v>632</v>
+      </c>
+      <c r="G502">
+        <v>1</v>
       </c>
       <c r="H502" t="s">
         <v>44</v>
@@ -32756,8 +35762,14 @@
       <c r="D503" t="s">
         <v>631</v>
       </c>
+      <c r="E503">
+        <v>0</v>
+      </c>
       <c r="F503" t="s">
         <v>632</v>
+      </c>
+      <c r="G503">
+        <v>1</v>
       </c>
       <c r="H503" t="s">
         <v>44</v>
@@ -32815,8 +35827,14 @@
       <c r="D504" t="s">
         <v>631</v>
       </c>
+      <c r="E504">
+        <v>0</v>
+      </c>
       <c r="F504" t="s">
         <v>632</v>
+      </c>
+      <c r="G504">
+        <v>1</v>
       </c>
       <c r="H504" t="s">
         <v>44</v>
@@ -32874,8 +35892,14 @@
       <c r="D505" t="s">
         <v>631</v>
       </c>
+      <c r="E505">
+        <v>0</v>
+      </c>
       <c r="F505" t="s">
         <v>632</v>
+      </c>
+      <c r="G505">
+        <v>1</v>
       </c>
       <c r="H505" t="s">
         <v>44</v>
@@ -32933,8 +35957,14 @@
       <c r="D506" t="s">
         <v>639</v>
       </c>
+      <c r="E506">
+        <v>0</v>
+      </c>
       <c r="F506" t="s">
         <v>640</v>
+      </c>
+      <c r="G506">
+        <v>1</v>
       </c>
       <c r="H506" t="s">
         <v>641</v>
@@ -32992,8 +36022,14 @@
       <c r="D507" t="s">
         <v>646</v>
       </c>
+      <c r="E507">
+        <v>0</v>
+      </c>
       <c r="F507" t="s">
         <v>647</v>
+      </c>
+      <c r="G507">
+        <v>1</v>
       </c>
       <c r="H507" t="s">
         <v>648</v>
@@ -33051,8 +36087,14 @@
       <c r="D508" t="s">
         <v>646</v>
       </c>
+      <c r="E508">
+        <v>0</v>
+      </c>
       <c r="F508" t="s">
         <v>652</v>
+      </c>
+      <c r="G508">
+        <v>0</v>
       </c>
       <c r="H508" t="s">
         <v>648</v>
@@ -33110,8 +36152,14 @@
       <c r="D509" t="s">
         <v>646</v>
       </c>
+      <c r="E509">
+        <v>0</v>
+      </c>
       <c r="F509" t="s">
         <v>654</v>
+      </c>
+      <c r="G509">
+        <v>0</v>
       </c>
       <c r="H509" t="s">
         <v>648</v>
@@ -33169,8 +36217,14 @@
       <c r="D510" t="s">
         <v>656</v>
       </c>
+      <c r="E510">
+        <v>0</v>
+      </c>
       <c r="F510" t="s">
         <v>647</v>
+      </c>
+      <c r="G510">
+        <v>1</v>
       </c>
       <c r="H510" t="s">
         <v>648</v>
@@ -33228,8 +36282,14 @@
       <c r="D511" t="s">
         <v>656</v>
       </c>
+      <c r="E511">
+        <v>0</v>
+      </c>
       <c r="F511" t="s">
         <v>652</v>
+      </c>
+      <c r="G511">
+        <v>0</v>
       </c>
       <c r="H511" t="s">
         <v>648</v>
@@ -33287,8 +36347,14 @@
       <c r="D512" t="s">
         <v>656</v>
       </c>
+      <c r="E512">
+        <v>0</v>
+      </c>
       <c r="F512" t="s">
         <v>654</v>
+      </c>
+      <c r="G512">
+        <v>0</v>
       </c>
       <c r="H512" t="s">
         <v>648</v>
@@ -33346,8 +36412,14 @@
       <c r="D513" t="s">
         <v>660</v>
       </c>
+      <c r="E513">
+        <v>0</v>
+      </c>
       <c r="F513" t="s">
         <v>647</v>
+      </c>
+      <c r="G513">
+        <v>1</v>
       </c>
       <c r="H513" t="s">
         <v>648</v>
@@ -33405,8 +36477,14 @@
       <c r="D514" t="s">
         <v>660</v>
       </c>
+      <c r="E514">
+        <v>0</v>
+      </c>
       <c r="F514" t="s">
         <v>652</v>
+      </c>
+      <c r="G514">
+        <v>0</v>
       </c>
       <c r="H514" t="s">
         <v>648</v>
@@ -33464,8 +36542,14 @@
       <c r="D515" t="s">
         <v>660</v>
       </c>
+      <c r="E515">
+        <v>0</v>
+      </c>
       <c r="F515" t="s">
         <v>654</v>
+      </c>
+      <c r="G515">
+        <v>0</v>
       </c>
       <c r="H515" t="s">
         <v>648</v>
@@ -33523,8 +36607,14 @@
       <c r="D516" t="s">
         <v>646</v>
       </c>
+      <c r="E516">
+        <v>0</v>
+      </c>
       <c r="F516" t="s">
         <v>647</v>
+      </c>
+      <c r="G516">
+        <v>1</v>
       </c>
       <c r="H516" t="s">
         <v>98</v>
@@ -33582,8 +36672,14 @@
       <c r="D517" t="s">
         <v>646</v>
       </c>
+      <c r="E517">
+        <v>0</v>
+      </c>
       <c r="F517" t="s">
         <v>652</v>
+      </c>
+      <c r="G517">
+        <v>0</v>
       </c>
       <c r="H517" t="s">
         <v>98</v>
@@ -33641,8 +36737,14 @@
       <c r="D518" t="s">
         <v>646</v>
       </c>
+      <c r="E518">
+        <v>0</v>
+      </c>
       <c r="F518" t="s">
         <v>652</v>
+      </c>
+      <c r="G518">
+        <v>0</v>
       </c>
       <c r="H518" t="s">
         <v>228</v>
@@ -33700,8 +36802,14 @@
       <c r="D519" t="s">
         <v>646</v>
       </c>
+      <c r="E519">
+        <v>0</v>
+      </c>
       <c r="F519" t="s">
         <v>652</v>
+      </c>
+      <c r="G519">
+        <v>0</v>
       </c>
       <c r="H519" t="s">
         <v>228</v>
@@ -33759,8 +36867,14 @@
       <c r="D520" t="s">
         <v>665</v>
       </c>
+      <c r="E520">
+        <v>0</v>
+      </c>
       <c r="F520" t="s">
         <v>652</v>
+      </c>
+      <c r="G520">
+        <v>0</v>
       </c>
       <c r="H520" t="s">
         <v>666</v>
@@ -33818,8 +36932,14 @@
       <c r="D521" t="s">
         <v>665</v>
       </c>
+      <c r="E521">
+        <v>0</v>
+      </c>
       <c r="F521" t="s">
         <v>647</v>
+      </c>
+      <c r="G521">
+        <v>1</v>
       </c>
       <c r="H521" t="s">
         <v>666</v>
@@ -33877,8 +36997,14 @@
       <c r="D522" t="s">
         <v>646</v>
       </c>
+      <c r="E522">
+        <v>0</v>
+      </c>
       <c r="F522" t="s">
         <v>647</v>
+      </c>
+      <c r="G522">
+        <v>1</v>
       </c>
       <c r="H522" t="s">
         <v>666</v>
@@ -33936,8 +37062,14 @@
       <c r="D523" t="s">
         <v>646</v>
       </c>
+      <c r="E523">
+        <v>0</v>
+      </c>
       <c r="F523" t="s">
         <v>652</v>
+      </c>
+      <c r="G523">
+        <v>0</v>
       </c>
       <c r="H523" t="s">
         <v>666</v>
@@ -33995,8 +37127,14 @@
       <c r="D524" t="s">
         <v>646</v>
       </c>
+      <c r="E524">
+        <v>0</v>
+      </c>
       <c r="F524" t="s">
         <v>654</v>
+      </c>
+      <c r="G524">
+        <v>0</v>
       </c>
       <c r="H524" t="s">
         <v>666</v>
@@ -34054,8 +37192,14 @@
       <c r="D525" t="s">
         <v>665</v>
       </c>
+      <c r="E525">
+        <v>0</v>
+      </c>
       <c r="F525" t="s">
         <v>654</v>
+      </c>
+      <c r="G525">
+        <v>0</v>
       </c>
       <c r="H525" t="s">
         <v>666</v>
@@ -34113,8 +37257,14 @@
       <c r="D526" t="s">
         <v>665</v>
       </c>
+      <c r="E526">
+        <v>0</v>
+      </c>
       <c r="F526" t="s">
         <v>652</v>
+      </c>
+      <c r="G526">
+        <v>0</v>
       </c>
       <c r="H526" t="s">
         <v>670</v>
@@ -34172,8 +37322,14 @@
       <c r="D527" t="s">
         <v>665</v>
       </c>
+      <c r="E527">
+        <v>0</v>
+      </c>
       <c r="F527" t="s">
         <v>647</v>
+      </c>
+      <c r="G527">
+        <v>1</v>
       </c>
       <c r="H527" t="s">
         <v>670</v>
@@ -34231,8 +37387,14 @@
       <c r="D528" t="s">
         <v>673</v>
       </c>
+      <c r="E528">
+        <v>0</v>
+      </c>
       <c r="F528" t="s">
         <v>647</v>
+      </c>
+      <c r="G528">
+        <v>1</v>
       </c>
       <c r="H528" t="s">
         <v>670</v>
@@ -34290,8 +37452,14 @@
       <c r="D529" t="s">
         <v>673</v>
       </c>
+      <c r="E529">
+        <v>0</v>
+      </c>
       <c r="F529" t="s">
         <v>652</v>
+      </c>
+      <c r="G529">
+        <v>0</v>
       </c>
       <c r="H529" t="s">
         <v>670</v>
@@ -34349,8 +37517,14 @@
       <c r="D530" t="s">
         <v>646</v>
       </c>
+      <c r="E530">
+        <v>0</v>
+      </c>
       <c r="F530" t="s">
         <v>647</v>
+      </c>
+      <c r="G530">
+        <v>1</v>
       </c>
       <c r="H530" t="s">
         <v>670</v>
@@ -34408,8 +37582,14 @@
       <c r="D531" t="s">
         <v>646</v>
       </c>
+      <c r="E531">
+        <v>0</v>
+      </c>
       <c r="F531" t="s">
         <v>652</v>
+      </c>
+      <c r="G531">
+        <v>0</v>
       </c>
       <c r="H531" t="s">
         <v>670</v>
@@ -34467,8 +37647,14 @@
       <c r="D532" t="s">
         <v>646</v>
       </c>
+      <c r="E532">
+        <v>0</v>
+      </c>
       <c r="F532" t="s">
         <v>654</v>
+      </c>
+      <c r="G532">
+        <v>0</v>
       </c>
       <c r="H532" t="s">
         <v>670</v>
@@ -34526,8 +37712,14 @@
       <c r="D533" t="s">
         <v>673</v>
       </c>
+      <c r="E533">
+        <v>0</v>
+      </c>
       <c r="F533" t="s">
         <v>654</v>
+      </c>
+      <c r="G533">
+        <v>0</v>
       </c>
       <c r="H533" t="s">
         <v>670</v>
@@ -34585,8 +37777,14 @@
       <c r="D534" t="s">
         <v>665</v>
       </c>
+      <c r="E534">
+        <v>0</v>
+      </c>
       <c r="F534" t="s">
         <v>654</v>
+      </c>
+      <c r="G534">
+        <v>0</v>
       </c>
       <c r="H534" t="s">
         <v>670</v>
@@ -34644,8 +37842,14 @@
       <c r="D535" t="s">
         <v>656</v>
       </c>
+      <c r="E535">
+        <v>0</v>
+      </c>
       <c r="F535" t="s">
         <v>647</v>
+      </c>
+      <c r="G535">
+        <v>1</v>
       </c>
       <c r="H535" t="s">
         <v>670</v>
@@ -34703,8 +37907,14 @@
       <c r="D536" t="s">
         <v>656</v>
       </c>
+      <c r="E536">
+        <v>0</v>
+      </c>
       <c r="F536" t="s">
         <v>652</v>
+      </c>
+      <c r="G536">
+        <v>0</v>
       </c>
       <c r="H536" t="s">
         <v>670</v>
@@ -34762,8 +37972,14 @@
       <c r="D537" t="s">
         <v>656</v>
       </c>
+      <c r="E537">
+        <v>0</v>
+      </c>
       <c r="F537" t="s">
         <v>654</v>
+      </c>
+      <c r="G537">
+        <v>0</v>
       </c>
       <c r="H537" t="s">
         <v>670</v>
@@ -34821,8 +38037,14 @@
       <c r="D538" t="s">
         <v>665</v>
       </c>
+      <c r="E538">
+        <v>0</v>
+      </c>
       <c r="F538" t="s">
         <v>652</v>
+      </c>
+      <c r="G538">
+        <v>0</v>
       </c>
       <c r="H538" t="s">
         <v>676</v>
@@ -34880,8 +38102,14 @@
       <c r="D539" t="s">
         <v>665</v>
       </c>
+      <c r="E539">
+        <v>0</v>
+      </c>
       <c r="F539" t="s">
         <v>647</v>
+      </c>
+      <c r="G539">
+        <v>1</v>
       </c>
       <c r="H539" t="s">
         <v>676</v>
@@ -34939,8 +38167,14 @@
       <c r="D540" t="s">
         <v>646</v>
       </c>
+      <c r="E540">
+        <v>0</v>
+      </c>
       <c r="F540" t="s">
         <v>647</v>
+      </c>
+      <c r="G540">
+        <v>1</v>
       </c>
       <c r="H540" t="s">
         <v>676</v>
@@ -34998,8 +38232,14 @@
       <c r="D541" t="s">
         <v>646</v>
       </c>
+      <c r="E541">
+        <v>0</v>
+      </c>
       <c r="F541" t="s">
         <v>652</v>
+      </c>
+      <c r="G541">
+        <v>0</v>
       </c>
       <c r="H541" t="s">
         <v>676</v>
@@ -35057,8 +38297,14 @@
       <c r="D542" t="s">
         <v>673</v>
       </c>
+      <c r="E542">
+        <v>0</v>
+      </c>
       <c r="F542" t="s">
         <v>647</v>
+      </c>
+      <c r="G542">
+        <v>1</v>
       </c>
       <c r="H542" t="s">
         <v>112</v>
@@ -35116,8 +38362,14 @@
       <c r="D543" t="s">
         <v>673</v>
       </c>
+      <c r="E543">
+        <v>0</v>
+      </c>
       <c r="F543" t="s">
         <v>652</v>
+      </c>
+      <c r="G543">
+        <v>0</v>
       </c>
       <c r="H543" t="s">
         <v>112</v>
@@ -35175,8 +38427,14 @@
       <c r="D544" t="s">
         <v>665</v>
       </c>
+      <c r="E544">
+        <v>0</v>
+      </c>
       <c r="F544" t="s">
         <v>652</v>
+      </c>
+      <c r="G544">
+        <v>0</v>
       </c>
       <c r="H544" t="s">
         <v>98</v>
@@ -35234,8 +38492,14 @@
       <c r="D545" t="s">
         <v>665</v>
       </c>
+      <c r="E545">
+        <v>0</v>
+      </c>
       <c r="F545" t="s">
         <v>647</v>
+      </c>
+      <c r="G545">
+        <v>1</v>
       </c>
       <c r="H545" t="s">
         <v>98</v>
@@ -35293,8 +38557,14 @@
       <c r="D546" t="s">
         <v>673</v>
       </c>
+      <c r="E546">
+        <v>0</v>
+      </c>
       <c r="F546" t="s">
         <v>647</v>
+      </c>
+      <c r="G546">
+        <v>1</v>
       </c>
       <c r="H546" t="s">
         <v>98</v>
@@ -35352,8 +38622,14 @@
       <c r="D547" t="s">
         <v>673</v>
       </c>
+      <c r="E547">
+        <v>0</v>
+      </c>
       <c r="F547" t="s">
         <v>652</v>
+      </c>
+      <c r="G547">
+        <v>0</v>
       </c>
       <c r="H547" t="s">
         <v>98</v>
@@ -35411,8 +38687,14 @@
       <c r="D548" t="s">
         <v>673</v>
       </c>
+      <c r="E548">
+        <v>0</v>
+      </c>
       <c r="F548" t="s">
         <v>654</v>
+      </c>
+      <c r="G548">
+        <v>0</v>
       </c>
       <c r="H548" t="s">
         <v>98</v>
@@ -35470,8 +38752,14 @@
       <c r="D549" t="s">
         <v>665</v>
       </c>
+      <c r="E549">
+        <v>0</v>
+      </c>
       <c r="F549" t="s">
         <v>654</v>
+      </c>
+      <c r="G549">
+        <v>0</v>
       </c>
       <c r="H549" t="s">
         <v>98</v>
@@ -35529,8 +38817,14 @@
       <c r="D550" t="s">
         <v>665</v>
       </c>
+      <c r="E550">
+        <v>0</v>
+      </c>
       <c r="F550" t="s">
         <v>652</v>
+      </c>
+      <c r="G550">
+        <v>0</v>
       </c>
       <c r="H550" t="s">
         <v>680</v>
@@ -35588,8 +38882,14 @@
       <c r="D551" t="s">
         <v>665</v>
       </c>
+      <c r="E551">
+        <v>0</v>
+      </c>
       <c r="F551" t="s">
         <v>647</v>
+      </c>
+      <c r="G551">
+        <v>1</v>
       </c>
       <c r="H551" t="s">
         <v>680</v>
@@ -35647,8 +38947,14 @@
       <c r="D552" t="s">
         <v>673</v>
       </c>
+      <c r="E552">
+        <v>0</v>
+      </c>
       <c r="F552" t="s">
         <v>647</v>
+      </c>
+      <c r="G552">
+        <v>1</v>
       </c>
       <c r="H552" t="s">
         <v>680</v>
@@ -35706,8 +39012,14 @@
       <c r="D553" t="s">
         <v>673</v>
       </c>
+      <c r="E553">
+        <v>0</v>
+      </c>
       <c r="F553" t="s">
         <v>652</v>
+      </c>
+      <c r="G553">
+        <v>0</v>
       </c>
       <c r="H553" t="s">
         <v>680</v>
@@ -35765,8 +39077,14 @@
       <c r="D554" t="s">
         <v>673</v>
       </c>
+      <c r="E554">
+        <v>0</v>
+      </c>
       <c r="F554" t="s">
         <v>654</v>
+      </c>
+      <c r="G554">
+        <v>0</v>
       </c>
       <c r="H554" t="s">
         <v>680</v>
@@ -35824,8 +39142,14 @@
       <c r="D555" t="s">
         <v>665</v>
       </c>
+      <c r="E555">
+        <v>0</v>
+      </c>
       <c r="F555" t="s">
         <v>654</v>
+      </c>
+      <c r="G555">
+        <v>0</v>
       </c>
       <c r="H555" t="s">
         <v>680</v>
@@ -35883,8 +39207,14 @@
       <c r="D556" t="s">
         <v>673</v>
       </c>
+      <c r="E556">
+        <v>0</v>
+      </c>
       <c r="F556" t="s">
         <v>652</v>
+      </c>
+      <c r="G556">
+        <v>0</v>
       </c>
       <c r="H556" t="s">
         <v>306</v>
@@ -35942,8 +39272,14 @@
       <c r="D557" t="s">
         <v>665</v>
       </c>
+      <c r="E557">
+        <v>0</v>
+      </c>
       <c r="F557" t="s">
         <v>652</v>
+      </c>
+      <c r="G557">
+        <v>0</v>
       </c>
       <c r="H557" t="s">
         <v>44</v>
@@ -36001,8 +39337,14 @@
       <c r="D558" t="s">
         <v>665</v>
       </c>
+      <c r="E558">
+        <v>0</v>
+      </c>
       <c r="F558" t="s">
         <v>647</v>
+      </c>
+      <c r="G558">
+        <v>1</v>
       </c>
       <c r="H558" t="s">
         <v>44</v>
@@ -36060,8 +39402,14 @@
       <c r="D559" t="s">
         <v>665</v>
       </c>
+      <c r="E559">
+        <v>0</v>
+      </c>
       <c r="F559" t="s">
         <v>652</v>
+      </c>
+      <c r="G559">
+        <v>0</v>
       </c>
       <c r="H559" t="s">
         <v>408</v>
@@ -36119,8 +39467,14 @@
       <c r="D560" t="s">
         <v>665</v>
       </c>
+      <c r="E560">
+        <v>0</v>
+      </c>
       <c r="F560" t="s">
         <v>647</v>
+      </c>
+      <c r="G560">
+        <v>1</v>
       </c>
       <c r="H560" t="s">
         <v>408</v>
@@ -36178,8 +39532,14 @@
       <c r="D561" t="s">
         <v>665</v>
       </c>
+      <c r="E561">
+        <v>0</v>
+      </c>
       <c r="F561" t="s">
         <v>652</v>
+      </c>
+      <c r="G561">
+        <v>0</v>
       </c>
       <c r="H561" t="s">
         <v>685</v>
@@ -36237,8 +39597,14 @@
       <c r="D562" t="s">
         <v>665</v>
       </c>
+      <c r="E562">
+        <v>0</v>
+      </c>
       <c r="F562" t="s">
         <v>652</v>
+      </c>
+      <c r="G562">
+        <v>0</v>
       </c>
       <c r="H562" t="s">
         <v>687</v>
@@ -36296,8 +39662,14 @@
       <c r="D563" t="s">
         <v>665</v>
       </c>
+      <c r="E563">
+        <v>0</v>
+      </c>
       <c r="F563" t="s">
         <v>647</v>
+      </c>
+      <c r="G563">
+        <v>1</v>
       </c>
       <c r="H563" t="s">
         <v>685</v>
@@ -36355,8 +39727,14 @@
       <c r="D564" t="s">
         <v>665</v>
       </c>
+      <c r="E564">
+        <v>0</v>
+      </c>
       <c r="F564" t="s">
         <v>647</v>
+      </c>
+      <c r="G564">
+        <v>1</v>
       </c>
       <c r="H564" t="s">
         <v>687</v>
@@ -36414,8 +39792,14 @@
       <c r="D565" t="s">
         <v>665</v>
       </c>
+      <c r="E565">
+        <v>0</v>
+      </c>
       <c r="F565" t="s">
         <v>652</v>
+      </c>
+      <c r="G565">
+        <v>0</v>
       </c>
       <c r="H565" t="s">
         <v>689</v>
@@ -36473,8 +39857,14 @@
       <c r="D566" t="s">
         <v>665</v>
       </c>
+      <c r="E566">
+        <v>0</v>
+      </c>
       <c r="F566" t="s">
         <v>647</v>
+      </c>
+      <c r="G566">
+        <v>1</v>
       </c>
       <c r="H566" t="s">
         <v>689</v>
@@ -36532,8 +39922,14 @@
       <c r="D567" t="s">
         <v>665</v>
       </c>
+      <c r="E567">
+        <v>0</v>
+      </c>
       <c r="F567" t="s">
         <v>652</v>
+      </c>
+      <c r="G567">
+        <v>0</v>
       </c>
       <c r="H567" t="s">
         <v>44</v>
@@ -36591,8 +39987,14 @@
       <c r="D568" t="s">
         <v>665</v>
       </c>
+      <c r="E568">
+        <v>0</v>
+      </c>
       <c r="F568" t="s">
         <v>652</v>
+      </c>
+      <c r="G568">
+        <v>0</v>
       </c>
       <c r="H568" t="s">
         <v>685</v>
@@ -36650,8 +40052,14 @@
       <c r="D569" t="s">
         <v>665</v>
       </c>
+      <c r="E569">
+        <v>0</v>
+      </c>
       <c r="F569" t="s">
         <v>652</v>
+      </c>
+      <c r="G569">
+        <v>0</v>
       </c>
       <c r="H569" t="s">
         <v>693</v>
@@ -36709,8 +40117,14 @@
       <c r="D570" t="s">
         <v>665</v>
       </c>
+      <c r="E570">
+        <v>0</v>
+      </c>
       <c r="F570" t="s">
         <v>652</v>
+      </c>
+      <c r="G570">
+        <v>0</v>
       </c>
       <c r="H570" t="s">
         <v>694</v>
@@ -36768,8 +40182,14 @@
       <c r="D571" t="s">
         <v>665</v>
       </c>
+      <c r="E571">
+        <v>0</v>
+      </c>
       <c r="F571" t="s">
         <v>652</v>
+      </c>
+      <c r="G571">
+        <v>0</v>
       </c>
       <c r="H571" t="s">
         <v>687</v>
@@ -36827,8 +40247,14 @@
       <c r="D572" t="s">
         <v>665</v>
       </c>
+      <c r="E572">
+        <v>0</v>
+      </c>
       <c r="F572" t="s">
         <v>652</v>
+      </c>
+      <c r="G572">
+        <v>0</v>
       </c>
       <c r="H572" t="s">
         <v>391</v>
@@ -36886,8 +40312,14 @@
       <c r="D573" t="s">
         <v>665</v>
       </c>
+      <c r="E573">
+        <v>0</v>
+      </c>
       <c r="F573" t="s">
         <v>652</v>
+      </c>
+      <c r="G573">
+        <v>0</v>
       </c>
       <c r="H573" t="s">
         <v>57</v>
@@ -36945,8 +40377,14 @@
       <c r="D574" t="s">
         <v>665</v>
       </c>
+      <c r="E574">
+        <v>0</v>
+      </c>
       <c r="F574" t="s">
         <v>652</v>
+      </c>
+      <c r="G574">
+        <v>0</v>
       </c>
       <c r="H574" t="s">
         <v>698</v>
@@ -37004,8 +40442,14 @@
       <c r="D575" t="s">
         <v>665</v>
       </c>
+      <c r="E575">
+        <v>0</v>
+      </c>
       <c r="F575" t="s">
         <v>652</v>
+      </c>
+      <c r="G575">
+        <v>0</v>
       </c>
       <c r="H575" t="s">
         <v>685</v>
@@ -37063,8 +40507,14 @@
       <c r="D576" t="s">
         <v>665</v>
       </c>
+      <c r="E576">
+        <v>0</v>
+      </c>
       <c r="F576" t="s">
         <v>652</v>
+      </c>
+      <c r="G576">
+        <v>0</v>
       </c>
       <c r="H576" t="s">
         <v>161</v>
@@ -37122,8 +40572,14 @@
       <c r="D577" t="s">
         <v>665</v>
       </c>
+      <c r="E577">
+        <v>0</v>
+      </c>
       <c r="F577" t="s">
         <v>652</v>
+      </c>
+      <c r="G577">
+        <v>0</v>
       </c>
       <c r="H577" t="s">
         <v>694</v>
@@ -37181,8 +40637,14 @@
       <c r="D578" t="s">
         <v>665</v>
       </c>
+      <c r="E578">
+        <v>0</v>
+      </c>
       <c r="F578" t="s">
         <v>652</v>
+      </c>
+      <c r="G578">
+        <v>0</v>
       </c>
       <c r="H578" t="s">
         <v>689</v>
@@ -37240,8 +40702,14 @@
       <c r="D579" t="s">
         <v>665</v>
       </c>
+      <c r="E579">
+        <v>0</v>
+      </c>
       <c r="F579" t="s">
         <v>652</v>
+      </c>
+      <c r="G579">
+        <v>0</v>
       </c>
       <c r="H579" t="s">
         <v>209</v>
@@ -37299,8 +40767,14 @@
       <c r="D580" t="s">
         <v>665</v>
       </c>
+      <c r="E580">
+        <v>0</v>
+      </c>
       <c r="F580" t="s">
         <v>652</v>
+      </c>
+      <c r="G580">
+        <v>0</v>
       </c>
       <c r="H580" t="s">
         <v>703</v>
@@ -37358,8 +40832,14 @@
       <c r="D581" t="s">
         <v>665</v>
       </c>
+      <c r="E581">
+        <v>0</v>
+      </c>
       <c r="F581" t="s">
         <v>652</v>
+      </c>
+      <c r="G581">
+        <v>0</v>
       </c>
       <c r="H581" t="s">
         <v>98</v>
@@ -37417,8 +40897,14 @@
       <c r="D582" t="s">
         <v>665</v>
       </c>
+      <c r="E582">
+        <v>0</v>
+      </c>
       <c r="F582" t="s">
         <v>652</v>
+      </c>
+      <c r="G582">
+        <v>0</v>
       </c>
       <c r="H582" t="s">
         <v>687</v>
@@ -37476,8 +40962,14 @@
       <c r="D583" t="s">
         <v>665</v>
       </c>
+      <c r="E583">
+        <v>0</v>
+      </c>
       <c r="F583" t="s">
         <v>652</v>
+      </c>
+      <c r="G583">
+        <v>0</v>
       </c>
       <c r="H583" t="s">
         <v>685</v>
@@ -37535,8 +41027,14 @@
       <c r="D584" t="s">
         <v>665</v>
       </c>
+      <c r="E584">
+        <v>0</v>
+      </c>
       <c r="F584" t="s">
         <v>652</v>
+      </c>
+      <c r="G584">
+        <v>0</v>
       </c>
       <c r="H584" t="s">
         <v>707</v>
@@ -37594,8 +41092,14 @@
       <c r="D585" t="s">
         <v>665</v>
       </c>
+      <c r="E585">
+        <v>0</v>
+      </c>
       <c r="F585" t="s">
         <v>652</v>
+      </c>
+      <c r="G585">
+        <v>0</v>
       </c>
       <c r="H585" t="s">
         <v>707</v>
@@ -37653,8 +41157,14 @@
       <c r="D586" t="s">
         <v>665</v>
       </c>
+      <c r="E586">
+        <v>0</v>
+      </c>
       <c r="F586" t="s">
         <v>647</v>
+      </c>
+      <c r="G586">
+        <v>1</v>
       </c>
       <c r="H586" t="s">
         <v>707</v>
@@ -37712,8 +41222,14 @@
       <c r="D587" t="s">
         <v>673</v>
       </c>
+      <c r="E587">
+        <v>0</v>
+      </c>
       <c r="F587" t="s">
         <v>652</v>
+      </c>
+      <c r="G587">
+        <v>0</v>
       </c>
       <c r="H587" t="s">
         <v>707</v>
@@ -37771,8 +41287,14 @@
       <c r="D588" t="s">
         <v>665</v>
       </c>
+      <c r="E588">
+        <v>0</v>
+      </c>
       <c r="F588" t="s">
         <v>652</v>
+      </c>
+      <c r="G588">
+        <v>0</v>
       </c>
       <c r="H588" t="s">
         <v>63</v>
@@ -37830,8 +41352,14 @@
       <c r="D589" t="s">
         <v>665</v>
       </c>
+      <c r="E589">
+        <v>0</v>
+      </c>
       <c r="F589" t="s">
         <v>652</v>
+      </c>
+      <c r="G589">
+        <v>0</v>
       </c>
       <c r="H589" t="s">
         <v>710</v>
@@ -37889,8 +41417,14 @@
       <c r="D590" t="s">
         <v>665</v>
       </c>
+      <c r="E590">
+        <v>0</v>
+      </c>
       <c r="F590" t="s">
         <v>652</v>
+      </c>
+      <c r="G590">
+        <v>0</v>
       </c>
       <c r="H590" t="s">
         <v>712</v>
@@ -37948,8 +41482,14 @@
       <c r="D591" t="s">
         <v>665</v>
       </c>
+      <c r="E591">
+        <v>0</v>
+      </c>
       <c r="F591" t="s">
         <v>652</v>
+      </c>
+      <c r="G591">
+        <v>0</v>
       </c>
       <c r="H591" t="s">
         <v>713</v>
@@ -38007,8 +41547,14 @@
       <c r="D592" t="s">
         <v>665</v>
       </c>
+      <c r="E592">
+        <v>0</v>
+      </c>
       <c r="F592" t="s">
         <v>652</v>
+      </c>
+      <c r="G592">
+        <v>0</v>
       </c>
       <c r="H592" t="s">
         <v>714</v>
@@ -38066,8 +41612,14 @@
       <c r="D593" t="s">
         <v>665</v>
       </c>
+      <c r="E593">
+        <v>0</v>
+      </c>
       <c r="F593" t="s">
         <v>652</v>
+      </c>
+      <c r="G593">
+        <v>0</v>
       </c>
       <c r="H593" t="s">
         <v>715</v>
@@ -38125,8 +41677,14 @@
       <c r="D594" t="s">
         <v>665</v>
       </c>
+      <c r="E594">
+        <v>0</v>
+      </c>
       <c r="F594" t="s">
         <v>652</v>
+      </c>
+      <c r="G594">
+        <v>0</v>
       </c>
       <c r="H594" t="s">
         <v>98</v>
@@ -38184,8 +41742,14 @@
       <c r="D595" t="s">
         <v>646</v>
       </c>
+      <c r="E595">
+        <v>0</v>
+      </c>
       <c r="F595" t="s">
         <v>652</v>
+      </c>
+      <c r="G595">
+        <v>0</v>
       </c>
       <c r="H595" t="s">
         <v>717</v>
@@ -38243,8 +41807,14 @@
       <c r="D596" t="s">
         <v>721</v>
       </c>
+      <c r="E596">
+        <v>1</v>
+      </c>
       <c r="F596" t="s">
         <v>722</v>
+      </c>
+      <c r="G596">
+        <v>0</v>
       </c>
       <c r="H596" t="s">
         <v>723</v>
@@ -38302,8 +41872,14 @@
       <c r="D597" t="s">
         <v>727</v>
       </c>
+      <c r="E597">
+        <v>1</v>
+      </c>
       <c r="F597" t="s">
         <v>728</v>
+      </c>
+      <c r="G597">
+        <v>0</v>
       </c>
       <c r="H597" t="s">
         <v>729</v>
@@ -38361,8 +41937,14 @@
       <c r="D598" t="s">
         <v>727</v>
       </c>
+      <c r="E598">
+        <v>1</v>
+      </c>
       <c r="F598" t="s">
         <v>732</v>
+      </c>
+      <c r="G598">
+        <v>0</v>
       </c>
       <c r="H598" t="s">
         <v>729</v>
@@ -38420,8 +42002,14 @@
       <c r="D599" t="s">
         <v>727</v>
       </c>
+      <c r="E599">
+        <v>1</v>
+      </c>
       <c r="F599" t="s">
         <v>734</v>
+      </c>
+      <c r="G599">
+        <v>0</v>
       </c>
       <c r="H599" t="s">
         <v>729</v>
@@ -38479,8 +42067,14 @@
       <c r="D600" t="s">
         <v>727</v>
       </c>
+      <c r="E600">
+        <v>1</v>
+      </c>
       <c r="F600" t="s">
         <v>728</v>
+      </c>
+      <c r="G600">
+        <v>0</v>
       </c>
       <c r="H600" t="s">
         <v>285</v>
@@ -38538,8 +42132,14 @@
       <c r="D601" t="s">
         <v>727</v>
       </c>
+      <c r="E601">
+        <v>1</v>
+      </c>
       <c r="F601" t="s">
         <v>732</v>
+      </c>
+      <c r="G601">
+        <v>0</v>
       </c>
       <c r="H601" t="s">
         <v>285</v>
@@ -38597,8 +42197,14 @@
       <c r="D602" t="s">
         <v>727</v>
       </c>
+      <c r="E602">
+        <v>1</v>
+      </c>
       <c r="F602" t="s">
         <v>734</v>
+      </c>
+      <c r="G602">
+        <v>0</v>
       </c>
       <c r="H602" t="s">
         <v>285</v>

--- a/Data/senate_general_polls_2026.xlsx
+++ b/Data/senate_general_polls_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennyqu/Library/CloudStorage/OneDrive-WilfridLaurierUniversity/us_trade_conflict/us_trade_conflict/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{62722A5A-5EA5-9349-804C-AA0C9F34F560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8E9552C-D7FA-494C-B96F-4F98FD4EAC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5600" yWindow="1760" windowWidth="28040" windowHeight="16660" xr2:uid="{03306125-F0D3-F642-8A56-CAC244325849}"/>
+    <workbookView xWindow="2060" yWindow="1160" windowWidth="28040" windowHeight="16660" xr2:uid="{03306125-F0D3-F642-8A56-CAC244325849}"/>
   </bookViews>
   <sheets>
     <sheet name="senate_general_polls_2026" sheetId="1" r:id="rId1"/>
@@ -1557,12 +1557,6 @@
     <t>New Mexico</t>
   </si>
   <si>
-    <t>Ben Ray Luj√°n (D) vs Larry Marker (R)</t>
-  </si>
-  <si>
-    <t>Ben Ray Luj√°n</t>
-  </si>
-  <si>
     <t>Larry Marker</t>
   </si>
   <si>
@@ -2248,6 +2242,12 @@
   </si>
   <si>
     <t>rep_Incumbent</t>
+  </si>
+  <si>
+    <t>Ben Ray Luján</t>
+  </si>
+  <si>
+    <t>Ben Ray Luján (D) vs Larry Marker (R)</t>
   </si>
 </sst>
 </file>
@@ -3133,13 +3133,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -29647,28 +29647,28 @@
         <v>20</v>
       </c>
       <c r="C409" t="s">
+        <v>737</v>
+      </c>
+      <c r="D409" t="s">
+        <v>736</v>
+      </c>
+      <c r="E409">
+        <v>1</v>
+      </c>
+      <c r="F409" t="s">
         <v>507</v>
       </c>
-      <c r="D409" t="s">
+      <c r="G409">
+        <v>0</v>
+      </c>
+      <c r="H409" t="s">
         <v>508</v>
       </c>
-      <c r="E409">
-        <v>1</v>
-      </c>
-      <c r="F409" t="s">
+      <c r="I409" t="b">
+        <v>0</v>
+      </c>
+      <c r="J409" t="s">
         <v>509</v>
-      </c>
-      <c r="G409">
-        <v>0</v>
-      </c>
-      <c r="H409" t="s">
-        <v>510</v>
-      </c>
-      <c r="I409" t="b">
-        <v>0</v>
-      </c>
-      <c r="J409" t="s">
-        <v>511</v>
       </c>
       <c r="K409" s="1" t="d">
         <v>2026-08-28</v>
@@ -29701,39 +29701,39 @@
         <v>27</v>
       </c>
       <c r="U409" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="410" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
+        <v>511</v>
+      </c>
+      <c r="B410" t="s">
+        <v>20</v>
+      </c>
+      <c r="C410" t="s">
+        <v>512</v>
+      </c>
+      <c r="D410" t="s">
         <v>513</v>
       </c>
-      <c r="B410" t="s">
-        <v>20</v>
-      </c>
-      <c r="C410" t="s">
+      <c r="E410">
+        <v>0</v>
+      </c>
+      <c r="F410" t="s">
         <v>514</v>
       </c>
-      <c r="D410" t="s">
+      <c r="G410">
+        <v>1</v>
+      </c>
+      <c r="H410" t="s">
         <v>515</v>
       </c>
-      <c r="E410">
-        <v>0</v>
-      </c>
-      <c r="F410" t="s">
+      <c r="I410" t="b">
+        <v>1</v>
+      </c>
+      <c r="J410" t="s">
         <v>516</v>
-      </c>
-      <c r="G410">
-        <v>1</v>
-      </c>
-      <c r="H410" t="s">
-        <v>517</v>
-      </c>
-      <c r="I410" t="b">
-        <v>1</v>
-      </c>
-      <c r="J410" t="s">
-        <v>518</v>
       </c>
       <c r="K410" s="1" t="d">
         <v>2024-11-29</v>
@@ -29766,39 +29766,39 @@
         <v>27</v>
       </c>
       <c r="U410" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="411" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
+        <v>511</v>
+      </c>
+      <c r="B411" t="s">
+        <v>20</v>
+      </c>
+      <c r="C411" t="s">
+        <v>518</v>
+      </c>
+      <c r="D411" t="s">
         <v>513</v>
       </c>
-      <c r="B411" t="s">
-        <v>20</v>
-      </c>
-      <c r="C411" t="s">
-        <v>520</v>
-      </c>
-      <c r="D411" t="s">
+      <c r="E411">
+        <v>0</v>
+      </c>
+      <c r="F411" t="s">
+        <v>519</v>
+      </c>
+      <c r="G411">
+        <v>0</v>
+      </c>
+      <c r="H411" t="s">
         <v>515</v>
       </c>
-      <c r="E411">
-        <v>0</v>
-      </c>
-      <c r="F411" t="s">
-        <v>521</v>
-      </c>
-      <c r="G411">
-        <v>0</v>
-      </c>
-      <c r="H411" t="s">
-        <v>517</v>
-      </c>
       <c r="I411" t="b">
         <v>1</v>
       </c>
       <c r="J411" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K411" s="1" t="d">
         <v>2024-11-29</v>
@@ -29831,27 +29831,27 @@
         <v>27</v>
       </c>
       <c r="U411" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="412" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
+        <v>511</v>
+      </c>
+      <c r="B412" t="s">
+        <v>20</v>
+      </c>
+      <c r="C412" t="s">
+        <v>512</v>
+      </c>
+      <c r="D412" t="s">
         <v>513</v>
       </c>
-      <c r="B412" t="s">
-        <v>20</v>
-      </c>
-      <c r="C412" t="s">
+      <c r="E412">
+        <v>0</v>
+      </c>
+      <c r="F412" t="s">
         <v>514</v>
-      </c>
-      <c r="D412" t="s">
-        <v>515</v>
-      </c>
-      <c r="E412">
-        <v>0</v>
-      </c>
-      <c r="F412" t="s">
-        <v>516</v>
       </c>
       <c r="G412">
         <v>1</v>
@@ -29863,7 +29863,7 @@
         <v>1</v>
       </c>
       <c r="J412" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K412" s="1" t="d">
         <v>2025-03-05</v>
@@ -29896,27 +29896,27 @@
         <v>27</v>
       </c>
       <c r="U412" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="413" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
+        <v>511</v>
+      </c>
+      <c r="B413" t="s">
+        <v>20</v>
+      </c>
+      <c r="C413" t="s">
+        <v>512</v>
+      </c>
+      <c r="D413" t="s">
         <v>513</v>
       </c>
-      <c r="B413" t="s">
-        <v>20</v>
-      </c>
-      <c r="C413" t="s">
+      <c r="E413">
+        <v>0</v>
+      </c>
+      <c r="F413" t="s">
         <v>514</v>
-      </c>
-      <c r="D413" t="s">
-        <v>515</v>
-      </c>
-      <c r="E413">
-        <v>0</v>
-      </c>
-      <c r="F413" t="s">
-        <v>516</v>
       </c>
       <c r="G413">
         <v>1</v>
@@ -29928,7 +29928,7 @@
         <v>1</v>
       </c>
       <c r="J413" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K413" s="1" t="d">
         <v>2025-04-04</v>
@@ -29961,27 +29961,27 @@
         <v>27</v>
       </c>
       <c r="U413" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="414" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
+        <v>511</v>
+      </c>
+      <c r="B414" t="s">
+        <v>20</v>
+      </c>
+      <c r="C414" t="s">
+        <v>512</v>
+      </c>
+      <c r="D414" t="s">
         <v>513</v>
       </c>
-      <c r="B414" t="s">
-        <v>20</v>
-      </c>
-      <c r="C414" t="s">
+      <c r="E414">
+        <v>0</v>
+      </c>
+      <c r="F414" t="s">
         <v>514</v>
-      </c>
-      <c r="D414" t="s">
-        <v>515</v>
-      </c>
-      <c r="E414">
-        <v>0</v>
-      </c>
-      <c r="F414" t="s">
-        <v>516</v>
       </c>
       <c r="G414">
         <v>1</v>
@@ -29993,7 +29993,7 @@
         <v>1</v>
       </c>
       <c r="J414" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K414" s="1" t="d">
         <v>2025-04-04</v>
@@ -30026,27 +30026,27 @@
         <v>27</v>
       </c>
       <c r="U414" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="415" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B415" t="s">
         <v>20</v>
       </c>
       <c r="C415" t="s">
+        <v>522</v>
+      </c>
+      <c r="D415" t="s">
+        <v>523</v>
+      </c>
+      <c r="E415">
+        <v>0</v>
+      </c>
+      <c r="F415" t="s">
         <v>524</v>
-      </c>
-      <c r="D415" t="s">
-        <v>525</v>
-      </c>
-      <c r="E415">
-        <v>0</v>
-      </c>
-      <c r="F415" t="s">
-        <v>526</v>
       </c>
       <c r="G415">
         <v>0</v>
@@ -30058,7 +30058,7 @@
         <v>0</v>
       </c>
       <c r="J415" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K415" s="1" t="d">
         <v>2025-07-30</v>
@@ -30091,39 +30091,39 @@
         <v>27</v>
       </c>
       <c r="U415" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="416" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B416" t="s">
         <v>20</v>
       </c>
       <c r="C416" t="s">
+        <v>522</v>
+      </c>
+      <c r="D416" t="s">
+        <v>523</v>
+      </c>
+      <c r="E416">
+        <v>0</v>
+      </c>
+      <c r="F416" t="s">
         <v>524</v>
       </c>
-      <c r="D416" t="s">
+      <c r="G416">
+        <v>0</v>
+      </c>
+      <c r="H416" t="s">
+        <v>515</v>
+      </c>
+      <c r="I416" t="b">
+        <v>1</v>
+      </c>
+      <c r="J416" t="s">
         <v>525</v>
-      </c>
-      <c r="E416">
-        <v>0</v>
-      </c>
-      <c r="F416" t="s">
-        <v>526</v>
-      </c>
-      <c r="G416">
-        <v>0</v>
-      </c>
-      <c r="H416" t="s">
-        <v>517</v>
-      </c>
-      <c r="I416" t="b">
-        <v>1</v>
-      </c>
-      <c r="J416" t="s">
-        <v>527</v>
       </c>
       <c r="K416" s="1" t="d">
         <v>2025-07-30</v>
@@ -30156,39 +30156,39 @@
         <v>27</v>
       </c>
       <c r="U416" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="417" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B417" t="s">
         <v>20</v>
       </c>
       <c r="C417" t="s">
+        <v>522</v>
+      </c>
+      <c r="D417" t="s">
+        <v>523</v>
+      </c>
+      <c r="E417">
+        <v>0</v>
+      </c>
+      <c r="F417" t="s">
         <v>524</v>
       </c>
-      <c r="D417" t="s">
+      <c r="G417">
+        <v>0</v>
+      </c>
+      <c r="H417" t="s">
+        <v>515</v>
+      </c>
+      <c r="I417" t="b">
+        <v>1</v>
+      </c>
+      <c r="J417" t="s">
         <v>525</v>
-      </c>
-      <c r="E417">
-        <v>0</v>
-      </c>
-      <c r="F417" t="s">
-        <v>526</v>
-      </c>
-      <c r="G417">
-        <v>0</v>
-      </c>
-      <c r="H417" t="s">
-        <v>517</v>
-      </c>
-      <c r="I417" t="b">
-        <v>1</v>
-      </c>
-      <c r="J417" t="s">
-        <v>527</v>
       </c>
       <c r="K417" s="1" t="d">
         <v>2025-07-30</v>
@@ -30221,39 +30221,39 @@
         <v>27</v>
       </c>
       <c r="U417" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="418" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B418" t="s">
         <v>20</v>
       </c>
       <c r="C418" t="s">
+        <v>522</v>
+      </c>
+      <c r="D418" t="s">
+        <v>523</v>
+      </c>
+      <c r="E418">
+        <v>0</v>
+      </c>
+      <c r="F418" t="s">
         <v>524</v>
       </c>
-      <c r="D418" t="s">
-        <v>525</v>
-      </c>
-      <c r="E418">
-        <v>0</v>
-      </c>
-      <c r="F418" t="s">
+      <c r="G418">
+        <v>0</v>
+      </c>
+      <c r="H418" t="s">
         <v>526</v>
       </c>
-      <c r="G418">
-        <v>0</v>
-      </c>
-      <c r="H418" t="s">
-        <v>528</v>
-      </c>
       <c r="I418" t="b">
         <v>1</v>
       </c>
       <c r="J418" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K418" s="1" t="d">
         <v>2025-08-12</v>
@@ -30286,27 +30286,27 @@
         <v>27</v>
       </c>
       <c r="U418" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="419" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B419" t="s">
         <v>20</v>
       </c>
       <c r="C419" t="s">
+        <v>522</v>
+      </c>
+      <c r="D419" t="s">
+        <v>523</v>
+      </c>
+      <c r="E419">
+        <v>0</v>
+      </c>
+      <c r="F419" t="s">
         <v>524</v>
-      </c>
-      <c r="D419" t="s">
-        <v>525</v>
-      </c>
-      <c r="E419">
-        <v>0</v>
-      </c>
-      <c r="F419" t="s">
-        <v>526</v>
       </c>
       <c r="G419">
         <v>0</v>
@@ -30318,7 +30318,7 @@
         <v>1</v>
       </c>
       <c r="J419" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K419" s="1" t="d">
         <v>2025-09-08</v>
@@ -30351,39 +30351,39 @@
         <v>27</v>
       </c>
       <c r="U419" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="420" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B420" t="s">
         <v>20</v>
       </c>
       <c r="C420" t="s">
+        <v>522</v>
+      </c>
+      <c r="D420" t="s">
+        <v>523</v>
+      </c>
+      <c r="E420">
+        <v>0</v>
+      </c>
+      <c r="F420" t="s">
         <v>524</v>
       </c>
-      <c r="D420" t="s">
-        <v>525</v>
-      </c>
-      <c r="E420">
-        <v>0</v>
-      </c>
-      <c r="F420" t="s">
+      <c r="G420">
+        <v>0</v>
+      </c>
+      <c r="H420" t="s">
         <v>526</v>
       </c>
-      <c r="G420">
-        <v>0</v>
-      </c>
-      <c r="H420" t="s">
-        <v>528</v>
-      </c>
       <c r="I420" t="b">
         <v>1</v>
       </c>
       <c r="J420" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K420" s="1" t="d">
         <v>2025-09-15</v>
@@ -30416,39 +30416,39 @@
         <v>27</v>
       </c>
       <c r="U420" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="421" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B421" t="s">
         <v>20</v>
       </c>
       <c r="C421" t="s">
+        <v>522</v>
+      </c>
+      <c r="D421" t="s">
+        <v>523</v>
+      </c>
+      <c r="E421">
+        <v>0</v>
+      </c>
+      <c r="F421" t="s">
         <v>524</v>
       </c>
-      <c r="D421" t="s">
-        <v>525</v>
-      </c>
-      <c r="E421">
-        <v>0</v>
-      </c>
-      <c r="F421" t="s">
+      <c r="G421">
+        <v>0</v>
+      </c>
+      <c r="H421" t="s">
         <v>526</v>
       </c>
-      <c r="G421">
-        <v>0</v>
-      </c>
-      <c r="H421" t="s">
-        <v>528</v>
-      </c>
       <c r="I421" t="b">
         <v>1</v>
       </c>
       <c r="J421" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K421" s="1" t="d">
         <v>2025-11-10</v>
@@ -30481,39 +30481,39 @@
         <v>27</v>
       </c>
       <c r="U421" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="422" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
+        <v>511</v>
+      </c>
+      <c r="B422" t="s">
+        <v>20</v>
+      </c>
+      <c r="C422" t="s">
+        <v>531</v>
+      </c>
+      <c r="D422" t="s">
         <v>513</v>
       </c>
-      <c r="B422" t="s">
-        <v>20</v>
-      </c>
-      <c r="C422" t="s">
-        <v>533</v>
-      </c>
-      <c r="D422" t="s">
-        <v>515</v>
-      </c>
       <c r="E422">
         <v>0</v>
       </c>
       <c r="F422" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G422">
         <v>0</v>
       </c>
       <c r="H422" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I422" t="b">
         <v>1</v>
       </c>
       <c r="J422" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K422" s="1" t="d">
         <v>2025-11-10</v>
@@ -30546,27 +30546,27 @@
         <v>27</v>
       </c>
       <c r="U422" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="423" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B423" t="s">
         <v>20</v>
       </c>
       <c r="C423" t="s">
+        <v>522</v>
+      </c>
+      <c r="D423" t="s">
+        <v>523</v>
+      </c>
+      <c r="E423">
+        <v>0</v>
+      </c>
+      <c r="F423" t="s">
         <v>524</v>
-      </c>
-      <c r="D423" t="s">
-        <v>525</v>
-      </c>
-      <c r="E423">
-        <v>0</v>
-      </c>
-      <c r="F423" t="s">
-        <v>526</v>
       </c>
       <c r="G423">
         <v>0</v>
@@ -30578,7 +30578,7 @@
         <v>1</v>
       </c>
       <c r="J423" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K423" s="1" t="d">
         <v>2026-01-07</v>
@@ -30611,27 +30611,27 @@
         <v>27</v>
       </c>
       <c r="U423" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="424" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B424" t="s">
         <v>20</v>
       </c>
       <c r="C424" t="s">
+        <v>522</v>
+      </c>
+      <c r="D424" t="s">
+        <v>523</v>
+      </c>
+      <c r="E424">
+        <v>0</v>
+      </c>
+      <c r="F424" t="s">
         <v>524</v>
-      </c>
-      <c r="D424" t="s">
-        <v>525</v>
-      </c>
-      <c r="E424">
-        <v>0</v>
-      </c>
-      <c r="F424" t="s">
-        <v>526</v>
       </c>
       <c r="G424">
         <v>0</v>
@@ -30643,7 +30643,7 @@
         <v>1</v>
       </c>
       <c r="J424" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K424" s="1" t="d">
         <v>2026-01-15</v>
@@ -30676,27 +30676,27 @@
         <v>27</v>
       </c>
       <c r="U424" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="425" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B425" t="s">
         <v>20</v>
       </c>
       <c r="C425" t="s">
+        <v>522</v>
+      </c>
+      <c r="D425" t="s">
+        <v>523</v>
+      </c>
+      <c r="E425">
+        <v>0</v>
+      </c>
+      <c r="F425" t="s">
         <v>524</v>
-      </c>
-      <c r="D425" t="s">
-        <v>525</v>
-      </c>
-      <c r="E425">
-        <v>0</v>
-      </c>
-      <c r="F425" t="s">
-        <v>526</v>
       </c>
       <c r="G425">
         <v>0</v>
@@ -30708,7 +30708,7 @@
         <v>1</v>
       </c>
       <c r="J425" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K425" s="1" t="d">
         <v>2026-02-04</v>
@@ -30741,39 +30741,39 @@
         <v>27</v>
       </c>
       <c r="U425" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="426" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B426" t="s">
         <v>20</v>
       </c>
       <c r="C426" t="s">
+        <v>522</v>
+      </c>
+      <c r="D426" t="s">
+        <v>523</v>
+      </c>
+      <c r="E426">
+        <v>0</v>
+      </c>
+      <c r="F426" t="s">
         <v>524</v>
       </c>
-      <c r="D426" t="s">
-        <v>525</v>
-      </c>
-      <c r="E426">
-        <v>0</v>
-      </c>
-      <c r="F426" t="s">
-        <v>526</v>
-      </c>
       <c r="G426">
         <v>0</v>
       </c>
       <c r="H426" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I426" t="b">
         <v>0</v>
       </c>
       <c r="J426" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K426" s="1" t="d">
         <v>2026-03-09</v>
@@ -30806,27 +30806,27 @@
         <v>27</v>
       </c>
       <c r="U426" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="427" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B427" t="s">
         <v>20</v>
       </c>
       <c r="C427" t="s">
+        <v>522</v>
+      </c>
+      <c r="D427" t="s">
+        <v>523</v>
+      </c>
+      <c r="E427">
+        <v>0</v>
+      </c>
+      <c r="F427" t="s">
         <v>524</v>
-      </c>
-      <c r="D427" t="s">
-        <v>525</v>
-      </c>
-      <c r="E427">
-        <v>0</v>
-      </c>
-      <c r="F427" t="s">
-        <v>526</v>
       </c>
       <c r="G427">
         <v>0</v>
@@ -30838,7 +30838,7 @@
         <v>1</v>
       </c>
       <c r="J427" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K427" s="1" t="d">
         <v>2026-03-14</v>
@@ -30871,39 +30871,39 @@
         <v>27</v>
       </c>
       <c r="U427" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="428" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B428" t="s">
         <v>20</v>
       </c>
       <c r="C428" t="s">
+        <v>522</v>
+      </c>
+      <c r="D428" t="s">
+        <v>523</v>
+      </c>
+      <c r="E428">
+        <v>0</v>
+      </c>
+      <c r="F428" t="s">
         <v>524</v>
       </c>
-      <c r="D428" t="s">
-        <v>525</v>
-      </c>
-      <c r="E428">
-        <v>0</v>
-      </c>
-      <c r="F428" t="s">
-        <v>526</v>
-      </c>
       <c r="G428">
         <v>0</v>
       </c>
       <c r="H428" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I428" t="b">
         <v>0</v>
       </c>
       <c r="J428" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K428" s="1" t="d">
         <v>2026-03-18</v>
@@ -30936,39 +30936,39 @@
         <v>27</v>
       </c>
       <c r="U428" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="429" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B429" t="s">
         <v>20</v>
       </c>
       <c r="C429" t="s">
+        <v>522</v>
+      </c>
+      <c r="D429" t="s">
+        <v>523</v>
+      </c>
+      <c r="E429">
+        <v>0</v>
+      </c>
+      <c r="F429" t="s">
         <v>524</v>
       </c>
-      <c r="D429" t="s">
-        <v>525</v>
-      </c>
-      <c r="E429">
-        <v>0</v>
-      </c>
-      <c r="F429" t="s">
+      <c r="G429">
+        <v>0</v>
+      </c>
+      <c r="H429" t="s">
         <v>526</v>
       </c>
-      <c r="G429">
-        <v>0</v>
-      </c>
-      <c r="H429" t="s">
-        <v>528</v>
-      </c>
       <c r="I429" t="b">
         <v>1</v>
       </c>
       <c r="J429" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K429" s="1" t="d">
         <v>2026-03-23</v>
@@ -31001,27 +31001,27 @@
         <v>27</v>
       </c>
       <c r="U429" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="430" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B430" t="s">
         <v>20</v>
       </c>
       <c r="C430" t="s">
+        <v>522</v>
+      </c>
+      <c r="D430" t="s">
+        <v>523</v>
+      </c>
+      <c r="E430">
+        <v>0</v>
+      </c>
+      <c r="F430" t="s">
         <v>524</v>
-      </c>
-      <c r="D430" t="s">
-        <v>525</v>
-      </c>
-      <c r="E430">
-        <v>0</v>
-      </c>
-      <c r="F430" t="s">
-        <v>526</v>
       </c>
       <c r="G430">
         <v>0</v>
@@ -31033,7 +31033,7 @@
         <v>1</v>
       </c>
       <c r="J430" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K430" s="1" t="d">
         <v>2026-04-01</v>
@@ -31066,39 +31066,39 @@
         <v>27</v>
       </c>
       <c r="U430" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="431" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B431" t="s">
         <v>20</v>
       </c>
       <c r="C431" t="s">
+        <v>522</v>
+      </c>
+      <c r="D431" t="s">
+        <v>523</v>
+      </c>
+      <c r="E431">
+        <v>0</v>
+      </c>
+      <c r="F431" t="s">
         <v>524</v>
       </c>
-      <c r="D431" t="s">
-        <v>525</v>
-      </c>
-      <c r="E431">
-        <v>0</v>
-      </c>
-      <c r="F431" t="s">
-        <v>526</v>
-      </c>
       <c r="G431">
         <v>0</v>
       </c>
       <c r="H431" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I431" t="b">
         <v>0</v>
       </c>
       <c r="J431" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K431" s="1" t="d">
         <v>2026-04-06</v>
@@ -31131,39 +31131,39 @@
         <v>27</v>
       </c>
       <c r="U431" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="432" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B432" t="s">
         <v>20</v>
       </c>
       <c r="C432" t="s">
+        <v>522</v>
+      </c>
+      <c r="D432" t="s">
+        <v>523</v>
+      </c>
+      <c r="E432">
+        <v>0</v>
+      </c>
+      <c r="F432" t="s">
         <v>524</v>
       </c>
-      <c r="D432" t="s">
-        <v>525</v>
-      </c>
-      <c r="E432">
-        <v>0</v>
-      </c>
-      <c r="F432" t="s">
-        <v>526</v>
-      </c>
       <c r="G432">
         <v>0</v>
       </c>
       <c r="H432" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I432" t="b">
         <v>0</v>
       </c>
       <c r="J432" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K432" s="1" t="d">
         <v>2026-04-06</v>
@@ -31196,39 +31196,39 @@
         <v>27</v>
       </c>
       <c r="U432" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="433" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B433" t="s">
         <v>20</v>
       </c>
       <c r="C433" t="s">
+        <v>522</v>
+      </c>
+      <c r="D433" t="s">
+        <v>523</v>
+      </c>
+      <c r="E433">
+        <v>0</v>
+      </c>
+      <c r="F433" t="s">
         <v>524</v>
       </c>
-      <c r="D433" t="s">
-        <v>525</v>
-      </c>
-      <c r="E433">
-        <v>0</v>
-      </c>
-      <c r="F433" t="s">
-        <v>526</v>
-      </c>
       <c r="G433">
         <v>0</v>
       </c>
       <c r="H433" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I433" t="b">
         <v>1</v>
       </c>
       <c r="J433" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="K433" s="1" t="d">
         <v>2026-04-24</v>
@@ -31261,27 +31261,27 @@
         <v>27</v>
       </c>
       <c r="U433" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="434" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B434" t="s">
         <v>20</v>
       </c>
       <c r="C434" t="s">
+        <v>522</v>
+      </c>
+      <c r="D434" t="s">
+        <v>523</v>
+      </c>
+      <c r="E434">
+        <v>0</v>
+      </c>
+      <c r="F434" t="s">
         <v>524</v>
-      </c>
-      <c r="D434" t="s">
-        <v>525</v>
-      </c>
-      <c r="E434">
-        <v>0</v>
-      </c>
-      <c r="F434" t="s">
-        <v>526</v>
       </c>
       <c r="G434">
         <v>0</v>
@@ -31293,7 +31293,7 @@
         <v>1</v>
       </c>
       <c r="J434" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="K434" s="1" t="d">
         <v>2026-05-08</v>
@@ -31326,39 +31326,39 @@
         <v>27</v>
       </c>
       <c r="U434" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="435" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B435" t="s">
         <v>20</v>
       </c>
       <c r="C435" t="s">
+        <v>522</v>
+      </c>
+      <c r="D435" t="s">
+        <v>523</v>
+      </c>
+      <c r="E435">
+        <v>0</v>
+      </c>
+      <c r="F435" t="s">
         <v>524</v>
       </c>
-      <c r="D435" t="s">
-        <v>525</v>
-      </c>
-      <c r="E435">
-        <v>0</v>
-      </c>
-      <c r="F435" t="s">
+      <c r="G435">
+        <v>0</v>
+      </c>
+      <c r="H435" t="s">
         <v>526</v>
       </c>
-      <c r="G435">
-        <v>0</v>
-      </c>
-      <c r="H435" t="s">
-        <v>528</v>
-      </c>
       <c r="I435" t="b">
         <v>1</v>
       </c>
       <c r="J435" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="K435" s="1" t="d">
         <v>2026-05-11</v>
@@ -31391,39 +31391,39 @@
         <v>27</v>
       </c>
       <c r="U435" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="436" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B436" t="s">
         <v>20</v>
       </c>
       <c r="C436" t="s">
+        <v>522</v>
+      </c>
+      <c r="D436" t="s">
+        <v>523</v>
+      </c>
+      <c r="E436">
+        <v>0</v>
+      </c>
+      <c r="F436" t="s">
         <v>524</v>
       </c>
-      <c r="D436" t="s">
-        <v>525</v>
-      </c>
-      <c r="E436">
-        <v>0</v>
-      </c>
-      <c r="F436" t="s">
-        <v>526</v>
-      </c>
       <c r="G436">
         <v>0</v>
       </c>
       <c r="H436" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I436" t="b">
         <v>0</v>
       </c>
       <c r="J436" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="K436" s="1" t="d">
         <v>2026-06-10</v>
@@ -31456,27 +31456,27 @@
         <v>27</v>
       </c>
       <c r="U436" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="437" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B437" t="s">
         <v>20</v>
       </c>
       <c r="C437" t="s">
+        <v>522</v>
+      </c>
+      <c r="D437" t="s">
+        <v>523</v>
+      </c>
+      <c r="E437">
+        <v>0</v>
+      </c>
+      <c r="F437" t="s">
         <v>524</v>
-      </c>
-      <c r="D437" t="s">
-        <v>525</v>
-      </c>
-      <c r="E437">
-        <v>0</v>
-      </c>
-      <c r="F437" t="s">
-        <v>526</v>
       </c>
       <c r="G437">
         <v>0</v>
@@ -31521,27 +31521,27 @@
         <v>27</v>
       </c>
       <c r="U437" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="438" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B438" t="s">
         <v>20</v>
       </c>
       <c r="C438" t="s">
+        <v>522</v>
+      </c>
+      <c r="D438" t="s">
+        <v>523</v>
+      </c>
+      <c r="E438">
+        <v>0</v>
+      </c>
+      <c r="F438" t="s">
         <v>524</v>
-      </c>
-      <c r="D438" t="s">
-        <v>525</v>
-      </c>
-      <c r="E438">
-        <v>0</v>
-      </c>
-      <c r="F438" t="s">
-        <v>526</v>
       </c>
       <c r="G438">
         <v>0</v>
@@ -31553,7 +31553,7 @@
         <v>1</v>
       </c>
       <c r="J438" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K438" s="1" t="d">
         <v>2026-07-11</v>
@@ -31586,27 +31586,27 @@
         <v>27</v>
       </c>
       <c r="U438" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="439" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B439" t="s">
         <v>20</v>
       </c>
       <c r="C439" t="s">
+        <v>522</v>
+      </c>
+      <c r="D439" t="s">
+        <v>523</v>
+      </c>
+      <c r="E439">
+        <v>0</v>
+      </c>
+      <c r="F439" t="s">
         <v>524</v>
-      </c>
-      <c r="D439" t="s">
-        <v>525</v>
-      </c>
-      <c r="E439">
-        <v>0</v>
-      </c>
-      <c r="F439" t="s">
-        <v>526</v>
       </c>
       <c r="G439">
         <v>0</v>
@@ -31651,39 +31651,39 @@
         <v>27</v>
       </c>
       <c r="U439" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="440" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B440" t="s">
         <v>20</v>
       </c>
       <c r="C440" t="s">
+        <v>522</v>
+      </c>
+      <c r="D440" t="s">
+        <v>523</v>
+      </c>
+      <c r="E440">
+        <v>0</v>
+      </c>
+      <c r="F440" t="s">
         <v>524</v>
       </c>
-      <c r="D440" t="s">
-        <v>525</v>
-      </c>
-      <c r="E440">
-        <v>0</v>
-      </c>
-      <c r="F440" t="s">
-        <v>526</v>
-      </c>
       <c r="G440">
         <v>0</v>
       </c>
       <c r="H440" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I440" t="b">
         <v>0</v>
       </c>
       <c r="J440" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="K440" s="1" t="d">
         <v>2026-07-31</v>
@@ -31716,39 +31716,39 @@
         <v>27</v>
       </c>
       <c r="U440" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="441" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B441" t="s">
         <v>20</v>
       </c>
       <c r="C441" t="s">
+        <v>522</v>
+      </c>
+      <c r="D441" t="s">
+        <v>523</v>
+      </c>
+      <c r="E441">
+        <v>0</v>
+      </c>
+      <c r="F441" t="s">
         <v>524</v>
       </c>
-      <c r="D441" t="s">
-        <v>525</v>
-      </c>
-      <c r="E441">
-        <v>0</v>
-      </c>
-      <c r="F441" t="s">
-        <v>526</v>
-      </c>
       <c r="G441">
         <v>0</v>
       </c>
       <c r="H441" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I441" t="b">
         <v>0</v>
       </c>
       <c r="J441" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="K441" s="1" t="d">
         <v>2026-07-31</v>
@@ -31781,39 +31781,39 @@
         <v>27</v>
       </c>
       <c r="U441" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="442" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B442" t="s">
         <v>20</v>
       </c>
       <c r="C442" t="s">
+        <v>522</v>
+      </c>
+      <c r="D442" t="s">
+        <v>523</v>
+      </c>
+      <c r="E442">
+        <v>0</v>
+      </c>
+      <c r="F442" t="s">
         <v>524</v>
       </c>
-      <c r="D442" t="s">
-        <v>525</v>
-      </c>
-      <c r="E442">
-        <v>0</v>
-      </c>
-      <c r="F442" t="s">
-        <v>526</v>
-      </c>
       <c r="G442">
         <v>0</v>
       </c>
       <c r="H442" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I442" t="b">
         <v>0</v>
       </c>
       <c r="J442" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="K442" s="1" t="d">
         <v>2026-07-31</v>
@@ -31846,27 +31846,27 @@
         <v>27</v>
       </c>
       <c r="U442" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="443" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B443" t="s">
         <v>20</v>
       </c>
       <c r="C443" t="s">
+        <v>522</v>
+      </c>
+      <c r="D443" t="s">
+        <v>523</v>
+      </c>
+      <c r="E443">
+        <v>0</v>
+      </c>
+      <c r="F443" t="s">
         <v>524</v>
-      </c>
-      <c r="D443" t="s">
-        <v>525</v>
-      </c>
-      <c r="E443">
-        <v>0</v>
-      </c>
-      <c r="F443" t="s">
-        <v>526</v>
       </c>
       <c r="G443">
         <v>0</v>
@@ -31878,7 +31878,7 @@
         <v>1</v>
       </c>
       <c r="J443" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="K443" s="1" t="d">
         <v>2026-08-01</v>
@@ -31911,27 +31911,27 @@
         <v>27</v>
       </c>
       <c r="U443" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="444" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B444" t="s">
         <v>20</v>
       </c>
       <c r="C444" t="s">
+        <v>522</v>
+      </c>
+      <c r="D444" t="s">
+        <v>523</v>
+      </c>
+      <c r="E444">
+        <v>0</v>
+      </c>
+      <c r="F444" t="s">
         <v>524</v>
-      </c>
-      <c r="D444" t="s">
-        <v>525</v>
-      </c>
-      <c r="E444">
-        <v>0</v>
-      </c>
-      <c r="F444" t="s">
-        <v>526</v>
       </c>
       <c r="G444">
         <v>0</v>
@@ -31943,7 +31943,7 @@
         <v>1</v>
       </c>
       <c r="J444" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="K444" s="1" t="d">
         <v>2026-08-06</v>
@@ -31976,39 +31976,39 @@
         <v>27</v>
       </c>
       <c r="U444" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="445" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B445" t="s">
         <v>20</v>
       </c>
       <c r="C445" t="s">
+        <v>522</v>
+      </c>
+      <c r="D445" t="s">
+        <v>523</v>
+      </c>
+      <c r="E445">
+        <v>0</v>
+      </c>
+      <c r="F445" t="s">
         <v>524</v>
       </c>
-      <c r="D445" t="s">
-        <v>525</v>
-      </c>
-      <c r="E445">
-        <v>0</v>
-      </c>
-      <c r="F445" t="s">
+      <c r="G445">
+        <v>0</v>
+      </c>
+      <c r="H445" t="s">
         <v>526</v>
       </c>
-      <c r="G445">
-        <v>0</v>
-      </c>
-      <c r="H445" t="s">
-        <v>528</v>
-      </c>
       <c r="I445" t="b">
         <v>1</v>
       </c>
       <c r="J445" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="K445" s="1" t="d">
         <v>2026-08-10</v>
@@ -32041,39 +32041,39 @@
         <v>27</v>
       </c>
       <c r="U445" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="446" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B446" t="s">
         <v>20</v>
       </c>
       <c r="C446" t="s">
+        <v>522</v>
+      </c>
+      <c r="D446" t="s">
+        <v>523</v>
+      </c>
+      <c r="E446">
+        <v>0</v>
+      </c>
+      <c r="F446" t="s">
         <v>524</v>
       </c>
-      <c r="D446" t="s">
-        <v>525</v>
-      </c>
-      <c r="E446">
-        <v>0</v>
-      </c>
-      <c r="F446" t="s">
-        <v>526</v>
-      </c>
       <c r="G446">
         <v>0</v>
       </c>
       <c r="H446" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I446" t="b">
         <v>0</v>
       </c>
       <c r="J446" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="K446" s="1" t="d">
         <v>2026-08-12</v>
@@ -32106,39 +32106,39 @@
         <v>27</v>
       </c>
       <c r="U446" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="447" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B447" t="s">
         <v>20</v>
       </c>
       <c r="C447" t="s">
+        <v>522</v>
+      </c>
+      <c r="D447" t="s">
+        <v>523</v>
+      </c>
+      <c r="E447">
+        <v>0</v>
+      </c>
+      <c r="F447" t="s">
         <v>524</v>
       </c>
-      <c r="D447" t="s">
-        <v>525</v>
-      </c>
-      <c r="E447">
-        <v>0</v>
-      </c>
-      <c r="F447" t="s">
-        <v>526</v>
-      </c>
       <c r="G447">
         <v>0</v>
       </c>
       <c r="H447" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I447" t="b">
         <v>0</v>
       </c>
       <c r="J447" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="K447" s="1" t="d">
         <v>2026-08-12</v>
@@ -32171,39 +32171,39 @@
         <v>27</v>
       </c>
       <c r="U447" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="448" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B448" t="s">
         <v>20</v>
       </c>
       <c r="C448" t="s">
+        <v>522</v>
+      </c>
+      <c r="D448" t="s">
+        <v>523</v>
+      </c>
+      <c r="E448">
+        <v>0</v>
+      </c>
+      <c r="F448" t="s">
         <v>524</v>
       </c>
-      <c r="D448" t="s">
-        <v>525</v>
-      </c>
-      <c r="E448">
-        <v>0</v>
-      </c>
-      <c r="F448" t="s">
-        <v>526</v>
-      </c>
       <c r="G448">
         <v>0</v>
       </c>
       <c r="H448" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I448" t="b">
         <v>0</v>
       </c>
       <c r="J448" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K448" s="1" t="d">
         <v>2026-08-31</v>
@@ -32236,39 +32236,39 @@
         <v>27</v>
       </c>
       <c r="U448" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="449" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B449" t="s">
         <v>20</v>
       </c>
       <c r="C449" t="s">
+        <v>522</v>
+      </c>
+      <c r="D449" t="s">
+        <v>523</v>
+      </c>
+      <c r="E449">
+        <v>0</v>
+      </c>
+      <c r="F449" t="s">
         <v>524</v>
       </c>
-      <c r="D449" t="s">
-        <v>525</v>
-      </c>
-      <c r="E449">
-        <v>0</v>
-      </c>
-      <c r="F449" t="s">
-        <v>526</v>
-      </c>
       <c r="G449">
         <v>0</v>
       </c>
       <c r="H449" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I449" t="b">
         <v>0</v>
       </c>
       <c r="J449" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K449" s="1" t="d">
         <v>2026-08-31</v>
@@ -32301,39 +32301,39 @@
         <v>27</v>
       </c>
       <c r="U449" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="450" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B450" t="s">
         <v>20</v>
       </c>
       <c r="C450" t="s">
+        <v>522</v>
+      </c>
+      <c r="D450" t="s">
+        <v>523</v>
+      </c>
+      <c r="E450">
+        <v>0</v>
+      </c>
+      <c r="F450" t="s">
         <v>524</v>
       </c>
-      <c r="D450" t="s">
-        <v>525</v>
-      </c>
-      <c r="E450">
-        <v>0</v>
-      </c>
-      <c r="F450" t="s">
-        <v>526</v>
-      </c>
       <c r="G450">
         <v>0</v>
       </c>
       <c r="H450" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I450" t="b">
         <v>0</v>
       </c>
       <c r="J450" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K450" s="1" t="d">
         <v>2026-08-31</v>
@@ -32366,33 +32366,33 @@
         <v>27</v>
       </c>
       <c r="U450" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="451" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B451" t="s">
         <v>20</v>
       </c>
       <c r="C451" t="s">
+        <v>522</v>
+      </c>
+      <c r="D451" t="s">
+        <v>523</v>
+      </c>
+      <c r="E451">
+        <v>0</v>
+      </c>
+      <c r="F451" t="s">
         <v>524</v>
       </c>
-      <c r="D451" t="s">
-        <v>525</v>
-      </c>
-      <c r="E451">
-        <v>0</v>
-      </c>
-      <c r="F451" t="s">
-        <v>526</v>
-      </c>
       <c r="G451">
         <v>0</v>
       </c>
       <c r="H451" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I451" t="b">
         <v>0</v>
@@ -32431,33 +32431,33 @@
         <v>27</v>
       </c>
       <c r="U451" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="452" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B452" t="s">
         <v>20</v>
       </c>
       <c r="C452" t="s">
+        <v>522</v>
+      </c>
+      <c r="D452" t="s">
+        <v>523</v>
+      </c>
+      <c r="E452">
+        <v>0</v>
+      </c>
+      <c r="F452" t="s">
         <v>524</v>
       </c>
-      <c r="D452" t="s">
-        <v>525</v>
-      </c>
-      <c r="E452">
-        <v>0</v>
-      </c>
-      <c r="F452" t="s">
-        <v>526</v>
-      </c>
       <c r="G452">
         <v>0</v>
       </c>
       <c r="H452" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I452" t="b">
         <v>0</v>
@@ -32496,33 +32496,33 @@
         <v>27</v>
       </c>
       <c r="U452" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="453" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B453" t="s">
         <v>20</v>
       </c>
       <c r="C453" t="s">
+        <v>522</v>
+      </c>
+      <c r="D453" t="s">
+        <v>523</v>
+      </c>
+      <c r="E453">
+        <v>0</v>
+      </c>
+      <c r="F453" t="s">
         <v>524</v>
       </c>
-      <c r="D453" t="s">
-        <v>525</v>
-      </c>
-      <c r="E453">
-        <v>0</v>
-      </c>
-      <c r="F453" t="s">
-        <v>526</v>
-      </c>
       <c r="G453">
         <v>0</v>
       </c>
       <c r="H453" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I453" t="b">
         <v>1</v>
@@ -32561,39 +32561,39 @@
         <v>27</v>
       </c>
       <c r="U453" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="454" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B454" t="s">
         <v>20</v>
       </c>
       <c r="C454" t="s">
+        <v>522</v>
+      </c>
+      <c r="D454" t="s">
+        <v>523</v>
+      </c>
+      <c r="E454">
+        <v>0</v>
+      </c>
+      <c r="F454" t="s">
         <v>524</v>
       </c>
-      <c r="D454" t="s">
-        <v>525</v>
-      </c>
-      <c r="E454">
-        <v>0</v>
-      </c>
-      <c r="F454" t="s">
+      <c r="G454">
+        <v>0</v>
+      </c>
+      <c r="H454" t="s">
         <v>526</v>
       </c>
-      <c r="G454">
-        <v>0</v>
-      </c>
-      <c r="H454" t="s">
-        <v>528</v>
-      </c>
       <c r="I454" t="b">
         <v>1</v>
       </c>
       <c r="J454" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="K454" s="1" t="d">
         <v>2026-09-15</v>
@@ -32626,27 +32626,27 @@
         <v>27</v>
       </c>
       <c r="U454" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="455" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B455" t="s">
         <v>20</v>
       </c>
       <c r="C455" t="s">
+        <v>522</v>
+      </c>
+      <c r="D455" t="s">
+        <v>523</v>
+      </c>
+      <c r="E455">
+        <v>0</v>
+      </c>
+      <c r="F455" t="s">
         <v>524</v>
-      </c>
-      <c r="D455" t="s">
-        <v>525</v>
-      </c>
-      <c r="E455">
-        <v>0</v>
-      </c>
-      <c r="F455" t="s">
-        <v>526</v>
       </c>
       <c r="G455">
         <v>0</v>
@@ -32691,39 +32691,39 @@
         <v>27</v>
       </c>
       <c r="U455" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="456" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B456" t="s">
         <v>83</v>
       </c>
       <c r="C456" t="s">
+        <v>562</v>
+      </c>
+      <c r="D456" t="s">
+        <v>563</v>
+      </c>
+      <c r="E456">
+        <v>0</v>
+      </c>
+      <c r="F456" t="s">
         <v>564</v>
       </c>
-      <c r="D456" t="s">
+      <c r="G456">
+        <v>1</v>
+      </c>
+      <c r="H456" t="s">
         <v>565</v>
       </c>
-      <c r="E456">
-        <v>0</v>
-      </c>
-      <c r="F456" t="s">
+      <c r="I456" t="b">
+        <v>0</v>
+      </c>
+      <c r="J456" t="s">
         <v>566</v>
-      </c>
-      <c r="G456">
-        <v>1</v>
-      </c>
-      <c r="H456" t="s">
-        <v>567</v>
-      </c>
-      <c r="I456" t="b">
-        <v>0</v>
-      </c>
-      <c r="J456" t="s">
-        <v>568</v>
       </c>
       <c r="K456" s="1" t="d">
         <v>2025-02-21</v>
@@ -32756,39 +32756,39 @@
         <v>27</v>
       </c>
       <c r="U456" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="457" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B457" t="s">
         <v>83</v>
       </c>
       <c r="C457" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D457" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E457">
         <v>0</v>
       </c>
       <c r="F457" t="s">
+        <v>564</v>
+      </c>
+      <c r="G457">
+        <v>1</v>
+      </c>
+      <c r="H457" t="s">
+        <v>565</v>
+      </c>
+      <c r="I457" t="b">
+        <v>0</v>
+      </c>
+      <c r="J457" t="s">
         <v>566</v>
-      </c>
-      <c r="G457">
-        <v>1</v>
-      </c>
-      <c r="H457" t="s">
-        <v>567</v>
-      </c>
-      <c r="I457" t="b">
-        <v>0</v>
-      </c>
-      <c r="J457" t="s">
-        <v>568</v>
       </c>
       <c r="K457" s="1" t="d">
         <v>2025-02-21</v>
@@ -32821,39 +32821,39 @@
         <v>27</v>
       </c>
       <c r="U457" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="458" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B458" t="s">
         <v>83</v>
       </c>
       <c r="C458" t="s">
+        <v>562</v>
+      </c>
+      <c r="D458" t="s">
+        <v>563</v>
+      </c>
+      <c r="E458">
+        <v>0</v>
+      </c>
+      <c r="F458" t="s">
         <v>564</v>
       </c>
-      <c r="D458" t="s">
+      <c r="G458">
+        <v>1</v>
+      </c>
+      <c r="H458" t="s">
         <v>565</v>
       </c>
-      <c r="E458">
-        <v>0</v>
-      </c>
-      <c r="F458" t="s">
-        <v>566</v>
-      </c>
-      <c r="G458">
-        <v>1</v>
-      </c>
-      <c r="H458" t="s">
-        <v>567</v>
-      </c>
       <c r="I458" t="b">
         <v>0</v>
       </c>
       <c r="J458" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="K458" s="1" t="d">
         <v>2025-04-24</v>
@@ -32886,39 +32886,39 @@
         <v>27</v>
       </c>
       <c r="U458" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="459" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B459" t="s">
         <v>83</v>
       </c>
       <c r="C459" t="s">
+        <v>568</v>
+      </c>
+      <c r="D459" t="s">
+        <v>569</v>
+      </c>
+      <c r="E459">
+        <v>0</v>
+      </c>
+      <c r="F459" t="s">
+        <v>564</v>
+      </c>
+      <c r="G459">
+        <v>1</v>
+      </c>
+      <c r="H459" t="s">
+        <v>565</v>
+      </c>
+      <c r="I459" t="b">
+        <v>0</v>
+      </c>
+      <c r="J459" t="s">
         <v>570</v>
-      </c>
-      <c r="D459" t="s">
-        <v>571</v>
-      </c>
-      <c r="E459">
-        <v>0</v>
-      </c>
-      <c r="F459" t="s">
-        <v>566</v>
-      </c>
-      <c r="G459">
-        <v>1</v>
-      </c>
-      <c r="H459" t="s">
-        <v>567</v>
-      </c>
-      <c r="I459" t="b">
-        <v>0</v>
-      </c>
-      <c r="J459" t="s">
-        <v>572</v>
       </c>
       <c r="K459" s="1" t="d">
         <v>2025-04-24</v>
@@ -32951,27 +32951,27 @@
         <v>27</v>
       </c>
       <c r="U459" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="460" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B460" t="s">
         <v>83</v>
       </c>
       <c r="C460" t="s">
+        <v>562</v>
+      </c>
+      <c r="D460" t="s">
+        <v>563</v>
+      </c>
+      <c r="E460">
+        <v>0</v>
+      </c>
+      <c r="F460" t="s">
         <v>564</v>
-      </c>
-      <c r="D460" t="s">
-        <v>565</v>
-      </c>
-      <c r="E460">
-        <v>0</v>
-      </c>
-      <c r="F460" t="s">
-        <v>566</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -33016,27 +33016,27 @@
         <v>27</v>
       </c>
       <c r="U460" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="461" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B461" t="s">
         <v>83</v>
       </c>
       <c r="C461" t="s">
+        <v>562</v>
+      </c>
+      <c r="D461" t="s">
+        <v>563</v>
+      </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
+      <c r="F461" t="s">
         <v>564</v>
-      </c>
-      <c r="D461" t="s">
-        <v>565</v>
-      </c>
-      <c r="E461">
-        <v>0</v>
-      </c>
-      <c r="F461" t="s">
-        <v>566</v>
       </c>
       <c r="G461">
         <v>1</v>
@@ -33048,7 +33048,7 @@
         <v>1</v>
       </c>
       <c r="J461" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="K461" s="1" t="d">
         <v>2025-09-22</v>
@@ -33081,39 +33081,39 @@
         <v>27</v>
       </c>
       <c r="U461" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="462" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B462" t="s">
         <v>83</v>
       </c>
       <c r="C462" t="s">
+        <v>562</v>
+      </c>
+      <c r="D462" t="s">
+        <v>563</v>
+      </c>
+      <c r="E462">
+        <v>0</v>
+      </c>
+      <c r="F462" t="s">
         <v>564</v>
       </c>
-      <c r="D462" t="s">
+      <c r="G462">
+        <v>1</v>
+      </c>
+      <c r="H462" t="s">
         <v>565</v>
       </c>
-      <c r="E462">
-        <v>0</v>
-      </c>
-      <c r="F462" t="s">
-        <v>566</v>
-      </c>
-      <c r="G462">
-        <v>1</v>
-      </c>
-      <c r="H462" t="s">
-        <v>567</v>
-      </c>
       <c r="I462" t="b">
         <v>0</v>
       </c>
       <c r="J462" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="K462" s="1" t="d">
         <v>2025-10-14</v>
@@ -33146,27 +33146,27 @@
         <v>27</v>
       </c>
       <c r="U462" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="463" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B463" t="s">
         <v>83</v>
       </c>
       <c r="C463" t="s">
+        <v>562</v>
+      </c>
+      <c r="D463" t="s">
+        <v>563</v>
+      </c>
+      <c r="E463">
+        <v>0</v>
+      </c>
+      <c r="F463" t="s">
         <v>564</v>
-      </c>
-      <c r="D463" t="s">
-        <v>565</v>
-      </c>
-      <c r="E463">
-        <v>0</v>
-      </c>
-      <c r="F463" t="s">
-        <v>566</v>
       </c>
       <c r="G463">
         <v>1</v>
@@ -33178,7 +33178,7 @@
         <v>0</v>
       </c>
       <c r="J463" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K463" s="1" t="d">
         <v>2025-12-08</v>
@@ -33211,39 +33211,39 @@
         <v>27</v>
       </c>
       <c r="U463" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="464" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B464" t="s">
         <v>83</v>
       </c>
       <c r="C464" t="s">
+        <v>562</v>
+      </c>
+      <c r="D464" t="s">
+        <v>563</v>
+      </c>
+      <c r="E464">
+        <v>0</v>
+      </c>
+      <c r="F464" t="s">
         <v>564</v>
       </c>
-      <c r="D464" t="s">
-        <v>565</v>
-      </c>
-      <c r="E464">
-        <v>0</v>
-      </c>
-      <c r="F464" t="s">
-        <v>566</v>
-      </c>
       <c r="G464">
         <v>1</v>
       </c>
       <c r="H464" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I464" t="b">
         <v>1</v>
       </c>
       <c r="J464" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K464" s="1" t="d">
         <v>2026-02-22</v>
@@ -33276,27 +33276,27 @@
         <v>27</v>
       </c>
       <c r="U464" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="465" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B465" t="s">
         <v>83</v>
       </c>
       <c r="C465" t="s">
+        <v>562</v>
+      </c>
+      <c r="D465" t="s">
+        <v>563</v>
+      </c>
+      <c r="E465">
+        <v>0</v>
+      </c>
+      <c r="F465" t="s">
         <v>564</v>
-      </c>
-      <c r="D465" t="s">
-        <v>565</v>
-      </c>
-      <c r="E465">
-        <v>0</v>
-      </c>
-      <c r="F465" t="s">
-        <v>566</v>
       </c>
       <c r="G465">
         <v>1</v>
@@ -33341,27 +33341,27 @@
         <v>27</v>
       </c>
       <c r="U465" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="466" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B466" t="s">
         <v>83</v>
       </c>
       <c r="C466" t="s">
+        <v>562</v>
+      </c>
+      <c r="D466" t="s">
+        <v>563</v>
+      </c>
+      <c r="E466">
+        <v>0</v>
+      </c>
+      <c r="F466" t="s">
         <v>564</v>
-      </c>
-      <c r="D466" t="s">
-        <v>565</v>
-      </c>
-      <c r="E466">
-        <v>0</v>
-      </c>
-      <c r="F466" t="s">
-        <v>566</v>
       </c>
       <c r="G466">
         <v>1</v>
@@ -33373,7 +33373,7 @@
         <v>1</v>
       </c>
       <c r="J466" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K466" s="1" t="d">
         <v>2026-03-14</v>
@@ -33406,27 +33406,27 @@
         <v>27</v>
       </c>
       <c r="U466" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="467" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B467" t="s">
         <v>83</v>
       </c>
       <c r="C467" t="s">
+        <v>562</v>
+      </c>
+      <c r="D467" t="s">
+        <v>563</v>
+      </c>
+      <c r="E467">
+        <v>0</v>
+      </c>
+      <c r="F467" t="s">
         <v>564</v>
-      </c>
-      <c r="D467" t="s">
-        <v>565</v>
-      </c>
-      <c r="E467">
-        <v>0</v>
-      </c>
-      <c r="F467" t="s">
-        <v>566</v>
       </c>
       <c r="G467">
         <v>1</v>
@@ -33471,39 +33471,39 @@
         <v>27</v>
       </c>
       <c r="U467" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="468" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B468" t="s">
         <v>83</v>
       </c>
       <c r="C468" t="s">
+        <v>562</v>
+      </c>
+      <c r="D468" t="s">
+        <v>563</v>
+      </c>
+      <c r="E468">
+        <v>0</v>
+      </c>
+      <c r="F468" t="s">
         <v>564</v>
       </c>
-      <c r="D468" t="s">
+      <c r="G468">
+        <v>1</v>
+      </c>
+      <c r="H468" t="s">
         <v>565</v>
       </c>
-      <c r="E468">
-        <v>0</v>
-      </c>
-      <c r="F468" t="s">
-        <v>566</v>
-      </c>
-      <c r="G468">
-        <v>1</v>
-      </c>
-      <c r="H468" t="s">
-        <v>567</v>
-      </c>
       <c r="I468" t="b">
         <v>0</v>
       </c>
       <c r="J468" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="K468" s="1" t="d">
         <v>2026-04-14</v>
@@ -33536,27 +33536,27 @@
         <v>27</v>
       </c>
       <c r="U468" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="469" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B469" t="s">
         <v>83</v>
       </c>
       <c r="C469" t="s">
+        <v>562</v>
+      </c>
+      <c r="D469" t="s">
+        <v>563</v>
+      </c>
+      <c r="E469">
+        <v>0</v>
+      </c>
+      <c r="F469" t="s">
         <v>564</v>
-      </c>
-      <c r="D469" t="s">
-        <v>565</v>
-      </c>
-      <c r="E469">
-        <v>0</v>
-      </c>
-      <c r="F469" t="s">
-        <v>566</v>
       </c>
       <c r="G469">
         <v>1</v>
@@ -33568,7 +33568,7 @@
         <v>1</v>
       </c>
       <c r="J469" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K469" s="1" t="d">
         <v>2026-06-01</v>
@@ -33601,27 +33601,27 @@
         <v>27</v>
       </c>
       <c r="U469" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="470" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B470" t="s">
         <v>83</v>
       </c>
       <c r="C470" t="s">
+        <v>562</v>
+      </c>
+      <c r="D470" t="s">
+        <v>563</v>
+      </c>
+      <c r="E470">
+        <v>0</v>
+      </c>
+      <c r="F470" t="s">
         <v>564</v>
-      </c>
-      <c r="D470" t="s">
-        <v>565</v>
-      </c>
-      <c r="E470">
-        <v>0</v>
-      </c>
-      <c r="F470" t="s">
-        <v>566</v>
       </c>
       <c r="G470">
         <v>1</v>
@@ -33666,27 +33666,27 @@
         <v>27</v>
       </c>
       <c r="U470" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="471" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B471" t="s">
         <v>83</v>
       </c>
       <c r="C471" t="s">
+        <v>562</v>
+      </c>
+      <c r="D471" t="s">
+        <v>563</v>
+      </c>
+      <c r="E471">
+        <v>0</v>
+      </c>
+      <c r="F471" t="s">
         <v>564</v>
-      </c>
-      <c r="D471" t="s">
-        <v>565</v>
-      </c>
-      <c r="E471">
-        <v>0</v>
-      </c>
-      <c r="F471" t="s">
-        <v>566</v>
       </c>
       <c r="G471">
         <v>1</v>
@@ -33698,7 +33698,7 @@
         <v>1</v>
       </c>
       <c r="J471" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="K471" s="1" t="d">
         <v>2026-06-16</v>
@@ -33731,27 +33731,27 @@
         <v>27</v>
       </c>
       <c r="U471" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="472" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B472" t="s">
         <v>83</v>
       </c>
       <c r="C472" t="s">
+        <v>562</v>
+      </c>
+      <c r="D472" t="s">
+        <v>563</v>
+      </c>
+      <c r="E472">
+        <v>0</v>
+      </c>
+      <c r="F472" t="s">
         <v>564</v>
-      </c>
-      <c r="D472" t="s">
-        <v>565</v>
-      </c>
-      <c r="E472">
-        <v>0</v>
-      </c>
-      <c r="F472" t="s">
-        <v>566</v>
       </c>
       <c r="G472">
         <v>1</v>
@@ -33763,7 +33763,7 @@
         <v>0</v>
       </c>
       <c r="J472" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="K472" s="1" t="d">
         <v>2026-06-28</v>
@@ -33796,27 +33796,27 @@
         <v>27</v>
       </c>
       <c r="U472" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="473" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B473" t="s">
         <v>83</v>
       </c>
       <c r="C473" t="s">
+        <v>562</v>
+      </c>
+      <c r="D473" t="s">
+        <v>563</v>
+      </c>
+      <c r="E473">
+        <v>0</v>
+      </c>
+      <c r="F473" t="s">
         <v>564</v>
-      </c>
-      <c r="D473" t="s">
-        <v>565</v>
-      </c>
-      <c r="E473">
-        <v>0</v>
-      </c>
-      <c r="F473" t="s">
-        <v>566</v>
       </c>
       <c r="G473">
         <v>1</v>
@@ -33828,7 +33828,7 @@
         <v>1</v>
       </c>
       <c r="J473" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K473" s="1" t="d">
         <v>2026-08-04</v>
@@ -33861,27 +33861,27 @@
         <v>27</v>
       </c>
       <c r="U473" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="474" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B474" t="s">
         <v>83</v>
       </c>
       <c r="C474" t="s">
+        <v>562</v>
+      </c>
+      <c r="D474" t="s">
+        <v>563</v>
+      </c>
+      <c r="E474">
+        <v>0</v>
+      </c>
+      <c r="F474" t="s">
         <v>564</v>
-      </c>
-      <c r="D474" t="s">
-        <v>565</v>
-      </c>
-      <c r="E474">
-        <v>0</v>
-      </c>
-      <c r="F474" t="s">
-        <v>566</v>
       </c>
       <c r="G474">
         <v>1</v>
@@ -33926,27 +33926,27 @@
         <v>27</v>
       </c>
       <c r="U474" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="475" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B475" t="s">
         <v>83</v>
       </c>
       <c r="C475" t="s">
+        <v>562</v>
+      </c>
+      <c r="D475" t="s">
+        <v>563</v>
+      </c>
+      <c r="E475">
+        <v>0</v>
+      </c>
+      <c r="F475" t="s">
         <v>564</v>
-      </c>
-      <c r="D475" t="s">
-        <v>565</v>
-      </c>
-      <c r="E475">
-        <v>0</v>
-      </c>
-      <c r="F475" t="s">
-        <v>566</v>
       </c>
       <c r="G475">
         <v>1</v>
@@ -33958,7 +33958,7 @@
         <v>0</v>
       </c>
       <c r="J475" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="K475" s="1" t="d">
         <v>2026-08-13</v>
@@ -33991,27 +33991,27 @@
         <v>27</v>
       </c>
       <c r="U475" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="476" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B476" t="s">
         <v>83</v>
       </c>
       <c r="C476" t="s">
+        <v>562</v>
+      </c>
+      <c r="D476" t="s">
+        <v>563</v>
+      </c>
+      <c r="E476">
+        <v>0</v>
+      </c>
+      <c r="F476" t="s">
         <v>564</v>
-      </c>
-      <c r="D476" t="s">
-        <v>565</v>
-      </c>
-      <c r="E476">
-        <v>0</v>
-      </c>
-      <c r="F476" t="s">
-        <v>566</v>
       </c>
       <c r="G476">
         <v>1</v>
@@ -34056,27 +34056,27 @@
         <v>27</v>
       </c>
       <c r="U476" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="477" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B477" t="s">
         <v>83</v>
       </c>
       <c r="C477" t="s">
+        <v>562</v>
+      </c>
+      <c r="D477" t="s">
+        <v>563</v>
+      </c>
+      <c r="E477">
+        <v>0</v>
+      </c>
+      <c r="F477" t="s">
         <v>564</v>
-      </c>
-      <c r="D477" t="s">
-        <v>565</v>
-      </c>
-      <c r="E477">
-        <v>0</v>
-      </c>
-      <c r="F477" t="s">
-        <v>566</v>
       </c>
       <c r="G477">
         <v>1</v>
@@ -34121,27 +34121,27 @@
         <v>27</v>
       </c>
       <c r="U477" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="478" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B478" t="s">
         <v>83</v>
       </c>
       <c r="C478" t="s">
+        <v>562</v>
+      </c>
+      <c r="D478" t="s">
+        <v>563</v>
+      </c>
+      <c r="E478">
+        <v>0</v>
+      </c>
+      <c r="F478" t="s">
         <v>564</v>
-      </c>
-      <c r="D478" t="s">
-        <v>565</v>
-      </c>
-      <c r="E478">
-        <v>0</v>
-      </c>
-      <c r="F478" t="s">
-        <v>566</v>
       </c>
       <c r="G478">
         <v>1</v>
@@ -34153,7 +34153,7 @@
         <v>1</v>
       </c>
       <c r="J478" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="K478" s="1" t="d">
         <v>2026-09-09</v>
@@ -34186,39 +34186,39 @@
         <v>27</v>
       </c>
       <c r="U478" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="479" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B479" t="s">
         <v>83</v>
       </c>
       <c r="C479" t="s">
+        <v>562</v>
+      </c>
+      <c r="D479" t="s">
+        <v>563</v>
+      </c>
+      <c r="E479">
+        <v>0</v>
+      </c>
+      <c r="F479" t="s">
         <v>564</v>
       </c>
-      <c r="D479" t="s">
+      <c r="G479">
+        <v>1</v>
+      </c>
+      <c r="H479" t="s">
         <v>565</v>
       </c>
-      <c r="E479">
-        <v>0</v>
-      </c>
-      <c r="F479" t="s">
-        <v>566</v>
-      </c>
-      <c r="G479">
-        <v>1</v>
-      </c>
-      <c r="H479" t="s">
-        <v>567</v>
-      </c>
       <c r="I479" t="b">
         <v>0</v>
       </c>
       <c r="J479" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="K479" s="1" t="d">
         <v>2026-09-10</v>
@@ -34251,27 +34251,27 @@
         <v>27</v>
       </c>
       <c r="U479" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="480" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B480" t="s">
         <v>83</v>
       </c>
       <c r="C480" t="s">
+        <v>562</v>
+      </c>
+      <c r="D480" t="s">
+        <v>563</v>
+      </c>
+      <c r="E480">
+        <v>0</v>
+      </c>
+      <c r="F480" t="s">
         <v>564</v>
-      </c>
-      <c r="D480" t="s">
-        <v>565</v>
-      </c>
-      <c r="E480">
-        <v>0</v>
-      </c>
-      <c r="F480" t="s">
-        <v>566</v>
       </c>
       <c r="G480">
         <v>1</v>
@@ -34316,39 +34316,39 @@
         <v>27</v>
       </c>
       <c r="U480" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="481" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
+        <v>584</v>
+      </c>
+      <c r="B481" t="s">
+        <v>20</v>
+      </c>
+      <c r="C481" t="s">
+        <v>585</v>
+      </c>
+      <c r="D481" t="s">
         <v>586</v>
       </c>
-      <c r="B481" t="s">
-        <v>20</v>
-      </c>
-      <c r="C481" t="s">
+      <c r="E481">
+        <v>0</v>
+      </c>
+      <c r="F481" t="s">
         <v>587</v>
       </c>
-      <c r="D481" t="s">
+      <c r="G481">
+        <v>0</v>
+      </c>
+      <c r="H481" t="s">
         <v>588</v>
       </c>
-      <c r="E481">
-        <v>0</v>
-      </c>
-      <c r="F481" t="s">
-        <v>589</v>
-      </c>
-      <c r="G481">
-        <v>0</v>
-      </c>
-      <c r="H481" t="s">
-        <v>590</v>
-      </c>
       <c r="I481" t="b">
         <v>0</v>
       </c>
       <c r="J481" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="K481" s="1" t="d">
         <v>2026-08-06</v>
@@ -34381,39 +34381,39 @@
         <v>27</v>
       </c>
       <c r="U481" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="482" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B482" t="s">
         <v>20</v>
       </c>
       <c r="C482" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D482" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E482">
         <v>0</v>
       </c>
       <c r="F482" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G482">
         <v>0</v>
       </c>
       <c r="H482" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="I482" t="b">
         <v>0</v>
       </c>
       <c r="J482" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="K482" s="1" t="d">
         <v>2026-08-06</v>
@@ -34446,27 +34446,27 @@
         <v>27</v>
       </c>
       <c r="U482" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="483" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
+        <v>592</v>
+      </c>
+      <c r="B483" t="s">
+        <v>20</v>
+      </c>
+      <c r="C483" t="s">
+        <v>593</v>
+      </c>
+      <c r="D483" t="s">
         <v>594</v>
       </c>
-      <c r="B483" t="s">
-        <v>20</v>
-      </c>
-      <c r="C483" t="s">
+      <c r="E483">
+        <v>1</v>
+      </c>
+      <c r="F483" t="s">
         <v>595</v>
-      </c>
-      <c r="D483" t="s">
-        <v>596</v>
-      </c>
-      <c r="E483">
-        <v>1</v>
-      </c>
-      <c r="F483" t="s">
-        <v>597</v>
       </c>
       <c r="G483">
         <v>0</v>
@@ -34511,27 +34511,27 @@
         <v>27</v>
       </c>
       <c r="U483" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="484" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
+        <v>592</v>
+      </c>
+      <c r="B484" t="s">
+        <v>20</v>
+      </c>
+      <c r="C484" t="s">
+        <v>593</v>
+      </c>
+      <c r="D484" t="s">
         <v>594</v>
       </c>
-      <c r="B484" t="s">
-        <v>20</v>
-      </c>
-      <c r="C484" t="s">
+      <c r="E484">
+        <v>1</v>
+      </c>
+      <c r="F484" t="s">
         <v>595</v>
-      </c>
-      <c r="D484" t="s">
-        <v>596</v>
-      </c>
-      <c r="E484">
-        <v>1</v>
-      </c>
-      <c r="F484" t="s">
-        <v>597</v>
       </c>
       <c r="G484">
         <v>0</v>
@@ -34576,27 +34576,27 @@
         <v>27</v>
       </c>
       <c r="U484" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="485" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
+        <v>592</v>
+      </c>
+      <c r="B485" t="s">
+        <v>20</v>
+      </c>
+      <c r="C485" t="s">
+        <v>593</v>
+      </c>
+      <c r="D485" t="s">
         <v>594</v>
       </c>
-      <c r="B485" t="s">
-        <v>20</v>
-      </c>
-      <c r="C485" t="s">
+      <c r="E485">
+        <v>1</v>
+      </c>
+      <c r="F485" t="s">
         <v>595</v>
-      </c>
-      <c r="D485" t="s">
-        <v>596</v>
-      </c>
-      <c r="E485">
-        <v>1</v>
-      </c>
-      <c r="F485" t="s">
-        <v>597</v>
       </c>
       <c r="G485">
         <v>0</v>
@@ -34641,27 +34641,27 @@
         <v>27</v>
       </c>
       <c r="U485" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="486" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
+        <v>597</v>
+      </c>
+      <c r="B486" t="s">
+        <v>20</v>
+      </c>
+      <c r="C486" t="s">
+        <v>598</v>
+      </c>
+      <c r="D486" t="s">
         <v>599</v>
       </c>
-      <c r="B486" t="s">
-        <v>20</v>
-      </c>
-      <c r="C486" t="s">
+      <c r="E486">
+        <v>0</v>
+      </c>
+      <c r="F486" t="s">
         <v>600</v>
-      </c>
-      <c r="D486" t="s">
-        <v>601</v>
-      </c>
-      <c r="E486">
-        <v>0</v>
-      </c>
-      <c r="F486" t="s">
-        <v>602</v>
       </c>
       <c r="G486">
         <v>1</v>
@@ -34673,7 +34673,7 @@
         <v>1</v>
       </c>
       <c r="J486" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="K486" s="1" t="d">
         <v>2025-11-22</v>
@@ -34706,27 +34706,27 @@
         <v>27</v>
       </c>
       <c r="U486" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="487" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
+        <v>597</v>
+      </c>
+      <c r="B487" t="s">
+        <v>20</v>
+      </c>
+      <c r="C487" t="s">
+        <v>598</v>
+      </c>
+      <c r="D487" t="s">
         <v>599</v>
       </c>
-      <c r="B487" t="s">
-        <v>20</v>
-      </c>
-      <c r="C487" t="s">
+      <c r="E487">
+        <v>0</v>
+      </c>
+      <c r="F487" t="s">
         <v>600</v>
-      </c>
-      <c r="D487" t="s">
-        <v>601</v>
-      </c>
-      <c r="E487">
-        <v>0</v>
-      </c>
-      <c r="F487" t="s">
-        <v>602</v>
       </c>
       <c r="G487">
         <v>1</v>
@@ -34738,7 +34738,7 @@
         <v>1</v>
       </c>
       <c r="J487" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="K487" s="1" t="d">
         <v>2026-03-01</v>
@@ -34771,27 +34771,27 @@
         <v>27</v>
       </c>
       <c r="U487" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="488" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
+        <v>597</v>
+      </c>
+      <c r="B488" t="s">
+        <v>20</v>
+      </c>
+      <c r="C488" t="s">
+        <v>598</v>
+      </c>
+      <c r="D488" t="s">
         <v>599</v>
       </c>
-      <c r="B488" t="s">
-        <v>20</v>
-      </c>
-      <c r="C488" t="s">
+      <c r="E488">
+        <v>0</v>
+      </c>
+      <c r="F488" t="s">
         <v>600</v>
-      </c>
-      <c r="D488" t="s">
-        <v>601</v>
-      </c>
-      <c r="E488">
-        <v>0</v>
-      </c>
-      <c r="F488" t="s">
-        <v>602</v>
       </c>
       <c r="G488">
         <v>1</v>
@@ -34803,7 +34803,7 @@
         <v>1</v>
       </c>
       <c r="J488" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="K488" s="1" t="d">
         <v>2026-06-22</v>
@@ -34836,27 +34836,27 @@
         <v>27</v>
       </c>
       <c r="U488" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="489" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B489" t="s">
         <v>20</v>
       </c>
       <c r="C489" t="s">
+        <v>605</v>
+      </c>
+      <c r="D489" t="s">
+        <v>606</v>
+      </c>
+      <c r="E489">
+        <v>0</v>
+      </c>
+      <c r="F489" t="s">
         <v>607</v>
-      </c>
-      <c r="D489" t="s">
-        <v>608</v>
-      </c>
-      <c r="E489">
-        <v>0</v>
-      </c>
-      <c r="F489" t="s">
-        <v>609</v>
       </c>
       <c r="G489">
         <v>0</v>
@@ -34868,7 +34868,7 @@
         <v>1</v>
       </c>
       <c r="J489" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K489" s="1" t="d">
         <v>2026-07-17</v>
@@ -34901,27 +34901,27 @@
         <v>27</v>
       </c>
       <c r="U489" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="490" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B490" t="s">
         <v>20</v>
       </c>
       <c r="C490" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D490" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E490">
         <v>0</v>
       </c>
       <c r="F490" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G490">
         <v>0</v>
@@ -34933,7 +34933,7 @@
         <v>1</v>
       </c>
       <c r="J490" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K490" s="1" t="d">
         <v>2026-07-17</v>
@@ -34966,27 +34966,27 @@
         <v>27</v>
       </c>
       <c r="U490" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="491" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B491" t="s">
         <v>20</v>
       </c>
       <c r="C491" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D491" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E491">
         <v>0</v>
       </c>
       <c r="F491" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G491">
         <v>0</v>
@@ -34998,7 +34998,7 @@
         <v>1</v>
       </c>
       <c r="J491" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K491" s="1" t="d">
         <v>2026-07-17</v>
@@ -35031,27 +35031,27 @@
         <v>27</v>
       </c>
       <c r="U491" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="492" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B492" t="s">
         <v>20</v>
       </c>
       <c r="C492" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D492" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E492">
         <v>0</v>
       </c>
       <c r="F492" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G492">
         <v>0</v>
@@ -35063,7 +35063,7 @@
         <v>1</v>
       </c>
       <c r="J492" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K492" s="1" t="d">
         <v>2026-07-17</v>
@@ -35096,27 +35096,27 @@
         <v>27</v>
       </c>
       <c r="U492" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="493" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B493" t="s">
         <v>20</v>
       </c>
       <c r="C493" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D493" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E493">
         <v>0</v>
       </c>
       <c r="F493" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G493">
         <v>0</v>
@@ -35128,7 +35128,7 @@
         <v>1</v>
       </c>
       <c r="J493" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K493" s="1" t="d">
         <v>2026-07-17</v>
@@ -35161,27 +35161,27 @@
         <v>27</v>
       </c>
       <c r="U493" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="494" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B494" t="s">
         <v>20</v>
       </c>
       <c r="C494" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D494" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E494">
         <v>0</v>
       </c>
       <c r="F494" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G494">
         <v>0</v>
@@ -35193,7 +35193,7 @@
         <v>1</v>
       </c>
       <c r="J494" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K494" s="1" t="d">
         <v>2026-07-17</v>
@@ -35226,27 +35226,27 @@
         <v>27</v>
       </c>
       <c r="U494" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="495" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B495" t="s">
         <v>20</v>
       </c>
       <c r="C495" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D495" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E495">
         <v>0</v>
       </c>
       <c r="F495" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G495">
         <v>0</v>
@@ -35258,7 +35258,7 @@
         <v>1</v>
       </c>
       <c r="J495" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K495" s="1" t="d">
         <v>2026-07-17</v>
@@ -35291,27 +35291,27 @@
         <v>27</v>
       </c>
       <c r="U495" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="496" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B496" t="s">
         <v>20</v>
       </c>
       <c r="C496" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D496" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E496">
         <v>0</v>
       </c>
       <c r="F496" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G496">
         <v>0</v>
@@ -35323,7 +35323,7 @@
         <v>1</v>
       </c>
       <c r="J496" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K496" s="1" t="d">
         <v>2026-07-17</v>
@@ -35356,27 +35356,27 @@
         <v>27</v>
       </c>
       <c r="U496" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="497" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
+        <v>597</v>
+      </c>
+      <c r="B497" t="s">
+        <v>20</v>
+      </c>
+      <c r="C497" t="s">
+        <v>623</v>
+      </c>
+      <c r="D497" t="s">
         <v>599</v>
       </c>
-      <c r="B497" t="s">
-        <v>20</v>
-      </c>
-      <c r="C497" t="s">
-        <v>625</v>
-      </c>
-      <c r="D497" t="s">
-        <v>601</v>
-      </c>
       <c r="E497">
         <v>0</v>
       </c>
       <c r="F497" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G497">
         <v>1</v>
@@ -35388,7 +35388,7 @@
         <v>1</v>
       </c>
       <c r="J497" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="K497" s="1" t="d">
         <v>2026-08-22</v>
@@ -35421,27 +35421,27 @@
         <v>27</v>
       </c>
       <c r="U497" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="498" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
+        <v>597</v>
+      </c>
+      <c r="B498" t="s">
+        <v>20</v>
+      </c>
+      <c r="C498" t="s">
+        <v>623</v>
+      </c>
+      <c r="D498" t="s">
         <v>599</v>
       </c>
-      <c r="B498" t="s">
-        <v>20</v>
-      </c>
-      <c r="C498" t="s">
-        <v>625</v>
-      </c>
-      <c r="D498" t="s">
-        <v>601</v>
-      </c>
       <c r="E498">
         <v>0</v>
       </c>
       <c r="F498" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G498">
         <v>1</v>
@@ -35453,7 +35453,7 @@
         <v>1</v>
       </c>
       <c r="J498" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="K498" s="1" t="d">
         <v>2026-08-24</v>
@@ -35486,27 +35486,27 @@
         <v>27</v>
       </c>
       <c r="U498" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="499" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
+        <v>597</v>
+      </c>
+      <c r="B499" t="s">
+        <v>20</v>
+      </c>
+      <c r="C499" t="s">
+        <v>623</v>
+      </c>
+      <c r="D499" t="s">
         <v>599</v>
       </c>
-      <c r="B499" t="s">
-        <v>20</v>
-      </c>
-      <c r="C499" t="s">
-        <v>625</v>
-      </c>
-      <c r="D499" t="s">
-        <v>601</v>
-      </c>
       <c r="E499">
         <v>0</v>
       </c>
       <c r="F499" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G499">
         <v>1</v>
@@ -35551,27 +35551,27 @@
         <v>27</v>
       </c>
       <c r="U499" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="500" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
+        <v>597</v>
+      </c>
+      <c r="B500" t="s">
+        <v>20</v>
+      </c>
+      <c r="C500" t="s">
+        <v>623</v>
+      </c>
+      <c r="D500" t="s">
         <v>599</v>
       </c>
-      <c r="B500" t="s">
-        <v>20</v>
-      </c>
-      <c r="C500" t="s">
-        <v>625</v>
-      </c>
-      <c r="D500" t="s">
-        <v>601</v>
-      </c>
       <c r="E500">
         <v>0</v>
       </c>
       <c r="F500" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G500">
         <v>1</v>
@@ -35616,27 +35616,27 @@
         <v>27</v>
       </c>
       <c r="U500" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="501" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
+        <v>597</v>
+      </c>
+      <c r="B501" t="s">
+        <v>20</v>
+      </c>
+      <c r="C501" t="s">
+        <v>623</v>
+      </c>
+      <c r="D501" t="s">
         <v>599</v>
       </c>
-      <c r="B501" t="s">
-        <v>20</v>
-      </c>
-      <c r="C501" t="s">
-        <v>625</v>
-      </c>
-      <c r="D501" t="s">
-        <v>601</v>
-      </c>
       <c r="E501">
         <v>0</v>
       </c>
       <c r="F501" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G501">
         <v>1</v>
@@ -35648,7 +35648,7 @@
         <v>1</v>
       </c>
       <c r="J501" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="K501" s="1" t="d">
         <v>2026-09-09</v>
@@ -35681,27 +35681,27 @@
         <v>27</v>
       </c>
       <c r="U501" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="502" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
+        <v>627</v>
+      </c>
+      <c r="B502" t="s">
+        <v>20</v>
+      </c>
+      <c r="C502" t="s">
+        <v>628</v>
+      </c>
+      <c r="D502" t="s">
         <v>629</v>
       </c>
-      <c r="B502" t="s">
-        <v>20</v>
-      </c>
-      <c r="C502" t="s">
+      <c r="E502">
+        <v>0</v>
+      </c>
+      <c r="F502" t="s">
         <v>630</v>
-      </c>
-      <c r="D502" t="s">
-        <v>631</v>
-      </c>
-      <c r="E502">
-        <v>0</v>
-      </c>
-      <c r="F502" t="s">
-        <v>632</v>
       </c>
       <c r="G502">
         <v>1</v>
@@ -35713,7 +35713,7 @@
         <v>1</v>
       </c>
       <c r="J502" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="K502" s="1" t="d">
         <v>2025-11-14</v>
@@ -35746,27 +35746,27 @@
         <v>27</v>
       </c>
       <c r="U502" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="503" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
+        <v>627</v>
+      </c>
+      <c r="B503" t="s">
+        <v>20</v>
+      </c>
+      <c r="C503" t="s">
+        <v>628</v>
+      </c>
+      <c r="D503" t="s">
         <v>629</v>
       </c>
-      <c r="B503" t="s">
-        <v>20</v>
-      </c>
-      <c r="C503" t="s">
+      <c r="E503">
+        <v>0</v>
+      </c>
+      <c r="F503" t="s">
         <v>630</v>
-      </c>
-      <c r="D503" t="s">
-        <v>631</v>
-      </c>
-      <c r="E503">
-        <v>0</v>
-      </c>
-      <c r="F503" t="s">
-        <v>632</v>
       </c>
       <c r="G503">
         <v>1</v>
@@ -35778,7 +35778,7 @@
         <v>1</v>
       </c>
       <c r="J503" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K503" s="1" t="d">
         <v>2026-02-18</v>
@@ -35811,27 +35811,27 @@
         <v>27</v>
       </c>
       <c r="U503" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="504" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
+        <v>627</v>
+      </c>
+      <c r="B504" t="s">
+        <v>20</v>
+      </c>
+      <c r="C504" t="s">
+        <v>628</v>
+      </c>
+      <c r="D504" t="s">
         <v>629</v>
       </c>
-      <c r="B504" t="s">
-        <v>20</v>
-      </c>
-      <c r="C504" t="s">
+      <c r="E504">
+        <v>0</v>
+      </c>
+      <c r="F504" t="s">
         <v>630</v>
-      </c>
-      <c r="D504" t="s">
-        <v>631</v>
-      </c>
-      <c r="E504">
-        <v>0</v>
-      </c>
-      <c r="F504" t="s">
-        <v>632</v>
       </c>
       <c r="G504">
         <v>1</v>
@@ -35843,7 +35843,7 @@
         <v>1</v>
       </c>
       <c r="J504" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K504" s="1" t="d">
         <v>2026-05-30</v>
@@ -35876,27 +35876,27 @@
         <v>27</v>
       </c>
       <c r="U504" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="505" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
+        <v>627</v>
+      </c>
+      <c r="B505" t="s">
+        <v>20</v>
+      </c>
+      <c r="C505" t="s">
+        <v>628</v>
+      </c>
+      <c r="D505" t="s">
         <v>629</v>
       </c>
-      <c r="B505" t="s">
-        <v>20</v>
-      </c>
-      <c r="C505" t="s">
+      <c r="E505">
+        <v>0</v>
+      </c>
+      <c r="F505" t="s">
         <v>630</v>
-      </c>
-      <c r="D505" t="s">
-        <v>631</v>
-      </c>
-      <c r="E505">
-        <v>0</v>
-      </c>
-      <c r="F505" t="s">
-        <v>632</v>
       </c>
       <c r="G505">
         <v>1</v>
@@ -35908,7 +35908,7 @@
         <v>1</v>
       </c>
       <c r="J505" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K505" s="1" t="d">
         <v>2026-05-30</v>
@@ -35941,39 +35941,39 @@
         <v>27</v>
       </c>
       <c r="U505" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="506" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
+        <v>635</v>
+      </c>
+      <c r="B506" t="s">
+        <v>20</v>
+      </c>
+      <c r="C506" t="s">
+        <v>636</v>
+      </c>
+      <c r="D506" t="s">
         <v>637</v>
       </c>
-      <c r="B506" t="s">
-        <v>20</v>
-      </c>
-      <c r="C506" t="s">
+      <c r="E506">
+        <v>0</v>
+      </c>
+      <c r="F506" t="s">
         <v>638</v>
       </c>
-      <c r="D506" t="s">
+      <c r="G506">
+        <v>1</v>
+      </c>
+      <c r="H506" t="s">
         <v>639</v>
       </c>
-      <c r="E506">
-        <v>0</v>
-      </c>
-      <c r="F506" t="s">
+      <c r="I506" t="b">
+        <v>0</v>
+      </c>
+      <c r="J506" t="s">
         <v>640</v>
-      </c>
-      <c r="G506">
-        <v>1</v>
-      </c>
-      <c r="H506" t="s">
-        <v>641</v>
-      </c>
-      <c r="I506" t="b">
-        <v>0</v>
-      </c>
-      <c r="J506" t="s">
-        <v>642</v>
       </c>
       <c r="K506" s="1" t="d">
         <v>2026-08-26</v>
@@ -36006,39 +36006,39 @@
         <v>27</v>
       </c>
       <c r="U506" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="507" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
+        <v>642</v>
+      </c>
+      <c r="B507" t="s">
+        <v>20</v>
+      </c>
+      <c r="C507" t="s">
+        <v>643</v>
+      </c>
+      <c r="D507" t="s">
         <v>644</v>
       </c>
-      <c r="B507" t="s">
-        <v>20</v>
-      </c>
-      <c r="C507" t="s">
+      <c r="E507">
+        <v>0</v>
+      </c>
+      <c r="F507" t="s">
         <v>645</v>
       </c>
-      <c r="D507" t="s">
+      <c r="G507">
+        <v>1</v>
+      </c>
+      <c r="H507" t="s">
         <v>646</v>
       </c>
-      <c r="E507">
-        <v>0</v>
-      </c>
-      <c r="F507" t="s">
+      <c r="I507" t="b">
+        <v>0</v>
+      </c>
+      <c r="J507" t="s">
         <v>647</v>
-      </c>
-      <c r="G507">
-        <v>1</v>
-      </c>
-      <c r="H507" t="s">
-        <v>648</v>
-      </c>
-      <c r="I507" t="b">
-        <v>0</v>
-      </c>
-      <c r="J507" t="s">
-        <v>649</v>
       </c>
       <c r="K507" s="1" t="d">
         <v>2025-05-19</v>
@@ -36071,39 +36071,39 @@
         <v>27</v>
       </c>
       <c r="U507" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="508" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
+        <v>642</v>
+      </c>
+      <c r="B508" t="s">
+        <v>20</v>
+      </c>
+      <c r="C508" t="s">
+        <v>649</v>
+      </c>
+      <c r="D508" t="s">
         <v>644</v>
       </c>
-      <c r="B508" t="s">
-        <v>20</v>
-      </c>
-      <c r="C508" t="s">
-        <v>651</v>
-      </c>
-      <c r="D508" t="s">
+      <c r="E508">
+        <v>0</v>
+      </c>
+      <c r="F508" t="s">
+        <v>650</v>
+      </c>
+      <c r="G508">
+        <v>0</v>
+      </c>
+      <c r="H508" t="s">
         <v>646</v>
       </c>
-      <c r="E508">
-        <v>0</v>
-      </c>
-      <c r="F508" t="s">
-        <v>652</v>
-      </c>
-      <c r="G508">
-        <v>0</v>
-      </c>
-      <c r="H508" t="s">
-        <v>648</v>
-      </c>
       <c r="I508" t="b">
         <v>0</v>
       </c>
       <c r="J508" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K508" s="1" t="d">
         <v>2025-05-19</v>
@@ -36136,39 +36136,39 @@
         <v>27</v>
       </c>
       <c r="U508" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="509" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
+        <v>642</v>
+      </c>
+      <c r="B509" t="s">
+        <v>20</v>
+      </c>
+      <c r="C509" t="s">
+        <v>651</v>
+      </c>
+      <c r="D509" t="s">
         <v>644</v>
       </c>
-      <c r="B509" t="s">
-        <v>20</v>
-      </c>
-      <c r="C509" t="s">
-        <v>653</v>
-      </c>
-      <c r="D509" t="s">
+      <c r="E509">
+        <v>0</v>
+      </c>
+      <c r="F509" t="s">
+        <v>652</v>
+      </c>
+      <c r="G509">
+        <v>0</v>
+      </c>
+      <c r="H509" t="s">
         <v>646</v>
       </c>
-      <c r="E509">
-        <v>0</v>
-      </c>
-      <c r="F509" t="s">
-        <v>654</v>
-      </c>
-      <c r="G509">
-        <v>0</v>
-      </c>
-      <c r="H509" t="s">
-        <v>648</v>
-      </c>
       <c r="I509" t="b">
         <v>0</v>
       </c>
       <c r="J509" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K509" s="1" t="d">
         <v>2025-05-19</v>
@@ -36201,39 +36201,39 @@
         <v>27</v>
       </c>
       <c r="U509" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="510" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B510" t="s">
         <v>20</v>
       </c>
       <c r="C510" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D510" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E510">
         <v>0</v>
       </c>
       <c r="F510" t="s">
+        <v>645</v>
+      </c>
+      <c r="G510">
+        <v>1</v>
+      </c>
+      <c r="H510" t="s">
+        <v>646</v>
+      </c>
+      <c r="I510" t="b">
+        <v>0</v>
+      </c>
+      <c r="J510" t="s">
         <v>647</v>
-      </c>
-      <c r="G510">
-        <v>1</v>
-      </c>
-      <c r="H510" t="s">
-        <v>648</v>
-      </c>
-      <c r="I510" t="b">
-        <v>0</v>
-      </c>
-      <c r="J510" t="s">
-        <v>649</v>
       </c>
       <c r="K510" s="1" t="d">
         <v>2025-05-19</v>
@@ -36266,39 +36266,39 @@
         <v>27</v>
       </c>
       <c r="U510" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="511" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B511" t="s">
         <v>20</v>
       </c>
       <c r="C511" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D511" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E511">
         <v>0</v>
       </c>
       <c r="F511" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G511">
         <v>0</v>
       </c>
       <c r="H511" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="I511" t="b">
         <v>0</v>
       </c>
       <c r="J511" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K511" s="1" t="d">
         <v>2025-05-19</v>
@@ -36331,39 +36331,39 @@
         <v>27</v>
       </c>
       <c r="U511" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="512" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B512" t="s">
         <v>20</v>
       </c>
       <c r="C512" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D512" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E512">
         <v>0</v>
       </c>
       <c r="F512" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G512">
         <v>0</v>
       </c>
       <c r="H512" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="I512" t="b">
         <v>0</v>
       </c>
       <c r="J512" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K512" s="1" t="d">
         <v>2025-05-19</v>
@@ -36396,39 +36396,39 @@
         <v>27</v>
       </c>
       <c r="U512" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="513" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B513" t="s">
         <v>20</v>
       </c>
       <c r="C513" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D513" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E513">
         <v>0</v>
       </c>
       <c r="F513" t="s">
+        <v>645</v>
+      </c>
+      <c r="G513">
+        <v>1</v>
+      </c>
+      <c r="H513" t="s">
+        <v>646</v>
+      </c>
+      <c r="I513" t="b">
+        <v>0</v>
+      </c>
+      <c r="J513" t="s">
         <v>647</v>
-      </c>
-      <c r="G513">
-        <v>1</v>
-      </c>
-      <c r="H513" t="s">
-        <v>648</v>
-      </c>
-      <c r="I513" t="b">
-        <v>0</v>
-      </c>
-      <c r="J513" t="s">
-        <v>649</v>
       </c>
       <c r="K513" s="1" t="d">
         <v>2025-05-19</v>
@@ -36461,39 +36461,39 @@
         <v>27</v>
       </c>
       <c r="U513" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="514" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B514" t="s">
         <v>20</v>
       </c>
       <c r="C514" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D514" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E514">
         <v>0</v>
       </c>
       <c r="F514" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G514">
         <v>0</v>
       </c>
       <c r="H514" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="I514" t="b">
         <v>0</v>
       </c>
       <c r="J514" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K514" s="1" t="d">
         <v>2025-05-19</v>
@@ -36526,39 +36526,39 @@
         <v>27</v>
       </c>
       <c r="U514" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="515" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B515" t="s">
         <v>20</v>
       </c>
       <c r="C515" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D515" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E515">
         <v>0</v>
       </c>
       <c r="F515" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G515">
         <v>0</v>
       </c>
       <c r="H515" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="I515" t="b">
         <v>0</v>
       </c>
       <c r="J515" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="K515" s="1" t="d">
         <v>2025-05-19</v>
@@ -36591,27 +36591,27 @@
         <v>27</v>
       </c>
       <c r="U515" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="516" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
+        <v>642</v>
+      </c>
+      <c r="B516" t="s">
+        <v>20</v>
+      </c>
+      <c r="C516" t="s">
+        <v>643</v>
+      </c>
+      <c r="D516" t="s">
         <v>644</v>
       </c>
-      <c r="B516" t="s">
-        <v>20</v>
-      </c>
-      <c r="C516" t="s">
+      <c r="E516">
+        <v>0</v>
+      </c>
+      <c r="F516" t="s">
         <v>645</v>
-      </c>
-      <c r="D516" t="s">
-        <v>646</v>
-      </c>
-      <c r="E516">
-        <v>0</v>
-      </c>
-      <c r="F516" t="s">
-        <v>647</v>
       </c>
       <c r="G516">
         <v>1</v>
@@ -36623,7 +36623,7 @@
         <v>0</v>
       </c>
       <c r="J516" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K516" s="1" t="d">
         <v>2025-08-12</v>
@@ -36656,27 +36656,27 @@
         <v>27</v>
       </c>
       <c r="U516" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="517" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
+        <v>642</v>
+      </c>
+      <c r="B517" t="s">
+        <v>20</v>
+      </c>
+      <c r="C517" t="s">
+        <v>649</v>
+      </c>
+      <c r="D517" t="s">
         <v>644</v>
       </c>
-      <c r="B517" t="s">
-        <v>20</v>
-      </c>
-      <c r="C517" t="s">
-        <v>651</v>
-      </c>
-      <c r="D517" t="s">
-        <v>646</v>
-      </c>
       <c r="E517">
         <v>0</v>
       </c>
       <c r="F517" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G517">
         <v>0</v>
@@ -36688,7 +36688,7 @@
         <v>0</v>
       </c>
       <c r="J517" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K517" s="1" t="d">
         <v>2025-08-12</v>
@@ -36721,27 +36721,27 @@
         <v>27</v>
       </c>
       <c r="U517" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="518" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
+        <v>642</v>
+      </c>
+      <c r="B518" t="s">
+        <v>20</v>
+      </c>
+      <c r="C518" t="s">
+        <v>649</v>
+      </c>
+      <c r="D518" t="s">
         <v>644</v>
       </c>
-      <c r="B518" t="s">
-        <v>20</v>
-      </c>
-      <c r="C518" t="s">
-        <v>651</v>
-      </c>
-      <c r="D518" t="s">
-        <v>646</v>
-      </c>
       <c r="E518">
         <v>0</v>
       </c>
       <c r="F518" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G518">
         <v>0</v>
@@ -36753,7 +36753,7 @@
         <v>1</v>
       </c>
       <c r="J518" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="K518" s="1" t="d">
         <v>2025-08-18</v>
@@ -36786,27 +36786,27 @@
         <v>27</v>
       </c>
       <c r="U518" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="519" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
+        <v>642</v>
+      </c>
+      <c r="B519" t="s">
+        <v>20</v>
+      </c>
+      <c r="C519" t="s">
+        <v>649</v>
+      </c>
+      <c r="D519" t="s">
         <v>644</v>
       </c>
-      <c r="B519" t="s">
-        <v>20</v>
-      </c>
-      <c r="C519" t="s">
-        <v>651</v>
-      </c>
-      <c r="D519" t="s">
-        <v>646</v>
-      </c>
       <c r="E519">
         <v>0</v>
       </c>
       <c r="F519" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G519">
         <v>0</v>
@@ -36818,7 +36818,7 @@
         <v>1</v>
       </c>
       <c r="J519" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="K519" s="1" t="d">
         <v>2025-08-18</v>
@@ -36851,39 +36851,39 @@
         <v>27</v>
       </c>
       <c r="U519" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="520" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B520" t="s">
         <v>20</v>
       </c>
       <c r="C520" t="s">
+        <v>662</v>
+      </c>
+      <c r="D520" t="s">
+        <v>663</v>
+      </c>
+      <c r="E520">
+        <v>0</v>
+      </c>
+      <c r="F520" t="s">
+        <v>650</v>
+      </c>
+      <c r="G520">
+        <v>0</v>
+      </c>
+      <c r="H520" t="s">
         <v>664</v>
       </c>
-      <c r="D520" t="s">
+      <c r="I520" t="b">
+        <v>0</v>
+      </c>
+      <c r="J520" t="s">
         <v>665</v>
-      </c>
-      <c r="E520">
-        <v>0</v>
-      </c>
-      <c r="F520" t="s">
-        <v>652</v>
-      </c>
-      <c r="G520">
-        <v>0</v>
-      </c>
-      <c r="H520" t="s">
-        <v>666</v>
-      </c>
-      <c r="I520" t="b">
-        <v>0</v>
-      </c>
-      <c r="J520" t="s">
-        <v>667</v>
       </c>
       <c r="K520" s="1" t="d">
         <v>2025-09-24</v>
@@ -36916,39 +36916,39 @@
         <v>27</v>
       </c>
       <c r="U520" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="521" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B521" t="s">
         <v>20</v>
       </c>
       <c r="C521" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D521" t="s">
+        <v>663</v>
+      </c>
+      <c r="E521">
+        <v>0</v>
+      </c>
+      <c r="F521" t="s">
+        <v>645</v>
+      </c>
+      <c r="G521">
+        <v>1</v>
+      </c>
+      <c r="H521" t="s">
+        <v>664</v>
+      </c>
+      <c r="I521" t="b">
+        <v>0</v>
+      </c>
+      <c r="J521" t="s">
         <v>665</v>
-      </c>
-      <c r="E521">
-        <v>0</v>
-      </c>
-      <c r="F521" t="s">
-        <v>647</v>
-      </c>
-      <c r="G521">
-        <v>1</v>
-      </c>
-      <c r="H521" t="s">
-        <v>666</v>
-      </c>
-      <c r="I521" t="b">
-        <v>0</v>
-      </c>
-      <c r="J521" t="s">
-        <v>667</v>
       </c>
       <c r="K521" s="1" t="d">
         <v>2025-09-24</v>
@@ -36981,39 +36981,39 @@
         <v>27</v>
       </c>
       <c r="U521" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="522" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
+        <v>642</v>
+      </c>
+      <c r="B522" t="s">
+        <v>20</v>
+      </c>
+      <c r="C522" t="s">
+        <v>643</v>
+      </c>
+      <c r="D522" t="s">
         <v>644</v>
       </c>
-      <c r="B522" t="s">
-        <v>20</v>
-      </c>
-      <c r="C522" t="s">
+      <c r="E522">
+        <v>0</v>
+      </c>
+      <c r="F522" t="s">
         <v>645</v>
       </c>
-      <c r="D522" t="s">
-        <v>646</v>
-      </c>
-      <c r="E522">
-        <v>0</v>
-      </c>
-      <c r="F522" t="s">
-        <v>647</v>
-      </c>
       <c r="G522">
         <v>1</v>
       </c>
       <c r="H522" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I522" t="b">
         <v>0</v>
       </c>
       <c r="J522" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K522" s="1" t="d">
         <v>2025-09-24</v>
@@ -37046,39 +37046,39 @@
         <v>27</v>
       </c>
       <c r="U522" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="523" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>642</v>
+      </c>
+      <c r="B523" t="s">
+        <v>20</v>
+      </c>
+      <c r="C523" t="s">
+        <v>649</v>
+      </c>
+      <c r="D523" t="s">
         <v>644</v>
       </c>
-      <c r="B523" t="s">
-        <v>20</v>
-      </c>
-      <c r="C523" t="s">
-        <v>651</v>
-      </c>
-      <c r="D523" t="s">
-        <v>646</v>
-      </c>
       <c r="E523">
         <v>0</v>
       </c>
       <c r="F523" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G523">
         <v>0</v>
       </c>
       <c r="H523" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I523" t="b">
         <v>0</v>
       </c>
       <c r="J523" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K523" s="1" t="d">
         <v>2025-09-24</v>
@@ -37111,39 +37111,39 @@
         <v>27</v>
       </c>
       <c r="U523" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="524" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
+        <v>642</v>
+      </c>
+      <c r="B524" t="s">
+        <v>20</v>
+      </c>
+      <c r="C524" t="s">
+        <v>651</v>
+      </c>
+      <c r="D524" t="s">
         <v>644</v>
       </c>
-      <c r="B524" t="s">
-        <v>20</v>
-      </c>
-      <c r="C524" t="s">
-        <v>653</v>
-      </c>
-      <c r="D524" t="s">
-        <v>646</v>
-      </c>
       <c r="E524">
         <v>0</v>
       </c>
       <c r="F524" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G524">
         <v>0</v>
       </c>
       <c r="H524" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I524" t="b">
         <v>0</v>
       </c>
       <c r="J524" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K524" s="1" t="d">
         <v>2025-09-24</v>
@@ -37176,39 +37176,39 @@
         <v>27</v>
       </c>
       <c r="U524" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="525" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B525" t="s">
         <v>20</v>
       </c>
       <c r="C525" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D525" t="s">
+        <v>663</v>
+      </c>
+      <c r="E525">
+        <v>0</v>
+      </c>
+      <c r="F525" t="s">
+        <v>652</v>
+      </c>
+      <c r="G525">
+        <v>0</v>
+      </c>
+      <c r="H525" t="s">
+        <v>664</v>
+      </c>
+      <c r="I525" t="b">
+        <v>0</v>
+      </c>
+      <c r="J525" t="s">
         <v>665</v>
-      </c>
-      <c r="E525">
-        <v>0</v>
-      </c>
-      <c r="F525" t="s">
-        <v>654</v>
-      </c>
-      <c r="G525">
-        <v>0</v>
-      </c>
-      <c r="H525" t="s">
-        <v>666</v>
-      </c>
-      <c r="I525" t="b">
-        <v>0</v>
-      </c>
-      <c r="J525" t="s">
-        <v>667</v>
       </c>
       <c r="K525" s="1" t="d">
         <v>2025-09-24</v>
@@ -37241,39 +37241,39 @@
         <v>27</v>
       </c>
       <c r="U525" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="526" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B526" t="s">
         <v>20</v>
       </c>
       <c r="C526" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D526" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E526">
         <v>0</v>
       </c>
       <c r="F526" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G526">
         <v>0</v>
       </c>
       <c r="H526" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I526" t="b">
         <v>0</v>
       </c>
       <c r="J526" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K526" s="1" t="d">
         <v>2025-10-01</v>
@@ -37306,39 +37306,39 @@
         <v>27</v>
       </c>
       <c r="U526" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="527" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B527" t="s">
         <v>20</v>
       </c>
       <c r="C527" t="s">
+        <v>666</v>
+      </c>
+      <c r="D527" t="s">
+        <v>663</v>
+      </c>
+      <c r="E527">
+        <v>0</v>
+      </c>
+      <c r="F527" t="s">
+        <v>645</v>
+      </c>
+      <c r="G527">
+        <v>1</v>
+      </c>
+      <c r="H527" t="s">
         <v>668</v>
       </c>
-      <c r="D527" t="s">
-        <v>665</v>
-      </c>
-      <c r="E527">
-        <v>0</v>
-      </c>
-      <c r="F527" t="s">
-        <v>647</v>
-      </c>
-      <c r="G527">
-        <v>1</v>
-      </c>
-      <c r="H527" t="s">
-        <v>670</v>
-      </c>
       <c r="I527" t="b">
         <v>0</v>
       </c>
       <c r="J527" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K527" s="1" t="d">
         <v>2025-10-01</v>
@@ -37371,39 +37371,39 @@
         <v>27</v>
       </c>
       <c r="U527" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="528" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B528" t="s">
         <v>20</v>
       </c>
       <c r="C528" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D528" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E528">
         <v>0</v>
       </c>
       <c r="F528" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G528">
         <v>1</v>
       </c>
       <c r="H528" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I528" t="b">
         <v>0</v>
       </c>
       <c r="J528" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K528" s="1" t="d">
         <v>2025-10-01</v>
@@ -37436,39 +37436,39 @@
         <v>27</v>
       </c>
       <c r="U528" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="529" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B529" t="s">
         <v>20</v>
       </c>
       <c r="C529" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D529" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E529">
         <v>0</v>
       </c>
       <c r="F529" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G529">
         <v>0</v>
       </c>
       <c r="H529" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I529" t="b">
         <v>0</v>
       </c>
       <c r="J529" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K529" s="1" t="d">
         <v>2025-10-01</v>
@@ -37501,39 +37501,39 @@
         <v>27</v>
       </c>
       <c r="U529" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="530" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
+        <v>642</v>
+      </c>
+      <c r="B530" t="s">
+        <v>20</v>
+      </c>
+      <c r="C530" t="s">
+        <v>643</v>
+      </c>
+      <c r="D530" t="s">
         <v>644</v>
       </c>
-      <c r="B530" t="s">
-        <v>20</v>
-      </c>
-      <c r="C530" t="s">
+      <c r="E530">
+        <v>0</v>
+      </c>
+      <c r="F530" t="s">
         <v>645</v>
       </c>
-      <c r="D530" t="s">
-        <v>646</v>
-      </c>
-      <c r="E530">
-        <v>0</v>
-      </c>
-      <c r="F530" t="s">
-        <v>647</v>
-      </c>
       <c r="G530">
         <v>1</v>
       </c>
       <c r="H530" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I530" t="b">
         <v>0</v>
       </c>
       <c r="J530" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K530" s="1" t="d">
         <v>2025-10-01</v>
@@ -37566,39 +37566,39 @@
         <v>27</v>
       </c>
       <c r="U530" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="531" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
+        <v>642</v>
+      </c>
+      <c r="B531" t="s">
+        <v>20</v>
+      </c>
+      <c r="C531" t="s">
+        <v>649</v>
+      </c>
+      <c r="D531" t="s">
         <v>644</v>
       </c>
-      <c r="B531" t="s">
-        <v>20</v>
-      </c>
-      <c r="C531" t="s">
-        <v>651</v>
-      </c>
-      <c r="D531" t="s">
-        <v>646</v>
-      </c>
       <c r="E531">
         <v>0</v>
       </c>
       <c r="F531" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G531">
         <v>0</v>
       </c>
       <c r="H531" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I531" t="b">
         <v>0</v>
       </c>
       <c r="J531" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K531" s="1" t="d">
         <v>2025-10-01</v>
@@ -37631,39 +37631,39 @@
         <v>27</v>
       </c>
       <c r="U531" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="532" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
+        <v>642</v>
+      </c>
+      <c r="B532" t="s">
+        <v>20</v>
+      </c>
+      <c r="C532" t="s">
+        <v>651</v>
+      </c>
+      <c r="D532" t="s">
         <v>644</v>
       </c>
-      <c r="B532" t="s">
-        <v>20</v>
-      </c>
-      <c r="C532" t="s">
-        <v>653</v>
-      </c>
-      <c r="D532" t="s">
-        <v>646</v>
-      </c>
       <c r="E532">
         <v>0</v>
       </c>
       <c r="F532" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G532">
         <v>0</v>
       </c>
       <c r="H532" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I532" t="b">
         <v>0</v>
       </c>
       <c r="J532" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K532" s="1" t="d">
         <v>2025-10-01</v>
@@ -37696,39 +37696,39 @@
         <v>27</v>
       </c>
       <c r="U532" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="533" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B533" t="s">
         <v>20</v>
       </c>
       <c r="C533" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D533" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E533">
         <v>0</v>
       </c>
       <c r="F533" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G533">
         <v>0</v>
       </c>
       <c r="H533" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I533" t="b">
         <v>0</v>
       </c>
       <c r="J533" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K533" s="1" t="d">
         <v>2025-10-01</v>
@@ -37761,39 +37761,39 @@
         <v>27</v>
       </c>
       <c r="U533" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="534" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B534" t="s">
         <v>20</v>
       </c>
       <c r="C534" t="s">
+        <v>667</v>
+      </c>
+      <c r="D534" t="s">
+        <v>663</v>
+      </c>
+      <c r="E534">
+        <v>0</v>
+      </c>
+      <c r="F534" t="s">
+        <v>652</v>
+      </c>
+      <c r="G534">
+        <v>0</v>
+      </c>
+      <c r="H534" t="s">
+        <v>668</v>
+      </c>
+      <c r="I534" t="b">
+        <v>0</v>
+      </c>
+      <c r="J534" t="s">
         <v>669</v>
-      </c>
-      <c r="D534" t="s">
-        <v>665</v>
-      </c>
-      <c r="E534">
-        <v>0</v>
-      </c>
-      <c r="F534" t="s">
-        <v>654</v>
-      </c>
-      <c r="G534">
-        <v>0</v>
-      </c>
-      <c r="H534" t="s">
-        <v>670</v>
-      </c>
-      <c r="I534" t="b">
-        <v>0</v>
-      </c>
-      <c r="J534" t="s">
-        <v>671</v>
       </c>
       <c r="K534" s="1" t="d">
         <v>2025-10-01</v>
@@ -37826,39 +37826,39 @@
         <v>27</v>
       </c>
       <c r="U534" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="535" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B535" t="s">
         <v>20</v>
       </c>
       <c r="C535" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D535" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E535">
         <v>0</v>
       </c>
       <c r="F535" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G535">
         <v>1</v>
       </c>
       <c r="H535" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I535" t="b">
         <v>0</v>
       </c>
       <c r="J535" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K535" s="1" t="d">
         <v>2025-10-01</v>
@@ -37891,39 +37891,39 @@
         <v>27</v>
       </c>
       <c r="U535" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="536" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B536" t="s">
         <v>20</v>
       </c>
       <c r="C536" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D536" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E536">
         <v>0</v>
       </c>
       <c r="F536" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G536">
         <v>0</v>
       </c>
       <c r="H536" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I536" t="b">
         <v>0</v>
       </c>
       <c r="J536" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K536" s="1" t="d">
         <v>2025-10-01</v>
@@ -37956,39 +37956,39 @@
         <v>27</v>
       </c>
       <c r="U536" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="537" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B537" t="s">
         <v>20</v>
       </c>
       <c r="C537" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D537" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E537">
         <v>0</v>
       </c>
       <c r="F537" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G537">
         <v>0</v>
       </c>
       <c r="H537" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I537" t="b">
         <v>0</v>
       </c>
       <c r="J537" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K537" s="1" t="d">
         <v>2025-10-01</v>
@@ -38021,39 +38021,39 @@
         <v>27</v>
       </c>
       <c r="U537" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="538" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B538" t="s">
         <v>20</v>
       </c>
       <c r="C538" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D538" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E538">
         <v>0</v>
       </c>
       <c r="F538" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G538">
         <v>0</v>
       </c>
       <c r="H538" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="I538" t="b">
         <v>1</v>
       </c>
       <c r="J538" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="K538" s="1" t="d">
         <v>2025-11-17</v>
@@ -38086,39 +38086,39 @@
         <v>27</v>
       </c>
       <c r="U538" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="539" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B539" t="s">
         <v>20</v>
       </c>
       <c r="C539" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D539" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E539">
         <v>0</v>
       </c>
       <c r="F539" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G539">
         <v>1</v>
       </c>
       <c r="H539" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="I539" t="b">
         <v>1</v>
       </c>
       <c r="J539" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="K539" s="1" t="d">
         <v>2025-11-17</v>
@@ -38151,39 +38151,39 @@
         <v>27</v>
       </c>
       <c r="U539" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="540" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
+        <v>642</v>
+      </c>
+      <c r="B540" t="s">
+        <v>20</v>
+      </c>
+      <c r="C540" t="s">
+        <v>643</v>
+      </c>
+      <c r="D540" t="s">
         <v>644</v>
       </c>
-      <c r="B540" t="s">
-        <v>20</v>
-      </c>
-      <c r="C540" t="s">
+      <c r="E540">
+        <v>0</v>
+      </c>
+      <c r="F540" t="s">
         <v>645</v>
       </c>
-      <c r="D540" t="s">
-        <v>646</v>
-      </c>
-      <c r="E540">
-        <v>0</v>
-      </c>
-      <c r="F540" t="s">
-        <v>647</v>
-      </c>
       <c r="G540">
         <v>1</v>
       </c>
       <c r="H540" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="I540" t="b">
         <v>1</v>
       </c>
       <c r="J540" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="K540" s="1" t="d">
         <v>2025-11-17</v>
@@ -38216,39 +38216,39 @@
         <v>27</v>
       </c>
       <c r="U540" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="541" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
+        <v>642</v>
+      </c>
+      <c r="B541" t="s">
+        <v>20</v>
+      </c>
+      <c r="C541" t="s">
+        <v>649</v>
+      </c>
+      <c r="D541" t="s">
         <v>644</v>
       </c>
-      <c r="B541" t="s">
-        <v>20</v>
-      </c>
-      <c r="C541" t="s">
-        <v>651</v>
-      </c>
-      <c r="D541" t="s">
-        <v>646</v>
-      </c>
       <c r="E541">
         <v>0</v>
       </c>
       <c r="F541" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G541">
         <v>0</v>
       </c>
       <c r="H541" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="I541" t="b">
         <v>1</v>
       </c>
       <c r="J541" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="K541" s="1" t="d">
         <v>2025-11-17</v>
@@ -38281,27 +38281,27 @@
         <v>27</v>
       </c>
       <c r="U541" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="542" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B542" t="s">
         <v>20</v>
       </c>
       <c r="C542" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D542" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E542">
         <v>0</v>
       </c>
       <c r="F542" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G542">
         <v>1</v>
@@ -38313,7 +38313,7 @@
         <v>1</v>
       </c>
       <c r="J542" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="K542" s="1" t="d">
         <v>2025-11-26</v>
@@ -38346,27 +38346,27 @@
         <v>27</v>
       </c>
       <c r="U542" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="543" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B543" t="s">
         <v>20</v>
       </c>
       <c r="C543" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D543" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E543">
         <v>0</v>
       </c>
       <c r="F543" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G543">
         <v>0</v>
@@ -38378,7 +38378,7 @@
         <v>1</v>
       </c>
       <c r="J543" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="K543" s="1" t="d">
         <v>2025-11-26</v>
@@ -38411,27 +38411,27 @@
         <v>27</v>
       </c>
       <c r="U543" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="544" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B544" t="s">
         <v>20</v>
       </c>
       <c r="C544" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D544" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E544">
         <v>0</v>
       </c>
       <c r="F544" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G544">
         <v>0</v>
@@ -38443,7 +38443,7 @@
         <v>0</v>
       </c>
       <c r="J544" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K544" s="1" t="d">
         <v>2026-01-12</v>
@@ -38476,27 +38476,27 @@
         <v>27</v>
       </c>
       <c r="U544" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="545" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B545" t="s">
         <v>20</v>
       </c>
       <c r="C545" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D545" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E545">
         <v>0</v>
       </c>
       <c r="F545" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G545">
         <v>1</v>
@@ -38508,7 +38508,7 @@
         <v>0</v>
       </c>
       <c r="J545" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K545" s="1" t="d">
         <v>2026-01-12</v>
@@ -38541,27 +38541,27 @@
         <v>27</v>
       </c>
       <c r="U545" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="546" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B546" t="s">
         <v>20</v>
       </c>
       <c r="C546" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D546" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E546">
         <v>0</v>
       </c>
       <c r="F546" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G546">
         <v>1</v>
@@ -38573,7 +38573,7 @@
         <v>0</v>
       </c>
       <c r="J546" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K546" s="1" t="d">
         <v>2026-01-12</v>
@@ -38606,27 +38606,27 @@
         <v>27</v>
       </c>
       <c r="U546" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="547" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B547" t="s">
         <v>20</v>
       </c>
       <c r="C547" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D547" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E547">
         <v>0</v>
       </c>
       <c r="F547" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G547">
         <v>0</v>
@@ -38638,7 +38638,7 @@
         <v>0</v>
       </c>
       <c r="J547" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K547" s="1" t="d">
         <v>2026-01-12</v>
@@ -38671,27 +38671,27 @@
         <v>27</v>
       </c>
       <c r="U547" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="548" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B548" t="s">
         <v>20</v>
       </c>
       <c r="C548" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D548" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E548">
         <v>0</v>
       </c>
       <c r="F548" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G548">
         <v>0</v>
@@ -38703,7 +38703,7 @@
         <v>0</v>
       </c>
       <c r="J548" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K548" s="1" t="d">
         <v>2026-01-12</v>
@@ -38736,27 +38736,27 @@
         <v>27</v>
       </c>
       <c r="U548" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="549" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B549" t="s">
         <v>20</v>
       </c>
       <c r="C549" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D549" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E549">
         <v>0</v>
       </c>
       <c r="F549" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G549">
         <v>0</v>
@@ -38768,7 +38768,7 @@
         <v>0</v>
       </c>
       <c r="J549" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K549" s="1" t="d">
         <v>2026-01-12</v>
@@ -38801,39 +38801,39 @@
         <v>27</v>
       </c>
       <c r="U549" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="550" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B550" t="s">
         <v>20</v>
       </c>
       <c r="C550" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D550" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E550">
         <v>0</v>
       </c>
       <c r="F550" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G550">
         <v>0</v>
       </c>
       <c r="H550" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I550" t="b">
         <v>0</v>
       </c>
       <c r="J550" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K550" s="1" t="d">
         <v>2026-01-31</v>
@@ -38866,39 +38866,39 @@
         <v>27</v>
       </c>
       <c r="U550" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="551" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B551" t="s">
         <v>20</v>
       </c>
       <c r="C551" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D551" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E551">
         <v>0</v>
       </c>
       <c r="F551" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G551">
         <v>1</v>
       </c>
       <c r="H551" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I551" t="b">
         <v>0</v>
       </c>
       <c r="J551" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K551" s="1" t="d">
         <v>2026-01-31</v>
@@ -38931,39 +38931,39 @@
         <v>27</v>
       </c>
       <c r="U551" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="552" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B552" t="s">
         <v>20</v>
       </c>
       <c r="C552" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D552" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E552">
         <v>0</v>
       </c>
       <c r="F552" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G552">
         <v>1</v>
       </c>
       <c r="H552" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I552" t="b">
         <v>0</v>
       </c>
       <c r="J552" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K552" s="1" t="d">
         <v>2026-01-31</v>
@@ -38996,39 +38996,39 @@
         <v>27</v>
       </c>
       <c r="U552" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="553" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B553" t="s">
         <v>20</v>
       </c>
       <c r="C553" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D553" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E553">
         <v>0</v>
       </c>
       <c r="F553" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G553">
         <v>0</v>
       </c>
       <c r="H553" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I553" t="b">
         <v>0</v>
       </c>
       <c r="J553" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K553" s="1" t="d">
         <v>2026-01-31</v>
@@ -39061,39 +39061,39 @@
         <v>27</v>
       </c>
       <c r="U553" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="554" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B554" t="s">
         <v>20</v>
       </c>
       <c r="C554" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D554" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E554">
         <v>0</v>
       </c>
       <c r="F554" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G554">
         <v>0</v>
       </c>
       <c r="H554" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I554" t="b">
         <v>0</v>
       </c>
       <c r="J554" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K554" s="1" t="d">
         <v>2026-01-31</v>
@@ -39126,39 +39126,39 @@
         <v>27</v>
       </c>
       <c r="U554" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="555" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B555" t="s">
         <v>20</v>
       </c>
       <c r="C555" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D555" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E555">
         <v>0</v>
       </c>
       <c r="F555" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G555">
         <v>0</v>
       </c>
       <c r="H555" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="I555" t="b">
         <v>0</v>
       </c>
       <c r="J555" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K555" s="1" t="d">
         <v>2026-01-31</v>
@@ -39191,27 +39191,27 @@
         <v>27</v>
       </c>
       <c r="U555" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="556" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B556" t="s">
         <v>20</v>
       </c>
       <c r="C556" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D556" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E556">
         <v>0</v>
       </c>
       <c r="F556" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G556">
         <v>0</v>
@@ -39223,7 +39223,7 @@
         <v>1</v>
       </c>
       <c r="J556" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K556" s="1" t="d">
         <v>2026-02-12</v>
@@ -39256,27 +39256,27 @@
         <v>27</v>
       </c>
       <c r="U556" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="557" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B557" t="s">
         <v>20</v>
       </c>
       <c r="C557" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D557" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E557">
         <v>0</v>
       </c>
       <c r="F557" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G557">
         <v>0</v>
@@ -39288,7 +39288,7 @@
         <v>1</v>
       </c>
       <c r="J557" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="K557" s="1" t="d">
         <v>2026-03-05</v>
@@ -39321,27 +39321,27 @@
         <v>27</v>
       </c>
       <c r="U557" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="558" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B558" t="s">
         <v>20</v>
       </c>
       <c r="C558" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D558" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E558">
         <v>0</v>
       </c>
       <c r="F558" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G558">
         <v>1</v>
@@ -39353,7 +39353,7 @@
         <v>1</v>
       </c>
       <c r="J558" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="K558" s="1" t="d">
         <v>2026-03-05</v>
@@ -39386,27 +39386,27 @@
         <v>27</v>
       </c>
       <c r="U558" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="559" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B559" t="s">
         <v>20</v>
       </c>
       <c r="C559" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D559" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E559">
         <v>0</v>
       </c>
       <c r="F559" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G559">
         <v>0</v>
@@ -39418,7 +39418,7 @@
         <v>1</v>
       </c>
       <c r="J559" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K559" s="1" t="d">
         <v>2026-03-17</v>
@@ -39451,27 +39451,27 @@
         <v>27</v>
       </c>
       <c r="U559" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="560" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B560" t="s">
         <v>20</v>
       </c>
       <c r="C560" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D560" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E560">
         <v>0</v>
       </c>
       <c r="F560" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G560">
         <v>1</v>
@@ -39483,7 +39483,7 @@
         <v>1</v>
       </c>
       <c r="J560" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K560" s="1" t="d">
         <v>2026-03-17</v>
@@ -39516,39 +39516,39 @@
         <v>27</v>
       </c>
       <c r="U560" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="561" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B561" t="s">
         <v>20</v>
       </c>
       <c r="C561" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D561" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E561">
         <v>0</v>
       </c>
       <c r="F561" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G561">
         <v>0</v>
       </c>
       <c r="H561" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I561" t="b">
         <v>1</v>
       </c>
       <c r="J561" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="K561" s="1" t="d">
         <v>2026-04-20</v>
@@ -39581,39 +39581,39 @@
         <v>27</v>
       </c>
       <c r="U561" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="562" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B562" t="s">
         <v>20</v>
       </c>
       <c r="C562" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D562" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E562">
         <v>0</v>
       </c>
       <c r="F562" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G562">
         <v>0</v>
       </c>
       <c r="H562" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="I562" t="b">
         <v>0</v>
       </c>
       <c r="J562" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="K562" s="1" t="d">
         <v>2026-04-20</v>
@@ -39646,39 +39646,39 @@
         <v>27</v>
       </c>
       <c r="U562" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="563" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B563" t="s">
         <v>20</v>
       </c>
       <c r="C563" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D563" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E563">
         <v>0</v>
       </c>
       <c r="F563" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G563">
         <v>1</v>
       </c>
       <c r="H563" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I563" t="b">
         <v>1</v>
       </c>
       <c r="J563" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="K563" s="1" t="d">
         <v>2026-04-20</v>
@@ -39711,39 +39711,39 @@
         <v>27</v>
       </c>
       <c r="U563" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="564" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B564" t="s">
         <v>20</v>
       </c>
       <c r="C564" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D564" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E564">
         <v>0</v>
       </c>
       <c r="F564" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G564">
         <v>1</v>
       </c>
       <c r="H564" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="I564" t="b">
         <v>0</v>
       </c>
       <c r="J564" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="K564" s="1" t="d">
         <v>2026-04-20</v>
@@ -39776,39 +39776,39 @@
         <v>27</v>
       </c>
       <c r="U564" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="565" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B565" t="s">
         <v>20</v>
       </c>
       <c r="C565" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D565" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E565">
         <v>0</v>
       </c>
       <c r="F565" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G565">
         <v>0</v>
       </c>
       <c r="H565" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="I565" t="b">
         <v>0</v>
       </c>
       <c r="J565" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="K565" s="1" t="d">
         <v>2026-05-06</v>
@@ -39841,39 +39841,39 @@
         <v>27</v>
       </c>
       <c r="U565" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="566" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B566" t="s">
         <v>20</v>
       </c>
       <c r="C566" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D566" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E566">
         <v>0</v>
       </c>
       <c r="F566" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G566">
         <v>1</v>
       </c>
       <c r="H566" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="I566" t="b">
         <v>0</v>
       </c>
       <c r="J566" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="K566" s="1" t="d">
         <v>2026-05-06</v>
@@ -39906,27 +39906,27 @@
         <v>27</v>
       </c>
       <c r="U566" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="567" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B567" t="s">
         <v>20</v>
       </c>
       <c r="C567" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D567" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E567">
         <v>0</v>
       </c>
       <c r="F567" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G567">
         <v>0</v>
@@ -39938,7 +39938,7 @@
         <v>1</v>
       </c>
       <c r="J567" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="K567" s="1" t="d">
         <v>2026-05-23</v>
@@ -39971,39 +39971,39 @@
         <v>27</v>
       </c>
       <c r="U567" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="568" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B568" t="s">
         <v>20</v>
       </c>
       <c r="C568" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D568" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E568">
         <v>0</v>
       </c>
       <c r="F568" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G568">
         <v>0</v>
       </c>
       <c r="H568" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I568" t="b">
         <v>1</v>
       </c>
       <c r="J568" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K568" s="1" t="d">
         <v>2026-05-28</v>
@@ -40036,33 +40036,33 @@
         <v>27</v>
       </c>
       <c r="U568" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="569" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B569" t="s">
         <v>20</v>
       </c>
       <c r="C569" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D569" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E569">
         <v>0</v>
       </c>
       <c r="F569" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G569">
         <v>0</v>
       </c>
       <c r="H569" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="I569" t="b">
         <v>0</v>
@@ -40101,39 +40101,39 @@
         <v>27</v>
       </c>
       <c r="U569" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="570" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B570" t="s">
         <v>20</v>
       </c>
       <c r="C570" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D570" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E570">
         <v>0</v>
       </c>
       <c r="F570" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G570">
         <v>0</v>
       </c>
       <c r="H570" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="I570" t="b">
         <v>0</v>
       </c>
       <c r="J570" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K570" s="1" t="d">
         <v>2026-06-04</v>
@@ -40166,39 +40166,39 @@
         <v>27</v>
       </c>
       <c r="U570" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="571" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B571" t="s">
         <v>20</v>
       </c>
       <c r="C571" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D571" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E571">
         <v>0</v>
       </c>
       <c r="F571" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G571">
         <v>0</v>
       </c>
       <c r="H571" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="I571" t="b">
         <v>0</v>
       </c>
       <c r="J571" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K571" s="1" t="d">
         <v>2026-06-12</v>
@@ -40231,27 +40231,27 @@
         <v>27</v>
       </c>
       <c r="U571" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="572" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B572" t="s">
         <v>20</v>
       </c>
       <c r="C572" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D572" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E572">
         <v>0</v>
       </c>
       <c r="F572" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G572">
         <v>0</v>
@@ -40296,27 +40296,27 @@
         <v>27</v>
       </c>
       <c r="U572" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="573" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B573" t="s">
         <v>20</v>
       </c>
       <c r="C573" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D573" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E573">
         <v>0</v>
       </c>
       <c r="F573" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G573">
         <v>0</v>
@@ -40328,7 +40328,7 @@
         <v>0</v>
       </c>
       <c r="J573" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K573" s="1" t="d">
         <v>2026-06-27</v>
@@ -40361,39 +40361,39 @@
         <v>27</v>
       </c>
       <c r="U573" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="574" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B574" t="s">
         <v>20</v>
       </c>
       <c r="C574" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D574" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E574">
         <v>0</v>
       </c>
       <c r="F574" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G574">
         <v>0</v>
       </c>
       <c r="H574" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="I574" t="b">
         <v>0</v>
       </c>
       <c r="J574" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="K574" s="1" t="d">
         <v>2026-06-28</v>
@@ -40426,39 +40426,39 @@
         <v>27</v>
       </c>
       <c r="U574" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="575" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B575" t="s">
         <v>20</v>
       </c>
       <c r="C575" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D575" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E575">
         <v>0</v>
       </c>
       <c r="F575" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G575">
         <v>0</v>
       </c>
       <c r="H575" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I575" t="b">
         <v>1</v>
       </c>
       <c r="J575" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="K575" s="1" t="d">
         <v>2026-07-17</v>
@@ -40491,27 +40491,27 @@
         <v>27</v>
       </c>
       <c r="U575" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="576" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B576" t="s">
         <v>20</v>
       </c>
       <c r="C576" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D576" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E576">
         <v>0</v>
       </c>
       <c r="F576" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G576">
         <v>0</v>
@@ -40556,39 +40556,39 @@
         <v>27</v>
       </c>
       <c r="U576" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="577" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B577" t="s">
         <v>20</v>
       </c>
       <c r="C577" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D577" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E577">
         <v>0</v>
       </c>
       <c r="F577" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G577">
         <v>0</v>
       </c>
       <c r="H577" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="I577" t="b">
         <v>0</v>
       </c>
       <c r="J577" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K577" s="1" t="d">
         <v>2026-07-30</v>
@@ -40621,39 +40621,39 @@
         <v>27</v>
       </c>
       <c r="U577" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="578" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B578" t="s">
         <v>20</v>
       </c>
       <c r="C578" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D578" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E578">
         <v>0</v>
       </c>
       <c r="F578" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G578">
         <v>0</v>
       </c>
       <c r="H578" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="I578" t="b">
         <v>0</v>
       </c>
       <c r="J578" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K578" s="1" t="d">
         <v>2026-07-30</v>
@@ -40686,27 +40686,27 @@
         <v>27</v>
       </c>
       <c r="U578" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="579" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B579" t="s">
         <v>20</v>
       </c>
       <c r="C579" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D579" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E579">
         <v>0</v>
       </c>
       <c r="F579" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G579">
         <v>0</v>
@@ -40718,7 +40718,7 @@
         <v>0</v>
       </c>
       <c r="J579" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K579" s="1" t="d">
         <v>2026-07-31</v>
@@ -40751,39 +40751,39 @@
         <v>27</v>
       </c>
       <c r="U579" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="580" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B580" t="s">
         <v>20</v>
       </c>
       <c r="C580" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D580" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E580">
         <v>0</v>
       </c>
       <c r="F580" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G580">
         <v>0</v>
       </c>
       <c r="H580" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="I580" t="b">
         <v>1</v>
       </c>
       <c r="J580" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K580" s="1" t="d">
         <v>2026-07-31</v>
@@ -40816,27 +40816,27 @@
         <v>27</v>
       </c>
       <c r="U580" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="581" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B581" t="s">
         <v>20</v>
       </c>
       <c r="C581" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D581" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E581">
         <v>0</v>
       </c>
       <c r="F581" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G581">
         <v>0</v>
@@ -40848,7 +40848,7 @@
         <v>0</v>
       </c>
       <c r="J581" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="K581" s="1" t="d">
         <v>2026-08-10</v>
@@ -40881,39 +40881,39 @@
         <v>27</v>
       </c>
       <c r="U581" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="582" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B582" t="s">
         <v>20</v>
       </c>
       <c r="C582" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D582" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E582">
         <v>0</v>
       </c>
       <c r="F582" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G582">
         <v>0</v>
       </c>
       <c r="H582" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="I582" t="b">
         <v>0</v>
       </c>
       <c r="J582" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K582" s="1" t="d">
         <v>2026-08-13</v>
@@ -40946,39 +40946,39 @@
         <v>27</v>
       </c>
       <c r="U582" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="583" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B583" t="s">
         <v>20</v>
       </c>
       <c r="C583" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D583" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E583">
         <v>0</v>
       </c>
       <c r="F583" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G583">
         <v>0</v>
       </c>
       <c r="H583" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I583" t="b">
         <v>1</v>
       </c>
       <c r="J583" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K583" s="1" t="d">
         <v>2026-08-24</v>
@@ -41011,39 +41011,39 @@
         <v>27</v>
       </c>
       <c r="U583" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="584" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B584" t="s">
         <v>20</v>
       </c>
       <c r="C584" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D584" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E584">
         <v>0</v>
       </c>
       <c r="F584" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G584">
         <v>0</v>
       </c>
       <c r="H584" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="I584" t="b">
         <v>1</v>
       </c>
       <c r="J584" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K584" s="1" t="d">
         <v>2026-08-26</v>
@@ -41076,39 +41076,39 @@
         <v>27</v>
       </c>
       <c r="U584" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="585" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B585" t="s">
         <v>20</v>
       </c>
       <c r="C585" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D585" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E585">
         <v>0</v>
       </c>
       <c r="F585" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G585">
         <v>0</v>
       </c>
       <c r="H585" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="I585" t="b">
         <v>1</v>
       </c>
       <c r="J585" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K585" s="1" t="d">
         <v>2026-08-26</v>
@@ -41141,39 +41141,39 @@
         <v>27</v>
       </c>
       <c r="U585" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="586" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B586" t="s">
         <v>20</v>
       </c>
       <c r="C586" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D586" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E586">
         <v>0</v>
       </c>
       <c r="F586" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G586">
         <v>1</v>
       </c>
       <c r="H586" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="I586" t="b">
         <v>1</v>
       </c>
       <c r="J586" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K586" s="1" t="d">
         <v>2026-08-26</v>
@@ -41206,39 +41206,39 @@
         <v>27</v>
       </c>
       <c r="U586" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="587" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B587" t="s">
         <v>20</v>
       </c>
       <c r="C587" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D587" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E587">
         <v>0</v>
       </c>
       <c r="F587" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G587">
         <v>0</v>
       </c>
       <c r="H587" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="I587" t="b">
         <v>1</v>
       </c>
       <c r="J587" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K587" s="1" t="d">
         <v>2026-08-26</v>
@@ -41271,27 +41271,27 @@
         <v>27</v>
       </c>
       <c r="U587" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="588" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B588" t="s">
         <v>20</v>
       </c>
       <c r="C588" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D588" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E588">
         <v>0</v>
       </c>
       <c r="F588" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G588">
         <v>0</v>
@@ -41303,7 +41303,7 @@
         <v>1</v>
       </c>
       <c r="J588" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="K588" s="1" t="d">
         <v>2026-09-01</v>
@@ -41336,39 +41336,39 @@
         <v>27</v>
       </c>
       <c r="U588" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="589" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B589" t="s">
         <v>20</v>
       </c>
       <c r="C589" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D589" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E589">
         <v>0</v>
       </c>
       <c r="F589" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G589">
         <v>0</v>
       </c>
       <c r="H589" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="I589" t="b">
         <v>0</v>
       </c>
       <c r="J589" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="K589" s="1" t="d">
         <v>2026-09-04</v>
@@ -41401,39 +41401,39 @@
         <v>27</v>
       </c>
       <c r="U589" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="590" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B590" t="s">
         <v>20</v>
       </c>
       <c r="C590" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D590" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E590">
         <v>0</v>
       </c>
       <c r="F590" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G590">
         <v>0</v>
       </c>
       <c r="H590" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="I590" t="b">
         <v>0</v>
       </c>
       <c r="J590" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="K590" s="1" t="d">
         <v>2026-09-09</v>
@@ -41466,33 +41466,33 @@
         <v>27</v>
       </c>
       <c r="U590" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="591" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B591" t="s">
         <v>20</v>
       </c>
       <c r="C591" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D591" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E591">
         <v>0</v>
       </c>
       <c r="F591" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G591">
         <v>0</v>
       </c>
       <c r="H591" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="I591" t="b">
         <v>0</v>
@@ -41531,33 +41531,33 @@
         <v>27</v>
       </c>
       <c r="U591" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="592" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B592" t="s">
         <v>20</v>
       </c>
       <c r="C592" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D592" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E592">
         <v>0</v>
       </c>
       <c r="F592" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G592">
         <v>0</v>
       </c>
       <c r="H592" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="I592" t="b">
         <v>0</v>
@@ -41596,39 +41596,39 @@
         <v>27</v>
       </c>
       <c r="U592" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="593" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B593" t="s">
         <v>20</v>
       </c>
       <c r="C593" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D593" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E593">
         <v>0</v>
       </c>
       <c r="F593" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G593">
         <v>0</v>
       </c>
       <c r="H593" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="I593" t="b">
         <v>0</v>
       </c>
       <c r="J593" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="K593" s="1" t="d">
         <v>2026-09-13</v>
@@ -41661,27 +41661,27 @@
         <v>27</v>
       </c>
       <c r="U593" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="594" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B594" t="s">
         <v>20</v>
       </c>
       <c r="C594" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D594" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E594">
         <v>0</v>
       </c>
       <c r="F594" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G594">
         <v>0</v>
@@ -41726,39 +41726,39 @@
         <v>27</v>
       </c>
       <c r="U594" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="595" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
+        <v>642</v>
+      </c>
+      <c r="B595" t="s">
+        <v>20</v>
+      </c>
+      <c r="C595" t="s">
+        <v>649</v>
+      </c>
+      <c r="D595" t="s">
         <v>644</v>
       </c>
-      <c r="B595" t="s">
-        <v>20</v>
-      </c>
-      <c r="C595" t="s">
-        <v>651</v>
-      </c>
-      <c r="D595" t="s">
-        <v>646</v>
-      </c>
       <c r="E595">
         <v>0</v>
       </c>
       <c r="F595" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G595">
         <v>0</v>
       </c>
       <c r="H595" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="I595" t="b">
         <v>1</v>
       </c>
       <c r="J595" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="K595" t="s">
         <v>35</v>
@@ -41791,39 +41791,39 @@
         <v>27</v>
       </c>
       <c r="U595" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="596" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
+        <v>717</v>
+      </c>
+      <c r="B596" t="s">
+        <v>20</v>
+      </c>
+      <c r="C596" t="s">
+        <v>718</v>
+      </c>
+      <c r="D596" t="s">
         <v>719</v>
       </c>
-      <c r="B596" t="s">
-        <v>20</v>
-      </c>
-      <c r="C596" t="s">
+      <c r="E596">
+        <v>1</v>
+      </c>
+      <c r="F596" t="s">
         <v>720</v>
       </c>
-      <c r="D596" t="s">
+      <c r="G596">
+        <v>0</v>
+      </c>
+      <c r="H596" t="s">
         <v>721</v>
       </c>
-      <c r="E596">
-        <v>1</v>
-      </c>
-      <c r="F596" t="s">
+      <c r="I596" t="b">
+        <v>0</v>
+      </c>
+      <c r="J596" t="s">
         <v>722</v>
-      </c>
-      <c r="G596">
-        <v>0</v>
-      </c>
-      <c r="H596" t="s">
-        <v>723</v>
-      </c>
-      <c r="I596" t="b">
-        <v>0</v>
-      </c>
-      <c r="J596" t="s">
-        <v>724</v>
       </c>
       <c r="K596" s="1" t="d">
         <v>2024-12-18</v>
@@ -41856,39 +41856,39 @@
         <v>27</v>
       </c>
       <c r="U596" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="597" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B597" t="s">
         <v>20</v>
       </c>
       <c r="C597" t="s">
+        <v>724</v>
+      </c>
+      <c r="D597" t="s">
+        <v>725</v>
+      </c>
+      <c r="E597">
+        <v>1</v>
+      </c>
+      <c r="F597" t="s">
         <v>726</v>
       </c>
-      <c r="D597" t="s">
+      <c r="G597">
+        <v>0</v>
+      </c>
+      <c r="H597" t="s">
         <v>727</v>
       </c>
-      <c r="E597">
-        <v>1</v>
-      </c>
-      <c r="F597" t="s">
+      <c r="I597" t="b">
+        <v>1</v>
+      </c>
+      <c r="J597" t="s">
         <v>728</v>
-      </c>
-      <c r="G597">
-        <v>0</v>
-      </c>
-      <c r="H597" t="s">
-        <v>729</v>
-      </c>
-      <c r="I597" t="b">
-        <v>1</v>
-      </c>
-      <c r="J597" t="s">
-        <v>730</v>
       </c>
       <c r="K597" s="1" t="d">
         <v>2026-05-05</v>
@@ -41921,39 +41921,39 @@
         <v>27</v>
       </c>
       <c r="U597" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="598" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B598" t="s">
         <v>20</v>
       </c>
       <c r="C598" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D598" t="s">
+        <v>725</v>
+      </c>
+      <c r="E598">
+        <v>1</v>
+      </c>
+      <c r="F598" t="s">
+        <v>730</v>
+      </c>
+      <c r="G598">
+        <v>0</v>
+      </c>
+      <c r="H598" t="s">
         <v>727</v>
       </c>
-      <c r="E598">
-        <v>1</v>
-      </c>
-      <c r="F598" t="s">
-        <v>732</v>
-      </c>
-      <c r="G598">
-        <v>0</v>
-      </c>
-      <c r="H598" t="s">
-        <v>729</v>
-      </c>
       <c r="I598" t="b">
         <v>1</v>
       </c>
       <c r="J598" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="K598" s="1" t="d">
         <v>2026-05-05</v>
@@ -41986,39 +41986,39 @@
         <v>27</v>
       </c>
       <c r="U598" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="599" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B599" t="s">
         <v>20</v>
       </c>
       <c r="C599" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D599" t="s">
+        <v>725</v>
+      </c>
+      <c r="E599">
+        <v>1</v>
+      </c>
+      <c r="F599" t="s">
+        <v>732</v>
+      </c>
+      <c r="G599">
+        <v>0</v>
+      </c>
+      <c r="H599" t="s">
         <v>727</v>
       </c>
-      <c r="E599">
-        <v>1</v>
-      </c>
-      <c r="F599" t="s">
-        <v>734</v>
-      </c>
-      <c r="G599">
-        <v>0</v>
-      </c>
-      <c r="H599" t="s">
-        <v>729</v>
-      </c>
       <c r="I599" t="b">
         <v>1</v>
       </c>
       <c r="J599" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="K599" s="1" t="d">
         <v>2026-05-05</v>
@@ -42051,27 +42051,27 @@
         <v>27</v>
       </c>
       <c r="U599" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="600" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B600" t="s">
         <v>20</v>
       </c>
       <c r="C600" t="s">
+        <v>724</v>
+      </c>
+      <c r="D600" t="s">
+        <v>725</v>
+      </c>
+      <c r="E600">
+        <v>1</v>
+      </c>
+      <c r="F600" t="s">
         <v>726</v>
-      </c>
-      <c r="D600" t="s">
-        <v>727</v>
-      </c>
-      <c r="E600">
-        <v>1</v>
-      </c>
-      <c r="F600" t="s">
-        <v>728</v>
       </c>
       <c r="G600">
         <v>0</v>
@@ -42083,7 +42083,7 @@
         <v>0</v>
       </c>
       <c r="J600" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="K600" s="1" t="d">
         <v>2026-06-16</v>
@@ -42116,27 +42116,27 @@
         <v>27</v>
       </c>
       <c r="U600" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="601" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B601" t="s">
         <v>20</v>
       </c>
       <c r="C601" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D601" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E601">
         <v>1</v>
       </c>
       <c r="F601" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G601">
         <v>0</v>
@@ -42148,7 +42148,7 @@
         <v>0</v>
       </c>
       <c r="J601" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="K601" s="1" t="d">
         <v>2026-06-16</v>
@@ -42181,27 +42181,27 @@
         <v>27</v>
       </c>
       <c r="U601" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="602" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B602" t="s">
         <v>20</v>
       </c>
       <c r="C602" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D602" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E602">
         <v>1</v>
       </c>
       <c r="F602" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="G602">
         <v>0</v>
@@ -42213,7 +42213,7 @@
         <v>0</v>
       </c>
       <c r="J602" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="K602" s="1" t="d">
         <v>2026-06-16</v>
@@ -42246,7 +42246,7 @@
         <v>27</v>
       </c>
       <c r="U602" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
